--- a/platform-resources/bytedance-aidp/jinhua-helper/ai/assets/jinhua-pronunciation-reference.xlsx
+++ b/platform-resources/bytedance-aidp/jinhua-helper/ai/assets/jinhua-pronunciation-reference.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金华话差异表" sheetId="1" r:id="R1f776b0c0c3d4d10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="金华话差异表" sheetId="1" r:id="R99d7b23afa6f4c75"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,7 +334,7 @@
         <x:v>日头</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>ȵiəʔ21diu14</x:v>
+        <x:v>nie diu</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -348,7 +348,7 @@
         <x:v>星</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>ɕiŋ334</x:v>
+        <x:v>xing</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -362,7 +362,7 @@
         <x:v>霍刷=</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>xuəʔ3ɕyəʔ4</x:v>
+        <x:v>xue xye</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -376,7 +376,7 @@
         <x:v>天雷</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>thia33lɛ55</x:v>
+        <x:v>thia le</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -390,7 +390,7 @@
         <x:v>落雨</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>loʔ21Ǿy535</x:v>
+        <x:v>lo y</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -404,7 +404,7 @@
         <x:v>沰</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>toʔ4</x:v>
+        <x:v>to</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -418,7 +418,7 @@
         <x:v>落</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>loʔ212</x:v>
+        <x:v>lo</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -432,7 +432,7 @@
         <x:v>露水</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>lu53ɕy535</x:v>
+        <x:v>lu xy</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -446,7 +446,7 @@
         <x:v>鲎</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>xiu55</x:v>
+        <x:v>xiu</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -460,7 +460,7 @@
         <x:v>天狗吃日头</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>thia33kiu535tɕhiəʔ4ȵiəʔ21diu14</x:v>
+        <x:v>thia kiu qie nie diu</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -474,7 +474,7 @@
         <x:v>天狗吃月亮</x:v>
       </x:c>
       <x:c r="D12" s="5" t="str">
-        <x:v>thia33kiu535tɕhiəʔ4ȵyɤ55liɑŋ14</x:v>
+        <x:v>thia kiu qie nye liang</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -488,7 +488,7 @@
         <x:v>天公</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>thia33koŋ55</x:v>
+        <x:v>thia kong</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -502,7 +502,7 @@
         <x:v>晒去</x:v>
       </x:c>
       <x:c r="D14" s="5" t="str">
-        <x:v>sɑ55khɤ0</x:v>
+        <x:v>sa khe</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -516,7 +516,7 @@
         <x:v>满大水</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>mɤ53tuɤ53ɕy535</x:v>
+        <x:v>me tue xy</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -530,7 +530,7 @@
         <x:v>涨大水</x:v>
       </x:c>
       <x:c r="D16" s="5" t="str">
-        <x:v>tɕiɑŋ53tuɤ53ɕy535</x:v>
+        <x:v>jiang tue xy</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -544,7 +544,7 @@
         <x:v>燥田</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
-        <x:v>sɑo55dia313</x:v>
+        <x:v>sao dia</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -558,7 +558,7 @@
         <x:v>田塍</x:v>
       </x:c>
       <x:c r="D18" s="5" t="str">
-        <x:v>dia31ʑiŋ14</x:v>
+        <x:v>dia ring</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -572,7 +572,7 @@
         <x:v>山峡</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
-        <x:v>sɑ33ɡuɑ14</x:v>
+        <x:v>sa gua</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -586,7 +586,7 @@
         <x:v>大溪</x:v>
       </x:c>
       <x:c r="D20" s="5" t="str">
-        <x:v>tuɤ53tɕhie55</x:v>
+        <x:v>tue qie</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -600,7 +600,7 @@
         <x:v>小溪</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
-        <x:v>siɑo55tɕhie334</x:v>
+        <x:v>siao qie</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -614,7 +614,7 @@
         <x:v>渎</x:v>
       </x:c>
       <x:c r="D22" s="5" t="str">
-        <x:v>doʔ212</x:v>
+        <x:v>do</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -628,7 +628,7 @@
         <x:v>水渎</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
-        <x:v>ɕy55doʔ212</x:v>
+        <x:v>xy do</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -642,7 +642,7 @@
         <x:v>塘</x:v>
       </x:c>
       <x:c r="D24" s="5" t="str">
-        <x:v>dɑŋ313</x:v>
+        <x:v>dang</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -656,7 +656,7 @@
         <x:v>水堰＝凼</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
-        <x:v>ɕy55Ǿie55dɑŋ313</x:v>
+        <x:v>xy ie dang</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -670,7 +670,7 @@
         <x:v>大水</x:v>
       </x:c>
       <x:c r="D26" s="5" t="str">
-        <x:v>tuɤ53ɕy535</x:v>
+        <x:v>tue xy</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -684,7 +684,7 @@
         <x:v>𩑦</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str">
-        <x:v>Ǿuəʔ4</x:v>
+        <x:v>ue</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -698,7 +698,7 @@
         <x:v>磡</x:v>
       </x:c>
       <x:c r="D28" s="5" t="str">
-        <x:v>khɤ55</x:v>
+        <x:v>khe</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -712,7 +712,7 @@
         <x:v>岸</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
-        <x:v>Ǿɤ14</x:v>
+        <x:v>e</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -726,7 +726,7 @@
         <x:v>缝</x:v>
       </x:c>
       <x:c r="D30" s="5" t="str">
-        <x:v>voŋ14</x:v>
+        <x:v>vong</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -740,7 +740,7 @@
         <x:v>糊泥</x:v>
       </x:c>
       <x:c r="D31" s="5" t="str">
-        <x:v>Ǿu31ȵie14</x:v>
+        <x:v>u nie</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -754,7 +754,7 @@
         <x:v>糊泥</x:v>
       </x:c>
       <x:c r="D32" s="5" t="str">
-        <x:v>Ǿu31ȵie14</x:v>
+        <x:v>u nie</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -768,7 +768,7 @@
         <x:v>洋灰</x:v>
       </x:c>
       <x:c r="D33" s="5" t="str">
-        <x:v>Ǿiɑŋ31xui55</x:v>
+        <x:v>iang xui</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -782,7 +782,7 @@
         <x:v>沙泥</x:v>
       </x:c>
       <x:c r="D34" s="5" t="str">
-        <x:v>suɑ33ȵie55</x:v>
+        <x:v>sua nie</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -796,7 +796,7 @@
         <x:v>砖头</x:v>
       </x:c>
       <x:c r="D35" s="5" t="str">
-        <x:v>tɕyɤ33tiu55</x:v>
+        <x:v>jye tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -810,7 +810,7 @@
         <x:v>瓦片</x:v>
       </x:c>
       <x:c r="D36" s="5" t="str">
-        <x:v>Ǿuɑ53phie55</x:v>
+        <x:v>ua phie</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -824,7 +824,7 @@
         <x:v>洋油</x:v>
       </x:c>
       <x:c r="D37" s="5" t="str">
-        <x:v>Ǿiɑŋ31Ǿiu14</x:v>
+        <x:v>iang iu</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -838,7 +838,7 @@
         <x:v>灰塕</x:v>
       </x:c>
       <x:c r="D38" s="5" t="str">
-        <x:v>xui33Ǿoŋ535</x:v>
+        <x:v>xui ong</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -852,7 +852,7 @@
         <x:v>火着</x:v>
       </x:c>
       <x:c r="D39" s="5" t="str">
-        <x:v>xuɤ55dʑiəʔ212</x:v>
+        <x:v>xue jie</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -866,7 +866,7 @@
         <x:v>冷水</x:v>
       </x:c>
       <x:c r="D40" s="5" t="str">
-        <x:v>lɑŋ53ɕy535</x:v>
+        <x:v>lang xy</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -880,7 +880,7 @@
         <x:v>滚汤</x:v>
       </x:c>
       <x:c r="D41" s="5" t="str">
-        <x:v>kuəŋ55thɑŋ334</x:v>
+        <x:v>kueng thang</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -894,7 +894,7 @@
         <x:v>茶</x:v>
       </x:c>
       <x:c r="D42" s="5" t="str">
-        <x:v>dzuɑ313</x:v>
+        <x:v>dzua</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -908,7 +908,7 @@
         <x:v>吸铁石</x:v>
       </x:c>
       <x:c r="D43" s="5" t="str">
-        <x:v>ɕiəʔ3thia55ʑiəʔ212</x:v>
+        <x:v>xie thia rie</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -922,7 +922,7 @@
         <x:v>时节</x:v>
       </x:c>
       <x:c r="D44" s="5" t="str">
-        <x:v>zɿ31tsia55</x:v>
+        <x:v>zi tsia</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -936,7 +936,7 @@
         <x:v>哪记</x:v>
       </x:c>
       <x:c r="D45" s="5" t="str">
-        <x:v>lɑ53tɕie55</x:v>
+        <x:v>la jie</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -950,7 +950,7 @@
         <x:v>哪样节</x:v>
       </x:c>
       <x:c r="D46" s="5" t="str">
-        <x:v>lɑ53Ǿiɑŋ55tsia0</x:v>
+        <x:v>la iang tsia</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -964,7 +964,7 @@
         <x:v>个记</x:v>
       </x:c>
       <x:c r="D47" s="5" t="str">
-        <x:v>kəʔ3tɕie55</x:v>
+        <x:v>ke jie</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -978,7 +978,7 @@
         <x:v>样节</x:v>
       </x:c>
       <x:c r="D48" s="5" t="str">
-        <x:v>Ǿiɑŋ55tsia0</x:v>
+        <x:v>iang tsia</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -992,7 +992,7 @@
         <x:v>一世</x:v>
       </x:c>
       <x:c r="D49" s="5" t="str">
-        <x:v>Ǿiəʔ3ɕyɤ55</x:v>
+        <x:v>ie xye</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -1006,7 +1006,7 @@
         <x:v>上年</x:v>
       </x:c>
       <x:c r="D50" s="5" t="str">
-        <x:v>ɕiɑŋ55ȵia14</x:v>
+        <x:v>xiang nia</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -1020,7 +1020,7 @@
         <x:v>今日儿</x:v>
       </x:c>
       <x:c r="D51" s="5" t="str">
-        <x:v>tɕiŋ33ȵi55</x:v>
+        <x:v>jing ni</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -1034,7 +1034,7 @@
         <x:v>明朝</x:v>
       </x:c>
       <x:c r="D52" s="5" t="str">
-        <x:v>miŋ33tɕiɑo334</x:v>
+        <x:v>ming jiao</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -1048,7 +1048,7 @@
         <x:v>后日</x:v>
       </x:c>
       <x:c r="D53" s="5" t="str">
-        <x:v>Ǿeu55ȵiəʔ12</x:v>
+        <x:v>eu nie</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -1062,7 +1062,7 @@
         <x:v>大后日</x:v>
       </x:c>
       <x:c r="D54" s="5" t="str">
-        <x:v>duɤ14Ǿeu55ȵiəʔ12</x:v>
+        <x:v>due eu nie</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -1076,7 +1076,7 @@
         <x:v>昨儿日儿</x:v>
       </x:c>
       <x:c r="D55" s="5" t="str">
-        <x:v>sɑŋ55ȵi14</x:v>
+        <x:v>sang ni</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -1090,7 +1090,7 @@
         <x:v>前日儿</x:v>
       </x:c>
       <x:c r="D56" s="5" t="str">
-        <x:v>zia31ȵi14</x:v>
+        <x:v>zia ni</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -1104,7 +1104,7 @@
         <x:v>大前日儿</x:v>
       </x:c>
       <x:c r="D57" s="5" t="str">
-        <x:v>duɤ14zia31ȵi14</x:v>
+        <x:v>due zia ni</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -1118,7 +1118,7 @@
         <x:v>整日</x:v>
       </x:c>
       <x:c r="D58" s="5" t="str">
-        <x:v>tɕiŋ55ȵiəʔ12</x:v>
+        <x:v>jing nie</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -1132,7 +1132,7 @@
         <x:v>每日</x:v>
       </x:c>
       <x:c r="D59" s="5" t="str">
-        <x:v>mɛ55ȵiəʔ12</x:v>
+        <x:v>me nie</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -1146,7 +1146,7 @@
         <x:v>五更儿</x:v>
       </x:c>
       <x:c r="D60" s="5" t="str">
-        <x:v>Ǿŋ55kɛ̃334</x:v>
+        <x:v>ng ke</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -1160,7 +1160,7 @@
         <x:v>五更儿头儿</x:v>
       </x:c>
       <x:c r="D61" s="5" t="str">
-        <x:v>Ǿŋ55kɛ̃33diŋ313</x:v>
+        <x:v>ng ke ding</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -1174,7 +1174,7 @@
         <x:v>五更儿</x:v>
       </x:c>
       <x:c r="D62" s="5" t="str">
-        <x:v>Ǿŋ55kɛ̃334</x:v>
+        <x:v>ng ke</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -1188,7 +1188,7 @@
         <x:v>午前</x:v>
       </x:c>
       <x:c r="D63" s="5" t="str">
-        <x:v>Ǿŋ55zia313</x:v>
+        <x:v>ng zia</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -1202,7 +1202,7 @@
         <x:v>午饭</x:v>
       </x:c>
       <x:c r="D64" s="5" t="str">
-        <x:v>Ǿŋ55vɑ14</x:v>
+        <x:v>ng va</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -1216,7 +1216,7 @@
         <x:v>午罢</x:v>
       </x:c>
       <x:c r="D65" s="5" t="str">
-        <x:v>Ǿŋ33pɑ535</x:v>
+        <x:v>ng pa</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -1230,7 +1230,7 @@
         <x:v>午罢头儿</x:v>
       </x:c>
       <x:c r="D66" s="5" t="str">
-        <x:v>Ǿŋ33pɑ55diŋ313</x:v>
+        <x:v>ng pa ding</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -1244,7 +1244,7 @@
         <x:v>靠夜干</x:v>
       </x:c>
       <x:c r="D67" s="5" t="str">
-        <x:v>khɑo33Ǿia53kɤ55</x:v>
+        <x:v>khao ia ke</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -1258,7 +1258,7 @@
         <x:v>日里</x:v>
       </x:c>
       <x:c r="D68" s="5" t="str">
-        <x:v>ȵiəʔ21li14</x:v>
+        <x:v>nie li</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -1272,7 +1272,7 @@
         <x:v>夜里</x:v>
       </x:c>
       <x:c r="D69" s="5" t="str">
-        <x:v>Ǿia14li0</x:v>
+        <x:v>ia li</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -1286,7 +1286,7 @@
         <x:v>正月头</x:v>
       </x:c>
       <x:c r="D70" s="5" t="str">
-        <x:v>tɕiŋ33ȵyɤ55diu313</x:v>
+        <x:v>jing nye diu</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -1300,7 +1300,7 @@
         <x:v>年初一</x:v>
       </x:c>
       <x:c r="D71" s="5" t="str">
-        <x:v>ȵia33tshu33Ǿiəʔ4</x:v>
+        <x:v>nia tshu ie</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -1314,7 +1314,7 @@
         <x:v>元宵</x:v>
       </x:c>
       <x:c r="D72" s="5" t="str">
-        <x:v>Ǿyɛ̃31siɑo55</x:v>
+        <x:v>ye siao</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -1328,7 +1328,7 @@
         <x:v>七月半</x:v>
       </x:c>
       <x:c r="D73" s="5" t="str">
-        <x:v>tɕhiəʔ4ȵyɤ53pɤ55</x:v>
+        <x:v>qie nye pe</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -1342,7 +1342,7 @@
         <x:v>八月半</x:v>
       </x:c>
       <x:c r="D74" s="5" t="str">
-        <x:v>pɤa55ȵyɤ53pɤ55</x:v>
+        <x:v>pea nye pe</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -1356,7 +1356,7 @@
         <x:v>冬夜</x:v>
       </x:c>
       <x:c r="D75" s="5" t="str">
-        <x:v>toŋ33Ǿia55</x:v>
+        <x:v>tong ia</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -1370,7 +1370,7 @@
         <x:v>十两月</x:v>
       </x:c>
       <x:c r="D76" s="5" t="str">
-        <x:v>ɕiəʔ3liɑŋ55ȵyɤ14</x:v>
+        <x:v>xie liang nye</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -1384,7 +1384,7 @@
         <x:v>三十夜</x:v>
       </x:c>
       <x:c r="D77" s="5" t="str">
-        <x:v>sɑ33ɕiəʔ3Ǿia14</x:v>
+        <x:v>sa xie ia</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -1398,7 +1398,7 @@
         <x:v>农历</x:v>
       </x:c>
       <x:c r="D78" s="5" t="str">
-        <x:v>loŋ31liəʔ212</x:v>
+        <x:v>long lie</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -1412,7 +1412,7 @@
         <x:v>星期日</x:v>
       </x:c>
       <x:c r="D79" s="5" t="str">
-        <x:v>ɕiŋ33tɕi33ȵiəʔ212</x:v>
+        <x:v>xing ji nie</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -1426,7 +1426,7 @@
         <x:v>哪个地方</x:v>
       </x:c>
       <x:c r="D80" s="5" t="str">
-        <x:v>lɑ55kəʔ0ti53fɑŋ55</x:v>
+        <x:v>la ke ti fang</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -1440,7 +1440,7 @@
         <x:v>哪里</x:v>
       </x:c>
       <x:c r="D81" s="5" t="str">
-        <x:v>lɑ55li313</x:v>
+        <x:v>la li</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -1454,7 +1454,7 @@
         <x:v>哪耷</x:v>
       </x:c>
       <x:c r="D82" s="5" t="str">
-        <x:v>lɑ55dɑ14</x:v>
+        <x:v>la da</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -1468,7 +1468,7 @@
         <x:v>窝＝里</x:v>
       </x:c>
       <x:c r="D83" s="5" t="str">
-        <x:v>Ǿuɤ33li535</x:v>
+        <x:v>ue li</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -1482,7 +1482,7 @@
         <x:v>乡里</x:v>
       </x:c>
       <x:c r="D84" s="5" t="str">
-        <x:v>ɕiɑŋ33li55</x:v>
+        <x:v>xiang li</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -1496,7 +1496,7 @@
         <x:v>下底</x:v>
       </x:c>
       <x:c r="D85" s="5" t="str">
-        <x:v>Ǿuɑ53tie535</x:v>
+        <x:v>ua tie</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -1510,7 +1510,7 @@
         <x:v>左面</x:v>
       </x:c>
       <x:c r="D86" s="5" t="str">
-        <x:v>tsuɤ55mie0</x:v>
+        <x:v>tsue mie</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -1524,7 +1524,7 @@
         <x:v>右面</x:v>
       </x:c>
       <x:c r="D87" s="5" t="str">
-        <x:v>Ǿiu14mie0</x:v>
+        <x:v>iu mie</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -1538,7 +1538,7 @@
         <x:v>中央</x:v>
       </x:c>
       <x:c r="D88" s="5" t="str">
-        <x:v>tɕioŋ33Ǿiɑŋ55</x:v>
+        <x:v>jiong iang</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -1552,7 +1552,7 @@
         <x:v>罢=末</x:v>
       </x:c>
       <x:c r="D89" s="5" t="str">
-        <x:v>pɑ55mɤ14</x:v>
+        <x:v>pa me</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -1566,7 +1566,7 @@
         <x:v>面头前</x:v>
       </x:c>
       <x:c r="D90" s="5" t="str">
-        <x:v>mie55diu31zia14</x:v>
+        <x:v>mie diu zia</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -1580,7 +1580,7 @@
         <x:v>背脊后</x:v>
       </x:c>
       <x:c r="D91" s="5" t="str">
-        <x:v>pɛ33tɕiəʔ3Ǿeu535</x:v>
+        <x:v>pe jie eu</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -1594,7 +1594,7 @@
         <x:v>下底</x:v>
       </x:c>
       <x:c r="D92" s="5" t="str">
-        <x:v>Ǿuɑ53tie535</x:v>
+        <x:v>ua tie</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -1608,7 +1608,7 @@
         <x:v>边沿</x:v>
       </x:c>
       <x:c r="D93" s="5" t="str">
-        <x:v>pie33Ǿie55</x:v>
+        <x:v>pie ie</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -1622,7 +1622,7 @@
         <x:v>角落头</x:v>
       </x:c>
       <x:c r="D94" s="5" t="str">
-        <x:v>koʔ4loʔ4tiu55</x:v>
+        <x:v>ko lo tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -1636,7 +1636,7 @@
         <x:v>落来</x:v>
       </x:c>
       <x:c r="D95" s="5" t="str">
-        <x:v>loʔ21lɛ14</x:v>
+        <x:v>lo le</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -1650,7 +1650,7 @@
         <x:v>归来</x:v>
       </x:c>
       <x:c r="D96" s="5" t="str">
-        <x:v>kui33lɛ55</x:v>
+        <x:v>kui le</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -1664,7 +1664,7 @@
         <x:v>转来</x:v>
       </x:c>
       <x:c r="D97" s="5" t="str">
-        <x:v>tɕyɤ55lɛ14</x:v>
+        <x:v>jye le</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -1678,7 +1678,7 @@
         <x:v>杨柳树</x:v>
       </x:c>
       <x:c r="D98" s="5" t="str">
-        <x:v>Ǿiɑŋ33liu55ʑy14</x:v>
+        <x:v>iang liu ry</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -1692,7 +1692,7 @@
         <x:v>毛竹</x:v>
       </x:c>
       <x:c r="D99" s="5" t="str">
-        <x:v>mɑo33tɕioʔ4</x:v>
+        <x:v>mao jio</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -1706,7 +1706,7 @@
         <x:v>叶</x:v>
       </x:c>
       <x:c r="D100" s="5" t="str">
-        <x:v>Ǿie14</x:v>
+        <x:v>ie</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -1720,7 +1720,7 @@
         <x:v>花蕊儿</x:v>
       </x:c>
       <x:c r="D101" s="5" t="str">
-        <x:v>xuɑ33ȵy14</x:v>
+        <x:v>xua ny</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -1734,7 +1734,7 @@
         <x:v>桃</x:v>
       </x:c>
       <x:c r="D102" s="5" t="str">
-        <x:v>dɑo313</x:v>
+        <x:v>dao</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -1748,7 +1748,7 @@
         <x:v>李儿</x:v>
       </x:c>
       <x:c r="D103" s="5" t="str">
-        <x:v>li14</x:v>
+        <x:v>li</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -1762,7 +1762,7 @@
         <x:v>梅</x:v>
       </x:c>
       <x:c r="D104" s="5" t="str">
-        <x:v>mɛ313</x:v>
+        <x:v>me</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -1776,7 +1776,7 @@
         <x:v>桔儿</x:v>
       </x:c>
       <x:c r="D105" s="5" t="str">
-        <x:v>tɕyẽ55</x:v>
+        <x:v>jye</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -1790,7 +1790,7 @@
         <x:v>扑=</x:v>
       </x:c>
       <x:c r="D106" s="5" t="str">
-        <x:v>phoʔ4</x:v>
+        <x:v>pho</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -1804,7 +1804,7 @@
         <x:v>香扑=</x:v>
       </x:c>
       <x:c r="D107" s="5" t="str">
-        <x:v>ɕiɑŋ33phoʔ4</x:v>
+        <x:v>xiang pho</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -1818,7 +1818,7 @@
         <x:v>柿儿</x:v>
       </x:c>
       <x:c r="D108" s="5" t="str">
-        <x:v>zɿ14</x:v>
+        <x:v>zi</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -1832,7 +1832,7 @@
         <x:v>枣儿</x:v>
       </x:c>
       <x:c r="D109" s="5" t="str">
-        <x:v>tsɑo55</x:v>
+        <x:v>tsao</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -1846,7 +1846,7 @@
         <x:v>大栗</x:v>
       </x:c>
       <x:c r="D110" s="5" t="str">
-        <x:v>tuɤ53liəʔ212</x:v>
+        <x:v>tue lie</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -1860,7 +1860,7 @@
         <x:v>胡桃</x:v>
       </x:c>
       <x:c r="D111" s="5" t="str">
-        <x:v>Ǿu31dɑo14</x:v>
+        <x:v>u dao</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -1874,7 +1874,7 @@
         <x:v>白果</x:v>
       </x:c>
       <x:c r="D112" s="5" t="str">
-        <x:v>bəʔ21kuɤ535</x:v>
+        <x:v>be kue</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -1888,7 +1888,7 @@
         <x:v>蕈</x:v>
       </x:c>
       <x:c r="D113" s="5" t="str">
-        <x:v>ɕiŋ535</x:v>
+        <x:v>xing</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -1902,7 +1902,7 @@
         <x:v>谷</x:v>
       </x:c>
       <x:c r="D114" s="5" t="str">
-        <x:v>koʔ4</x:v>
+        <x:v>ko</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -1916,7 +1916,7 @@
         <x:v>稻秆</x:v>
       </x:c>
       <x:c r="D115" s="5" t="str">
-        <x:v>tɑo53kɤ535</x:v>
+        <x:v>tao ke</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -1930,7 +1930,7 @@
         <x:v>麦秆</x:v>
       </x:c>
       <x:c r="D116" s="5" t="str">
-        <x:v>məʔ21kɤ535</x:v>
+        <x:v>me ke</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -1944,7 +1944,7 @@
         <x:v>粟</x:v>
       </x:c>
       <x:c r="D117" s="5" t="str">
-        <x:v>soʔ4</x:v>
+        <x:v>so</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -1958,7 +1958,7 @@
         <x:v>芦穄</x:v>
       </x:c>
       <x:c r="D118" s="5" t="str">
-        <x:v>lu31tɕie55</x:v>
+        <x:v>lu jie</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -1972,7 +1972,7 @@
         <x:v>包萝</x:v>
       </x:c>
       <x:c r="D119" s="5" t="str">
-        <x:v>pɑo33luɤ55</x:v>
+        <x:v>pao lue</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -1986,7 +1986,7 @@
         <x:v>油麻</x:v>
       </x:c>
       <x:c r="D120" s="5" t="str">
-        <x:v>Ǿiu31mɤa14</x:v>
+        <x:v>iu mea</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -2000,7 +2000,7 @@
         <x:v>朝日葵</x:v>
       </x:c>
       <x:c r="D121" s="5" t="str">
-        <x:v>tɕiɑo33ȵiəʔ21dʑy14</x:v>
+        <x:v>jiao nie jy</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -2014,7 +2014,7 @@
         <x:v>佛豆</x:v>
       </x:c>
       <x:c r="D122" s="5" t="str">
-        <x:v>vəʔ21diu14</x:v>
+        <x:v>ve diu</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -2028,7 +2028,7 @@
         <x:v>蚕豆</x:v>
       </x:c>
       <x:c r="D123" s="5" t="str">
-        <x:v>zɤ31diu14</x:v>
+        <x:v>ze diu</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -2042,7 +2042,7 @@
         <x:v>落花生</x:v>
       </x:c>
       <x:c r="D124" s="5" t="str">
-        <x:v>loʔ21xuɑ33sɑŋ55</x:v>
+        <x:v>lo xua sang</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -2056,7 +2056,7 @@
         <x:v>豆</x:v>
       </x:c>
       <x:c r="D125" s="5" t="str">
-        <x:v>diu14</x:v>
+        <x:v>diu</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -2070,7 +2070,7 @@
         <x:v>胶菜</x:v>
       </x:c>
       <x:c r="D126" s="5" t="str">
-        <x:v>tɕiɑo33tshɛ55</x:v>
+        <x:v>jiao tshe</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -2084,7 +2084,7 @@
         <x:v>球菜</x:v>
       </x:c>
       <x:c r="D127" s="5" t="str">
-        <x:v>dʑiu31tshɛ55</x:v>
+        <x:v>jiu tshe</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -2098,7 +2098,7 @@
         <x:v>菠薐菜</x:v>
       </x:c>
       <x:c r="D128" s="5" t="str">
-        <x:v>po33ləŋ33tshɛ55</x:v>
+        <x:v>po leng tshe</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -2112,7 +2112,7 @@
         <x:v>圈=葱</x:v>
       </x:c>
       <x:c r="D129" s="5" t="str">
-        <x:v>tɕhyɤ33tshoŋ55</x:v>
+        <x:v>qye tshong</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -2126,7 +2126,7 @@
         <x:v>莴苣笋</x:v>
       </x:c>
       <x:c r="D130" s="5" t="str">
-        <x:v>Ǿu33tɕy33ɕiŋ535</x:v>
+        <x:v>u jy xing</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -2140,7 +2140,7 @@
         <x:v>芫荽</x:v>
       </x:c>
       <x:c r="D131" s="5" t="str">
-        <x:v>Ǿyɛ̃31suɛ̃55</x:v>
+        <x:v>ye sue</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -2154,7 +2154,7 @@
         <x:v>大蒜</x:v>
       </x:c>
       <x:c r="D132" s="5" t="str">
-        <x:v>dɑ31sɤ55</x:v>
+        <x:v>da se</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -2168,7 +2168,7 @@
         <x:v>生姜</x:v>
       </x:c>
       <x:c r="D133" s="5" t="str">
-        <x:v>sɑŋ33tɕiɑŋ55</x:v>
+        <x:v>sang jiang</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -2182,7 +2182,7 @@
         <x:v>辣虎</x:v>
       </x:c>
       <x:c r="D134" s="5" t="str">
-        <x:v>luɑ53xu55</x:v>
+        <x:v>lua xu</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -2196,7 +2196,7 @@
         <x:v>落苏</x:v>
       </x:c>
       <x:c r="D135" s="5" t="str">
-        <x:v>loʔ21su55</x:v>
+        <x:v>lo su</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -2210,7 +2210,7 @@
         <x:v>番茄</x:v>
       </x:c>
       <x:c r="D136" s="5" t="str">
-        <x:v>fɛ̃33tɕia55</x:v>
+        <x:v>fe jia</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -2224,7 +2224,7 @@
         <x:v>红萝卜</x:v>
       </x:c>
       <x:c r="D137" s="5" t="str">
-        <x:v>Ǿoŋ33lɑo33boʔ212</x:v>
+        <x:v>ong lao bo</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -2238,7 +2238,7 @@
         <x:v>天萝</x:v>
       </x:c>
       <x:c r="D138" s="5" t="str">
-        <x:v>thia33luɤ55</x:v>
+        <x:v>thia lue</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -2252,7 +2252,7 @@
         <x:v>金瓜</x:v>
       </x:c>
       <x:c r="D139" s="5" t="str">
-        <x:v>tɕiŋ33kuɑ55</x:v>
+        <x:v>jing kua</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -2266,7 +2266,7 @@
         <x:v>番芋</x:v>
       </x:c>
       <x:c r="D140" s="5" t="str">
-        <x:v>xuɑ33Ǿy55</x:v>
+        <x:v>xua y</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -2280,7 +2280,7 @@
         <x:v>洋芋</x:v>
       </x:c>
       <x:c r="D141" s="5" t="str">
-        <x:v>Ǿiɑŋ31Ǿy14</x:v>
+        <x:v>iang y</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -2294,7 +2294,7 @@
         <x:v>毛芋</x:v>
       </x:c>
       <x:c r="D142" s="5" t="str">
-        <x:v>mɑo31Ǿy14</x:v>
+        <x:v>mao y</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -2308,7 +2308,7 @@
         <x:v>猢狲</x:v>
       </x:c>
       <x:c r="D143" s="5" t="str">
-        <x:v>Ǿuəʔ21səŋ55</x:v>
+        <x:v>ue seng</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -2322,7 +2322,7 @@
         <x:v>老鼠皮翼</x:v>
       </x:c>
       <x:c r="D144" s="5" t="str">
-        <x:v>lɑo53tshɿ535pi33Ǿiəʔ212</x:v>
+        <x:v>lao tshi pi ie</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -2336,7 +2336,7 @@
         <x:v>麻雀儿</x:v>
       </x:c>
       <x:c r="D145" s="5" t="str">
-        <x:v>mɤa31tɕi55</x:v>
+        <x:v>mea ji</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -2350,7 +2350,7 @@
         <x:v>乌老鸦</x:v>
       </x:c>
       <x:c r="D146" s="5" t="str">
-        <x:v>Ǿu33lɑo53Ǿuɑ55</x:v>
+        <x:v>u lao ua</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -2364,7 +2364,7 @@
         <x:v>鹁鸽</x:v>
       </x:c>
       <x:c r="D147" s="5" t="str">
-        <x:v>boʔ21kɤ55</x:v>
+        <x:v>bo ke</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -2378,7 +2378,7 @@
         <x:v>翼膀</x:v>
       </x:c>
       <x:c r="D148" s="5" t="str">
-        <x:v>Ǿiəʔ21pɑŋ535</x:v>
+        <x:v>ie pang</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -2392,7 +2392,7 @@
         <x:v>爪</x:v>
       </x:c>
       <x:c r="D149" s="5" t="str">
-        <x:v>tsɑo535</x:v>
+        <x:v>tsao</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -2406,7 +2406,7 @@
         <x:v>尾巴儿</x:v>
       </x:c>
       <x:c r="D150" s="5" t="str">
-        <x:v>Ǿm55pɤɛ̃334</x:v>
+        <x:v>m pee</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -2420,7 +2420,7 @@
         <x:v>窠</x:v>
       </x:c>
       <x:c r="D151" s="5" t="str">
-        <x:v>khuɤ334</x:v>
+        <x:v>khue</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -2434,7 +2434,7 @@
         <x:v>虫</x:v>
       </x:c>
       <x:c r="D152" s="5" t="str">
-        <x:v>dʑioŋ313</x:v>
+        <x:v>jiong</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -2448,7 +2448,7 @@
         <x:v>蝴蝶儿</x:v>
       </x:c>
       <x:c r="D153" s="5" t="str">
-        <x:v>Ǿu33diɛ̃14</x:v>
+        <x:v>u die</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -2462,7 +2462,7 @@
         <x:v>蜂糖</x:v>
       </x:c>
       <x:c r="D154" s="5" t="str">
-        <x:v>foŋ33tɑŋ55</x:v>
+        <x:v>fong tang</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -2476,7 +2476,7 @@
         <x:v>虎=蚁</x:v>
       </x:c>
       <x:c r="D155" s="5" t="str">
-        <x:v>xu33Ǿuɑ535</x:v>
+        <x:v>xu ua</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -2490,7 +2490,7 @@
         <x:v>水=面=</x:v>
       </x:c>
       <x:c r="D156" s="5" t="str">
-        <x:v>ɕy55mie14</x:v>
+        <x:v>xy mie</x:v>
       </x:c>
     </x:row>
     <x:row r="157">
@@ -2504,7 +2504,7 @@
         <x:v>蟢</x:v>
       </x:c>
       <x:c r="D157" s="5" t="str">
-        <x:v>ɕi535</x:v>
+        <x:v>xi</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -2518,7 +2518,7 @@
         <x:v>蚊虫</x:v>
       </x:c>
       <x:c r="D158" s="5" t="str">
-        <x:v>miŋ31dʑioŋ14</x:v>
+        <x:v>ming jiong</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -2532,7 +2532,7 @@
         <x:v>虼蚤</x:v>
       </x:c>
       <x:c r="D159" s="5" t="str">
-        <x:v>kəʔ3tsɑo535</x:v>
+        <x:v>ke tsao</x:v>
       </x:c>
     </x:row>
     <x:row r="160">
@@ -2546,7 +2546,7 @@
         <x:v>虱</x:v>
       </x:c>
       <x:c r="D160" s="5" t="str">
-        <x:v>səʔ4</x:v>
+        <x:v>se</x:v>
       </x:c>
     </x:row>
     <x:row r="161">
@@ -2560,7 +2560,7 @@
         <x:v>鳙练=</x:v>
       </x:c>
       <x:c r="D161" s="5" t="str">
-        <x:v>zoŋ31lia14</x:v>
+        <x:v>zong lia</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -2574,7 +2574,7 @@
         <x:v>鳖</x:v>
       </x:c>
       <x:c r="D162" s="5" t="str">
-        <x:v>pie55</x:v>
+        <x:v>pie</x:v>
       </x:c>
     </x:row>
     <x:row r="163">
@@ -2588,7 +2588,7 @@
         <x:v>厣</x:v>
       </x:c>
       <x:c r="D163" s="5" t="str">
-        <x:v>Ǿie535</x:v>
+        <x:v>ie</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -2602,7 +2602,7 @@
         <x:v>虾儿</x:v>
       </x:c>
       <x:c r="D164" s="5" t="str">
-        <x:v>xuɛ̃334</x:v>
+        <x:v>xue</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -2616,7 +2616,7 @@
         <x:v>蟹</x:v>
       </x:c>
       <x:c r="D165" s="5" t="str">
-        <x:v>xɑ535</x:v>
+        <x:v>xa</x:v>
       </x:c>
     </x:row>
     <x:row r="166">
@@ -2630,7 +2630,7 @@
         <x:v>田鸡</x:v>
       </x:c>
       <x:c r="D166" s="5" t="str">
-        <x:v>dia31tɕie55</x:v>
+        <x:v>dia jie</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -2644,7 +2644,7 @@
         <x:v>蛤宝=</x:v>
       </x:c>
       <x:c r="D167" s="5" t="str">
-        <x:v>kəʔ4pɑo535</x:v>
+        <x:v>ke pao</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -2658,7 +2658,7 @@
         <x:v>雄牛</x:v>
       </x:c>
       <x:c r="D168" s="5" t="str">
-        <x:v>Ǿioŋ31ȵiu14</x:v>
+        <x:v>iong niu</x:v>
       </x:c>
     </x:row>
     <x:row r="169">
@@ -2672,7 +2672,7 @@
         <x:v>雌牛</x:v>
       </x:c>
       <x:c r="D169" s="5" t="str">
-        <x:v>tshɿ33ȵiu55</x:v>
+        <x:v>tshi niu</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -2686,7 +2686,7 @@
         <x:v>猪公</x:v>
       </x:c>
       <x:c r="D170" s="5" t="str">
-        <x:v>tɕy33koŋ55</x:v>
+        <x:v>jy kong</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -2700,7 +2700,7 @@
         <x:v>雄猪</x:v>
       </x:c>
       <x:c r="D171" s="5" t="str">
-        <x:v>Ǿioŋ31tɕy55</x:v>
+        <x:v>iong jy</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -2714,7 +2714,7 @@
         <x:v>猪娘</x:v>
       </x:c>
       <x:c r="D172" s="5" t="str">
-        <x:v>tɕy33ȵiɑŋ55</x:v>
+        <x:v>jy niang</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -2728,7 +2728,7 @@
         <x:v>小猪</x:v>
       </x:c>
       <x:c r="D173" s="5" t="str">
-        <x:v>siɑo55tɕy334</x:v>
+        <x:v>siao jy</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -2742,7 +2742,7 @@
         <x:v>猪栏</x:v>
       </x:c>
       <x:c r="D174" s="5" t="str">
-        <x:v>tɕy33lɑ55</x:v>
+        <x:v>jy la</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -2756,7 +2756,7 @@
         <x:v>饲猪</x:v>
       </x:c>
       <x:c r="D175" s="5" t="str">
-        <x:v>zɿ14tɕy334</x:v>
+        <x:v>zi jy</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -2770,7 +2770,7 @@
         <x:v>雄猫</x:v>
       </x:c>
       <x:c r="D176" s="5" t="str">
-        <x:v>Ǿioŋ31mɑo14</x:v>
+        <x:v>iong mao</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -2784,7 +2784,7 @@
         <x:v>雌猫</x:v>
       </x:c>
       <x:c r="D177" s="5" t="str">
-        <x:v>tshɿ33mɑo55</x:v>
+        <x:v>tshi mao</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -2798,7 +2798,7 @@
         <x:v>猫娘</x:v>
       </x:c>
       <x:c r="D178" s="5" t="str">
-        <x:v>mɑo31ȵiɑŋ14</x:v>
+        <x:v>mao niang</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -2812,7 +2812,7 @@
         <x:v>雄狗</x:v>
       </x:c>
       <x:c r="D179" s="5" t="str">
-        <x:v>Ǿioŋ313kiu535</x:v>
+        <x:v>iong kiu</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -2826,7 +2826,7 @@
         <x:v>雌狗</x:v>
       </x:c>
       <x:c r="D180" s="5" t="str">
-        <x:v>tshɿ33kiu535</x:v>
+        <x:v>tshi kiu</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -2840,7 +2840,7 @@
         <x:v>狗娘</x:v>
       </x:c>
       <x:c r="D181" s="5" t="str">
-        <x:v>kiu55ȵiɑŋ313</x:v>
+        <x:v>kiu niang</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -2854,7 +2854,7 @@
         <x:v>兔</x:v>
       </x:c>
       <x:c r="D182" s="5" t="str">
-        <x:v>thu55</x:v>
+        <x:v>thu</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -2868,7 +2868,7 @@
         <x:v>雄鸡</x:v>
       </x:c>
       <x:c r="D183" s="5" t="str">
-        <x:v>Ǿioŋ31tɕie55</x:v>
+        <x:v>iong jie</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -2882,7 +2882,7 @@
         <x:v>草鸡</x:v>
       </x:c>
       <x:c r="D184" s="5" t="str">
-        <x:v>tshɑo55tɕie334</x:v>
+        <x:v>tshao jie</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -2896,7 +2896,7 @@
         <x:v>啼</x:v>
       </x:c>
       <x:c r="D185" s="5" t="str">
-        <x:v>die313</x:v>
+        <x:v>die</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -2910,7 +2910,7 @@
         <x:v>生</x:v>
       </x:c>
       <x:c r="D186" s="5" t="str">
-        <x:v>sɑŋ334</x:v>
+        <x:v>sang</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -2924,7 +2924,7 @@
         <x:v>伏</x:v>
       </x:c>
       <x:c r="D187" s="5" t="str">
-        <x:v>bu14</x:v>
+        <x:v>bu</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -2938,7 +2938,7 @@
         <x:v>羯</x:v>
       </x:c>
       <x:c r="D188" s="5" t="str">
-        <x:v>tɕie55</x:v>
+        <x:v>jie</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -2952,7 +2952,7 @@
         <x:v>羯</x:v>
       </x:c>
       <x:c r="D189" s="5" t="str">
-        <x:v>tɕie55</x:v>
+        <x:v>jie</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -2966,7 +2966,7 @@
         <x:v>鏾</x:v>
       </x:c>
       <x:c r="D190" s="5" t="str">
-        <x:v>ɕie55</x:v>
+        <x:v>xie</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -2980,7 +2980,7 @@
         <x:v>饲</x:v>
       </x:c>
       <x:c r="D191" s="5" t="str">
-        <x:v>zɿ14</x:v>
+        <x:v>zi</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -2994,7 +2994,7 @@
         <x:v>修=</x:v>
       </x:c>
       <x:c r="D192" s="5" t="str">
-        <x:v>ɕiu334</x:v>
+        <x:v>xiu</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -3008,7 +3008,7 @@
         <x:v>人村</x:v>
       </x:c>
       <x:c r="D193" s="5" t="str">
-        <x:v>ȵiŋ31tshəŋ55</x:v>
+        <x:v>ning tsheng</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -3022,7 +3022,7 @@
         <x:v>村</x:v>
       </x:c>
       <x:c r="D194" s="5" t="str">
-        <x:v>tshəŋ334</x:v>
+        <x:v>tsheng</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -3036,7 +3036,7 @@
         <x:v>弄堂</x:v>
       </x:c>
       <x:c r="D195" s="5" t="str">
-        <x:v>loŋ55dɑŋ14</x:v>
+        <x:v>long dang</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -3050,7 +3050,7 @@
         <x:v>街路</x:v>
       </x:c>
       <x:c r="D196" s="5" t="str">
-        <x:v>kɑ33lu55</x:v>
+        <x:v>ka lu</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -3064,7 +3064,7 @@
         <x:v>起屋</x:v>
       </x:c>
       <x:c r="D197" s="5" t="str">
-        <x:v>tɕhi53Ǿoʔ4</x:v>
+        <x:v>qi o</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -3078,7 +3078,7 @@
         <x:v>造屋</x:v>
       </x:c>
       <x:c r="D198" s="5" t="str">
-        <x:v>sɑo53Ǿoʔ4</x:v>
+        <x:v>sao o</x:v>
       </x:c>
     </x:row>
     <x:row r="199">
@@ -3092,7 +3092,7 @@
         <x:v>屋</x:v>
       </x:c>
       <x:c r="D199" s="5" t="str">
-        <x:v>Ǿoʔ4</x:v>
+        <x:v>o</x:v>
       </x:c>
     </x:row>
     <x:row r="200">
@@ -3106,7 +3106,7 @@
         <x:v>房</x:v>
       </x:c>
       <x:c r="D200" s="5" t="str">
-        <x:v>vɑŋ313</x:v>
+        <x:v>vang</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -3120,7 +3120,7 @@
         <x:v>房间</x:v>
       </x:c>
       <x:c r="D201" s="5" t="str">
-        <x:v>vɑŋ31kɑ55</x:v>
+        <x:v>vang ka</x:v>
       </x:c>
     </x:row>
     <x:row r="202">
@@ -3134,7 +3134,7 @@
         <x:v>房间</x:v>
       </x:c>
       <x:c r="D202" s="5" t="str">
-        <x:v>vɑŋ31kɑ55</x:v>
+        <x:v>vang ka</x:v>
       </x:c>
     </x:row>
     <x:row r="203">
@@ -3148,7 +3148,7 @@
         <x:v>茅棚</x:v>
       </x:c>
       <x:c r="D203" s="5" t="str">
-        <x:v>mɑo31boŋ14</x:v>
+        <x:v>mao bong</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -3162,7 +3162,7 @@
         <x:v>镬头</x:v>
       </x:c>
       <x:c r="D204" s="5" t="str">
-        <x:v>Ǿoʔ21diu14</x:v>
+        <x:v>o diu</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
@@ -3176,7 +3176,7 @@
         <x:v>镬灶</x:v>
       </x:c>
       <x:c r="D205" s="5" t="str">
-        <x:v>Ǿoʔ21tsɑo55</x:v>
+        <x:v>o tsao</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -3190,7 +3190,7 @@
         <x:v>镬</x:v>
       </x:c>
       <x:c r="D206" s="5" t="str">
-        <x:v>Ǿoʔ212</x:v>
+        <x:v>o</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -3204,7 +3204,7 @@
         <x:v>镬</x:v>
       </x:c>
       <x:c r="D207" s="5" t="str">
-        <x:v>Ǿoʔ212</x:v>
+        <x:v>o</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -3218,7 +3218,7 @@
         <x:v>镬</x:v>
       </x:c>
       <x:c r="D208" s="5" t="str">
-        <x:v>Ǿoʔ212</x:v>
+        <x:v>o</x:v>
       </x:c>
     </x:row>
     <x:row r="209">
@@ -3232,7 +3232,7 @@
         <x:v>茅坑</x:v>
       </x:c>
       <x:c r="D209" s="5" t="str">
-        <x:v>mɑo31khɑŋ55</x:v>
+        <x:v>mao khang</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -3246,7 +3246,7 @@
         <x:v>桁条</x:v>
       </x:c>
       <x:c r="D210" s="5" t="str">
-        <x:v>Ǿɑŋ31diɑo14</x:v>
+        <x:v>ang diao</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -3260,7 +3260,7 @@
         <x:v>屋柱</x:v>
       </x:c>
       <x:c r="D211" s="5" t="str">
-        <x:v>Ǿoʔ3tɕy535</x:v>
+        <x:v>o jy</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -3274,7 +3274,7 @@
         <x:v>门㦿</x:v>
       </x:c>
       <x:c r="D212" s="5" t="str">
-        <x:v>məŋ31khɑ535</x:v>
+        <x:v>meng kha</x:v>
       </x:c>
     </x:row>
     <x:row r="213">
@@ -3288,7 +3288,7 @@
         <x:v>㦿头</x:v>
       </x:c>
       <x:c r="D213" s="5" t="str">
-        <x:v>khɑ55diu313</x:v>
+        <x:v>kha diu</x:v>
       </x:c>
     </x:row>
     <x:row r="214">
@@ -3302,7 +3302,7 @@
         <x:v>梯儿</x:v>
       </x:c>
       <x:c r="D214" s="5" t="str">
-        <x:v>thɛ̃334</x:v>
+        <x:v>the</x:v>
       </x:c>
     </x:row>
     <x:row r="215">
@@ -3316,7 +3316,7 @@
         <x:v>笤帚</x:v>
       </x:c>
       <x:c r="D215" s="5" t="str">
-        <x:v>tiɑo33tɕiu535</x:v>
+        <x:v>tiao jiu</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -3330,7 +3330,7 @@
         <x:v>#1#2</x:v>
       </x:c>
       <x:c r="D216" s="5" t="str">
-        <x:v>lɤ53sɤ55</x:v>
+        <x:v>le se</x:v>
       </x:c>
     </x:row>
     <x:row r="217">
@@ -3344,7 +3344,7 @@
         <x:v>被</x:v>
       </x:c>
       <x:c r="D217" s="5" t="str">
-        <x:v>pi535</x:v>
+        <x:v>pi</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -3358,7 +3358,7 @@
         <x:v>毯</x:v>
       </x:c>
       <x:c r="D218" s="5" t="str">
-        <x:v>thɑ535</x:v>
+        <x:v>tha</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -3372,7 +3372,7 @@
         <x:v>垫被</x:v>
       </x:c>
       <x:c r="D219" s="5" t="str">
-        <x:v>dia14pi535</x:v>
+        <x:v>dia pi</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -3386,7 +3386,7 @@
         <x:v>草席</x:v>
       </x:c>
       <x:c r="D220" s="5" t="str">
-        <x:v>tshɑo55ʑiəʔ212</x:v>
+        <x:v>tshao rie</x:v>
       </x:c>
     </x:row>
     <x:row r="221">
@@ -3400,7 +3400,7 @@
         <x:v>篾席</x:v>
       </x:c>
       <x:c r="D221" s="5" t="str">
-        <x:v>mie55ʑiəʔ212</x:v>
+        <x:v>mie rie</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -3414,7 +3414,7 @@
         <x:v>布帐</x:v>
       </x:c>
       <x:c r="D222" s="5" t="str">
-        <x:v>pu33tɕiɑŋ55</x:v>
+        <x:v>pu jiang</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
@@ -3428,7 +3428,7 @@
         <x:v>枱桌</x:v>
       </x:c>
       <x:c r="D223" s="5" t="str">
-        <x:v>tɛ33tɕioʔ4</x:v>
+        <x:v>te jio</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -3442,7 +3442,7 @@
         <x:v>柜</x:v>
       </x:c>
       <x:c r="D224" s="5" t="str">
-        <x:v>dʑy14</x:v>
+        <x:v>jy</x:v>
       </x:c>
     </x:row>
     <x:row r="225">
@@ -3456,7 +3456,7 @@
         <x:v>柜</x:v>
       </x:c>
       <x:c r="D225" s="5" t="str">
-        <x:v>ɡui14</x:v>
+        <x:v>gui</x:v>
       </x:c>
     </x:row>
     <x:row r="226">
@@ -3470,7 +3470,7 @@
         <x:v>喉=槽</x:v>
       </x:c>
       <x:c r="D226" s="5" t="str">
-        <x:v>Ǿeu31zɑo14</x:v>
+        <x:v>eu zao</x:v>
       </x:c>
     </x:row>
     <x:row r="227">
@@ -3484,7 +3484,7 @@
         <x:v>杠几</x:v>
       </x:c>
       <x:c r="D227" s="5" t="str">
-        <x:v>kɑŋ53tɕi55</x:v>
+        <x:v>kang ji</x:v>
       </x:c>
     </x:row>
     <x:row r="228">
@@ -3498,7 +3498,7 @@
         <x:v>交椅</x:v>
       </x:c>
       <x:c r="D228" s="5" t="str">
-        <x:v>kɑo33Ǿy535</x:v>
+        <x:v>kao y</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
@@ -3512,7 +3512,7 @@
         <x:v>凳</x:v>
       </x:c>
       <x:c r="D229" s="5" t="str">
-        <x:v>təŋ55</x:v>
+        <x:v>teng</x:v>
       </x:c>
     </x:row>
     <x:row r="230">
@@ -3526,7 +3526,7 @@
         <x:v>薄刀</x:v>
       </x:c>
       <x:c r="D230" s="5" t="str">
-        <x:v>bəʔ21tɑo55</x:v>
+        <x:v>be tao</x:v>
       </x:c>
     </x:row>
     <x:row r="231">
@@ -3540,7 +3540,7 @@
         <x:v>勺</x:v>
       </x:c>
       <x:c r="D231" s="5" t="str">
-        <x:v>zoʔ212</x:v>
+        <x:v>zo</x:v>
       </x:c>
     </x:row>
     <x:row r="232">
@@ -3554,7 +3554,7 @@
         <x:v>掇=瓶</x:v>
       </x:c>
       <x:c r="D232" s="5" t="str">
-        <x:v>tɤ55biŋ0</x:v>
+        <x:v>te bing</x:v>
       </x:c>
     </x:row>
     <x:row r="233">
@@ -3568,7 +3568,7 @@
         <x:v>瓶</x:v>
       </x:c>
       <x:c r="D233" s="5" t="str">
-        <x:v>biŋ313</x:v>
+        <x:v>bing</x:v>
       </x:c>
     </x:row>
     <x:row r="234">
@@ -3582,7 +3582,7 @@
         <x:v>盖</x:v>
       </x:c>
       <x:c r="D234" s="5" t="str">
-        <x:v>kɛ55</x:v>
+        <x:v>ke</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -3596,7 +3596,7 @@
         <x:v>箸</x:v>
       </x:c>
       <x:c r="D235" s="5" t="str">
-        <x:v>dʑy14</x:v>
+        <x:v>jy</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
@@ -3610,7 +3610,7 @@
         <x:v>瓢羹</x:v>
       </x:c>
       <x:c r="D236" s="5" t="str">
-        <x:v>biɑo31kɑŋ55</x:v>
+        <x:v>biao kang</x:v>
       </x:c>
     </x:row>
     <x:row r="237">
@@ -3624,7 +3624,7 @@
         <x:v>柴</x:v>
       </x:c>
       <x:c r="D237" s="5" t="str">
-        <x:v>zɑ313</x:v>
+        <x:v>za</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
@@ -3638,7 +3638,7 @@
         <x:v>洋火</x:v>
       </x:c>
       <x:c r="D238" s="5" t="str">
-        <x:v>Ǿiɑŋ33xuɤ535</x:v>
+        <x:v>iang xue</x:v>
       </x:c>
     </x:row>
     <x:row r="239">
@@ -3652,7 +3652,7 @@
         <x:v>热水瓶</x:v>
       </x:c>
       <x:c r="D239" s="5" t="str">
-        <x:v>ȵiəʔ21ɕy55biŋ313</x:v>
+        <x:v>nie xy bing</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -3666,7 +3666,7 @@
         <x:v>面桶</x:v>
       </x:c>
       <x:c r="D240" s="5" t="str">
-        <x:v>mie33toŋ535</x:v>
+        <x:v>mie tong</x:v>
       </x:c>
     </x:row>
     <x:row r="241">
@@ -3680,7 +3680,7 @@
         <x:v>洗面水</x:v>
       </x:c>
       <x:c r="D241" s="5" t="str">
-        <x:v>ɕie55mie14ɕy535</x:v>
+        <x:v>xie mie xy</x:v>
       </x:c>
     </x:row>
     <x:row r="242">
@@ -3694,7 +3694,7 @@
         <x:v>面布</x:v>
       </x:c>
       <x:c r="D242" s="5" t="str">
-        <x:v>mie31pu55</x:v>
+        <x:v>mie pu</x:v>
       </x:c>
     </x:row>
     <x:row r="243">
@@ -3708,7 +3708,7 @@
         <x:v>手巾</x:v>
       </x:c>
       <x:c r="D243" s="5" t="str">
-        <x:v>ɕiu55tɕiŋ334</x:v>
+        <x:v>xiu jing</x:v>
       </x:c>
     </x:row>
     <x:row r="244">
@@ -3722,7 +3722,7 @@
         <x:v>洋肥皂</x:v>
       </x:c>
       <x:c r="D244" s="5" t="str">
-        <x:v>Ǿiɑŋ33fi33sɑo535</x:v>
+        <x:v>iang fi sao</x:v>
       </x:c>
     </x:row>
     <x:row r="245">
@@ -3736,7 +3736,7 @@
         <x:v>掠儿</x:v>
       </x:c>
       <x:c r="D245" s="5" t="str">
-        <x:v>liɛ̃14</x:v>
+        <x:v>lie</x:v>
       </x:c>
     </x:row>
     <x:row r="246">
@@ -3750,7 +3750,7 @@
         <x:v>针</x:v>
       </x:c>
       <x:c r="D246" s="5" t="str">
-        <x:v>tɕiŋ334</x:v>
+        <x:v>jing</x:v>
       </x:c>
     </x:row>
     <x:row r="247">
@@ -3764,7 +3764,7 @@
         <x:v>剪刀</x:v>
       </x:c>
       <x:c r="D247" s="5" t="str">
-        <x:v>tsia55tɑo334</x:v>
+        <x:v>tsia tao</x:v>
       </x:c>
     </x:row>
     <x:row r="248">
@@ -3778,7 +3778,7 @@
         <x:v>电筒</x:v>
       </x:c>
       <x:c r="D248" s="5" t="str">
-        <x:v>tia55doŋ14</x:v>
+        <x:v>tia dong</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
@@ -3792,7 +3792,7 @@
         <x:v>洋伞</x:v>
       </x:c>
       <x:c r="D249" s="5" t="str">
-        <x:v>Ǿiɑŋ33sɑ535</x:v>
+        <x:v>iang sa</x:v>
       </x:c>
     </x:row>
     <x:row r="250">
@@ -3806,7 +3806,7 @@
         <x:v>脚踏车</x:v>
       </x:c>
       <x:c r="D250" s="5" t="str">
-        <x:v>tɕiəʔ4duɑ14tshia0</x:v>
+        <x:v>jie dua tshia</x:v>
       </x:c>
     </x:row>
     <x:row r="251">
@@ -3820,7 +3820,7 @@
         <x:v>衣裳</x:v>
       </x:c>
       <x:c r="D251" s="5" t="str">
-        <x:v>Ǿi33ɕiɑŋ55</x:v>
+        <x:v>i xiang</x:v>
       </x:c>
     </x:row>
     <x:row r="252">
@@ -3834,7 +3834,7 @@
         <x:v>着</x:v>
       </x:c>
       <x:c r="D252" s="5" t="str">
-        <x:v>tɕiəʔ4</x:v>
+        <x:v>jie</x:v>
       </x:c>
     </x:row>
     <x:row r="253">
@@ -3848,7 +3848,7 @@
         <x:v>缚</x:v>
       </x:c>
       <x:c r="D253" s="5" t="str">
-        <x:v>boʔ212</x:v>
+        <x:v>bo</x:v>
       </x:c>
     </x:row>
     <x:row r="254">
@@ -3862,7 +3862,7 @@
         <x:v>小布衫儿</x:v>
       </x:c>
       <x:c r="D254" s="5" t="str">
-        <x:v>siɑo55pu33sɛ̃334</x:v>
+        <x:v>siao pu se</x:v>
       </x:c>
     </x:row>
     <x:row r="255">
@@ -3876,7 +3876,7 @@
         <x:v>毛线衣</x:v>
       </x:c>
       <x:c r="D255" s="5" t="str">
-        <x:v>mɑo33ɕie33Ǿi55</x:v>
+        <x:v>mao xie i</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -3890,7 +3890,7 @@
         <x:v>棉袄</x:v>
       </x:c>
       <x:c r="D256" s="5" t="str">
-        <x:v>mie33Ǿɑo535</x:v>
+        <x:v>mie ao</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
@@ -3904,7 +3904,7 @@
         <x:v>衫袖</x:v>
       </x:c>
       <x:c r="D257" s="5" t="str">
-        <x:v>sɑ33ɕiu55</x:v>
+        <x:v>sa xiu</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -3918,7 +3918,7 @@
         <x:v>袋</x:v>
       </x:c>
       <x:c r="D258" s="5" t="str">
-        <x:v>dɛ14</x:v>
+        <x:v>de</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -3932,7 +3932,7 @@
         <x:v>裤</x:v>
       </x:c>
       <x:c r="D259" s="5" t="str">
-        <x:v>khu55</x:v>
+        <x:v>khu</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -3946,7 +3946,7 @@
         <x:v>裤脚</x:v>
       </x:c>
       <x:c r="D260" s="5" t="str">
-        <x:v>khu33tɕiəʔ4</x:v>
+        <x:v>khu jie</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
@@ -3960,7 +3960,7 @@
         <x:v>帽</x:v>
       </x:c>
       <x:c r="D261" s="5" t="str">
-        <x:v>mɑo14</x:v>
+        <x:v>mao</x:v>
       </x:c>
     </x:row>
     <x:row r="262">
@@ -3974,7 +3974,7 @@
         <x:v>鞋</x:v>
       </x:c>
       <x:c r="D262" s="5" t="str">
-        <x:v>Ǿɑ313</x:v>
+        <x:v>a</x:v>
       </x:c>
     </x:row>
     <x:row r="263">
@@ -3988,7 +3988,7 @@
         <x:v>袜</x:v>
       </x:c>
       <x:c r="D263" s="5" t="str">
-        <x:v>mɤa14</x:v>
+        <x:v>mea</x:v>
       </x:c>
     </x:row>
     <x:row r="264">
@@ -4002,7 +4002,7 @@
         <x:v>尿片</x:v>
       </x:c>
       <x:c r="D264" s="5" t="str">
-        <x:v>sɛ33phie55</x:v>
+        <x:v>se phie</x:v>
       </x:c>
     </x:row>
     <x:row r="265">
@@ -4016,7 +4016,7 @@
         <x:v>纽子</x:v>
       </x:c>
       <x:c r="D265" s="5" t="str">
-        <x:v>ȵiu53tsɿ55</x:v>
+        <x:v>niu tsi</x:v>
       </x:c>
     </x:row>
     <x:row r="266">
@@ -4030,7 +4030,7 @@
         <x:v>纽</x:v>
       </x:c>
       <x:c r="D266" s="5" t="str">
-        <x:v>ȵiu535</x:v>
+        <x:v>niu</x:v>
       </x:c>
     </x:row>
     <x:row r="267">
@@ -4044,7 +4044,7 @@
         <x:v>剃头</x:v>
       </x:c>
       <x:c r="D267" s="5" t="str">
-        <x:v>thie33diu313</x:v>
+        <x:v>thie diu</x:v>
       </x:c>
     </x:row>
     <x:row r="268">
@@ -4058,7 +4058,7 @@
         <x:v>钻＝头</x:v>
       </x:c>
       <x:c r="D268" s="5" t="str">
-        <x:v>tsɤ55diu313</x:v>
+        <x:v>tse diu</x:v>
       </x:c>
     </x:row>
     <x:row r="269">
@@ -4072,7 +4072,7 @@
         <x:v>饭</x:v>
       </x:c>
       <x:c r="D269" s="5" t="str">
-        <x:v>vɑ14</x:v>
+        <x:v>va</x:v>
       </x:c>
     </x:row>
     <x:row r="270">
@@ -4086,7 +4086,7 @@
         <x:v>粥</x:v>
       </x:c>
       <x:c r="D270" s="5" t="str">
-        <x:v>tɕioʔ4</x:v>
+        <x:v>jio</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
@@ -4100,7 +4100,7 @@
         <x:v>麦粉</x:v>
       </x:c>
       <x:c r="D271" s="5" t="str">
-        <x:v>məʔ21fəŋ535</x:v>
+        <x:v>me feng</x:v>
       </x:c>
     </x:row>
     <x:row r="272">
@@ -4114,7 +4114,7 @@
         <x:v>面</x:v>
       </x:c>
       <x:c r="D272" s="5" t="str">
-        <x:v>mie14</x:v>
+        <x:v>mie</x:v>
       </x:c>
     </x:row>
     <x:row r="273">
@@ -4128,7 +4128,7 @@
         <x:v>粉</x:v>
       </x:c>
       <x:c r="D273" s="5" t="str">
-        <x:v>fəŋ535</x:v>
+        <x:v>feng</x:v>
       </x:c>
     </x:row>
     <x:row r="274">
@@ -4142,7 +4142,7 @@
         <x:v>水饺</x:v>
       </x:c>
       <x:c r="D274" s="5" t="str">
-        <x:v>ɕy53tɕiɑo535</x:v>
+        <x:v>xy jiao</x:v>
       </x:c>
     </x:row>
     <x:row r="275">
@@ -4156,7 +4156,7 @@
         <x:v>馅</x:v>
       </x:c>
       <x:c r="D275" s="5" t="str">
-        <x:v>Ǿɑ535</x:v>
+        <x:v>a</x:v>
       </x:c>
     </x:row>
     <x:row r="276">
@@ -4170,7 +4170,7 @@
         <x:v>油杂=馃</x:v>
       </x:c>
       <x:c r="D276" s="5" t="str">
-        <x:v>Ǿiu31dzəʔ21kuɤ535</x:v>
+        <x:v>iu dze kue</x:v>
       </x:c>
     </x:row>
     <x:row r="277">
@@ -4184,7 +4184,7 @@
         <x:v>浆</x:v>
       </x:c>
       <x:c r="D277" s="5" t="str">
-        <x:v>tsiɑŋ334</x:v>
+        <x:v>tsiang</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -4198,7 +4198,7 @@
         <x:v>豆腐汤</x:v>
       </x:c>
       <x:c r="D278" s="5" t="str">
-        <x:v>tiu33fu53thɑŋ55</x:v>
+        <x:v>tiu fu thang</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -4212,7 +4212,7 @@
         <x:v>汤团</x:v>
       </x:c>
       <x:c r="D279" s="5" t="str">
-        <x:v>thɑŋ33tɤ55</x:v>
+        <x:v>thang te</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -4226,7 +4226,7 @@
         <x:v>粽</x:v>
       </x:c>
       <x:c r="D280" s="5" t="str">
-        <x:v>tsoŋ55</x:v>
+        <x:v>tsong</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -4240,7 +4240,7 @@
         <x:v>糕饼</x:v>
       </x:c>
       <x:c r="D281" s="5" t="str">
-        <x:v>kɑo33piŋ535</x:v>
+        <x:v>kao ping</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -4254,7 +4254,7 @@
         <x:v>糕点</x:v>
       </x:c>
       <x:c r="D282" s="5" t="str">
-        <x:v>kɑo33tiɛ̃535</x:v>
+        <x:v>kao tie</x:v>
       </x:c>
     </x:row>
     <x:row r="283">
@@ -4268,7 +4268,7 @@
         <x:v>猪脚爪</x:v>
       </x:c>
       <x:c r="D283" s="5" t="str">
-        <x:v>tɕy33tɕiəʔ3tsɑo535</x:v>
+        <x:v>jy jie tsao</x:v>
       </x:c>
     </x:row>
     <x:row r="284">
@@ -4282,7 +4282,7 @@
         <x:v>猪口舌</x:v>
       </x:c>
       <x:c r="D284" s="5" t="str">
-        <x:v>tɕy33khiu55dʑyɤ14</x:v>
+        <x:v>jy khiu jye</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -4296,7 +4296,7 @@
         <x:v>肚里货</x:v>
       </x:c>
       <x:c r="D285" s="5" t="str">
-        <x:v>tu33li53xuɤ55</x:v>
+        <x:v>tu li xue</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
@@ -4310,7 +4310,7 @@
         <x:v>鸡卵</x:v>
       </x:c>
       <x:c r="D286" s="5" t="str">
-        <x:v>tɕie33ləŋ535</x:v>
+        <x:v>jie leng</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -4324,7 +4324,7 @@
         <x:v>皮蛋</x:v>
       </x:c>
       <x:c r="D287" s="5" t="str">
-        <x:v>bi31dɛ̃14</x:v>
+        <x:v>bi de</x:v>
       </x:c>
     </x:row>
     <x:row r="288">
@@ -4338,7 +4338,7 @@
         <x:v>脂油</x:v>
       </x:c>
       <x:c r="D288" s="5" t="str">
-        <x:v>tsɿ33Ǿiu55</x:v>
+        <x:v>tsi iu</x:v>
       </x:c>
     </x:row>
     <x:row r="289">
@@ -4352,7 +4352,7 @@
         <x:v>麻油</x:v>
       </x:c>
       <x:c r="D289" s="5" t="str">
-        <x:v>mɤa31Ǿiu14</x:v>
+        <x:v>mea iu</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -4366,7 +4366,7 @@
         <x:v>烟丝</x:v>
       </x:c>
       <x:c r="D290" s="5" t="str">
-        <x:v>Ǿia33sɿ55</x:v>
+        <x:v>ia si</x:v>
       </x:c>
     </x:row>
     <x:row r="291">
@@ -4380,7 +4380,7 @@
         <x:v>土烟</x:v>
       </x:c>
       <x:c r="D291" s="5" t="str">
-        <x:v>thu55Ǿia334</x:v>
+        <x:v>thu ia</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
@@ -4394,7 +4394,7 @@
         <x:v>烧酒</x:v>
       </x:c>
       <x:c r="D292" s="5" t="str">
-        <x:v>ɕiɑo33tɕiu535</x:v>
+        <x:v>xiao jiu</x:v>
       </x:c>
     </x:row>
     <x:row r="293">
@@ -4408,7 +4408,7 @@
         <x:v>甜酒娘</x:v>
       </x:c>
       <x:c r="D293" s="5" t="str">
-        <x:v>tia33tɕiu55ȵiɑŋ313</x:v>
+        <x:v>tia jiu niang</x:v>
       </x:c>
     </x:row>
     <x:row r="294">
@@ -4422,7 +4422,7 @@
         <x:v>泡</x:v>
       </x:c>
       <x:c r="D294" s="5" t="str">
-        <x:v>phɑo55</x:v>
+        <x:v>phao</x:v>
       </x:c>
     </x:row>
     <x:row r="295">
@@ -4436,7 +4436,7 @@
         <x:v>棒冰</x:v>
       </x:c>
       <x:c r="D295" s="5" t="str">
-        <x:v>bɑŋ14piŋ0</x:v>
+        <x:v>bang ping</x:v>
       </x:c>
     </x:row>
     <x:row r="296">
@@ -4450,7 +4450,7 @@
         <x:v>烧饭</x:v>
       </x:c>
       <x:c r="D296" s="5" t="str">
-        <x:v>ɕiɑo33vɑ14</x:v>
+        <x:v>xiao va</x:v>
       </x:c>
     </x:row>
     <x:row r="297">
@@ -4464,7 +4464,7 @@
         <x:v>煠</x:v>
       </x:c>
       <x:c r="D297" s="5" t="str">
-        <x:v>zuɑ14</x:v>
+        <x:v>zua</x:v>
       </x:c>
     </x:row>
     <x:row r="298">
@@ -4478,7 +4478,7 @@
         <x:v>放</x:v>
       </x:c>
       <x:c r="D298" s="5" t="str">
-        <x:v>fɑŋ55</x:v>
+        <x:v>fang</x:v>
       </x:c>
     </x:row>
     <x:row r="299">
@@ -4492,7 +4492,7 @@
         <x:v>肉=</x:v>
       </x:c>
       <x:c r="D299" s="5" t="str">
-        <x:v>ȵioʔ212</x:v>
+        <x:v>nio</x:v>
       </x:c>
     </x:row>
     <x:row r="300">
@@ -4506,7 +4506,7 @@
         <x:v>𨀤</x:v>
       </x:c>
       <x:c r="D300" s="5" t="str">
-        <x:v>lɛ14</x:v>
+        <x:v>le</x:v>
       </x:c>
     </x:row>
     <x:row r="301">
@@ -4520,7 +4520,7 @@
         <x:v>吃五更儿饭</x:v>
       </x:c>
       <x:c r="D301" s="5" t="str">
-        <x:v>tɕhiəʔ4Ǿŋ55kɛ̃33fɑ55</x:v>
+        <x:v>qie ng ke fa</x:v>
       </x:c>
     </x:row>
     <x:row r="302">
@@ -4534,7 +4534,7 @@
         <x:v>吃夜饭</x:v>
       </x:c>
       <x:c r="D302" s="5" t="str">
-        <x:v>tɕhiəʔ4Ǿia55vɑ14</x:v>
+        <x:v>qie ia va</x:v>
       </x:c>
     </x:row>
     <x:row r="303">
@@ -4548,7 +4548,7 @@
         <x:v>吃</x:v>
       </x:c>
       <x:c r="D303" s="5" t="str">
-        <x:v>tɕhiəʔ4</x:v>
+        <x:v>qie</x:v>
       </x:c>
     </x:row>
     <x:row r="304">
@@ -4562,7 +4562,7 @@
         <x:v>吃</x:v>
       </x:c>
       <x:c r="D304" s="5" t="str">
-        <x:v>tɕhiəʔ4</x:v>
+        <x:v>qie</x:v>
       </x:c>
     </x:row>
     <x:row r="305">
@@ -4576,7 +4576,7 @@
         <x:v>吃</x:v>
       </x:c>
       <x:c r="D305" s="5" t="str">
-        <x:v>tɕhiəʔ4</x:v>
+        <x:v>qie</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
@@ -4590,7 +4590,7 @@
         <x:v>𣥼</x:v>
       </x:c>
       <x:c r="D306" s="5" t="str">
-        <x:v>tɕy55</x:v>
+        <x:v>jy</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
@@ -4604,7 +4604,7 @@
         <x:v>挟</x:v>
       </x:c>
       <x:c r="D307" s="5" t="str">
-        <x:v>tsia55</x:v>
+        <x:v>tsia</x:v>
       </x:c>
     </x:row>
     <x:row r="308">
@@ -4618,7 +4618,7 @@
         <x:v>倒</x:v>
       </x:c>
       <x:c r="D308" s="5" t="str">
-        <x:v>tɑo535</x:v>
+        <x:v>tao</x:v>
       </x:c>
     </x:row>
     <x:row r="309">
@@ -4632,7 +4632,7 @@
         <x:v>筛</x:v>
       </x:c>
       <x:c r="D309" s="5" t="str">
-        <x:v>sɑ334</x:v>
+        <x:v>sa</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
@@ -4646,7 +4646,7 @@
         <x:v>口燥</x:v>
       </x:c>
       <x:c r="D310" s="5" t="str">
-        <x:v>khiu53sɑo55</x:v>
+        <x:v>khiu sao</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
@@ -4660,7 +4660,7 @@
         <x:v>肚饥</x:v>
       </x:c>
       <x:c r="D311" s="5" t="str">
-        <x:v>tu55tɕi334</x:v>
+        <x:v>tu ji</x:v>
       </x:c>
     </x:row>
     <x:row r="312">
@@ -4674,7 +4674,7 @@
         <x:v>肚皮饿</x:v>
       </x:c>
       <x:c r="D312" s="5" t="str">
-        <x:v>tu55bi31Ǿuɤ14</x:v>
+        <x:v>tu bi ue</x:v>
       </x:c>
     </x:row>
     <x:row r="313">
@@ -4688,7 +4688,7 @@
         <x:v>哽</x:v>
       </x:c>
       <x:c r="D313" s="5" t="str">
-        <x:v>kɑŋ55</x:v>
+        <x:v>kang</x:v>
       </x:c>
     </x:row>
     <x:row r="314">
@@ -4702,7 +4702,7 @@
         <x:v>辫儿</x:v>
       </x:c>
       <x:c r="D314" s="5" t="str">
-        <x:v>biɛ̃14</x:v>
+        <x:v>bie</x:v>
       </x:c>
     </x:row>
     <x:row r="315">
@@ -4716,7 +4716,7 @@
         <x:v>头旋</x:v>
       </x:c>
       <x:c r="D315" s="5" t="str">
-        <x:v>diu31ʑie14</x:v>
+        <x:v>diu rie</x:v>
       </x:c>
     </x:row>
     <x:row r="316">
@@ -4730,7 +4730,7 @@
         <x:v>额骨头</x:v>
       </x:c>
       <x:c r="D316" s="5" t="str">
-        <x:v>Ǿəʔ21kuəʔ3tiu55</x:v>
+        <x:v>e kue tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="317">
@@ -4744,7 +4744,7 @@
         <x:v>样子</x:v>
       </x:c>
       <x:c r="D317" s="5" t="str">
-        <x:v>Ǿiɑŋ53tsɿ535</x:v>
+        <x:v>iang tsi</x:v>
       </x:c>
     </x:row>
     <x:row r="318">
@@ -4758,7 +4758,7 @@
         <x:v>面</x:v>
       </x:c>
       <x:c r="D318" s="5" t="str">
-        <x:v>mie14</x:v>
+        <x:v>mie</x:v>
       </x:c>
     </x:row>
     <x:row r="319">
@@ -4772,7 +4772,7 @@
         <x:v>眼睛乌珠</x:v>
       </x:c>
       <x:c r="D319" s="5" t="str">
-        <x:v>Ǿɑ55tɕiŋ33Ǿu33tɕy55</x:v>
+        <x:v>a jing u jy</x:v>
       </x:c>
     </x:row>
     <x:row r="320">
@@ -4786,7 +4786,7 @@
         <x:v>鼻头</x:v>
       </x:c>
       <x:c r="D320" s="5" t="str">
-        <x:v>biəʔ21diu14</x:v>
+        <x:v>bie diu</x:v>
       </x:c>
     </x:row>
     <x:row r="321">
@@ -4800,7 +4800,7 @@
         <x:v>口葡=</x:v>
       </x:c>
       <x:c r="D321" s="5" t="str">
-        <x:v>khiu55bu313</x:v>
+        <x:v>khiu bu</x:v>
       </x:c>
     </x:row>
     <x:row r="322">
@@ -4814,7 +4814,7 @@
         <x:v>口唇肉皮</x:v>
       </x:c>
       <x:c r="D322" s="5" t="str">
-        <x:v>khiu55ɕiŋ33ȵioʔ21bi14</x:v>
+        <x:v>khiu xing nio bi</x:v>
       </x:c>
     </x:row>
     <x:row r="323">
@@ -4828,7 +4828,7 @@
         <x:v>口唾水</x:v>
       </x:c>
       <x:c r="D323" s="5" t="str">
-        <x:v>khiu55thuɤ33ɕy535</x:v>
+        <x:v>khiu thue xy</x:v>
       </x:c>
     </x:row>
     <x:row r="324">
@@ -4842,7 +4842,7 @@
         <x:v>口吐水</x:v>
       </x:c>
       <x:c r="D324" s="5" t="str">
-        <x:v>khiu55thu33ɕy535</x:v>
+        <x:v>khiu thu xy</x:v>
       </x:c>
     </x:row>
     <x:row r="325">
@@ -4856,7 +4856,7 @@
         <x:v>口舌</x:v>
       </x:c>
       <x:c r="D325" s="5" t="str">
-        <x:v>khiu55dʑyɤ14</x:v>
+        <x:v>khiu jye</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
@@ -4870,7 +4870,7 @@
         <x:v>胡须</x:v>
       </x:c>
       <x:c r="D326" s="5" t="str">
-        <x:v>Ǿu31su55</x:v>
+        <x:v>u su</x:v>
       </x:c>
     </x:row>
     <x:row r="327">
@@ -4884,7 +4884,7 @@
         <x:v>项颈</x:v>
       </x:c>
       <x:c r="D327" s="5" t="str">
-        <x:v>Ǿɑŋ53tɕiŋ535</x:v>
+        <x:v>ang jing</x:v>
       </x:c>
     </x:row>
     <x:row r="328">
@@ -4898,7 +4898,7 @@
         <x:v>肩头</x:v>
       </x:c>
       <x:c r="D328" s="5" t="str">
-        <x:v>tɕie33tiu55</x:v>
+        <x:v>jie tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="329">
@@ -4912,7 +4912,7 @@
         <x:v>手臂</x:v>
       </x:c>
       <x:c r="D329" s="5" t="str">
-        <x:v>ɕiu53pi55</x:v>
+        <x:v>xiu pi</x:v>
       </x:c>
     </x:row>
     <x:row r="330">
@@ -4926,7 +4926,7 @@
         <x:v>借手</x:v>
       </x:c>
       <x:c r="D330" s="5" t="str">
-        <x:v>tsia33ɕiu535</x:v>
+        <x:v>tsia xiu</x:v>
       </x:c>
     </x:row>
     <x:row r="331">
@@ -4940,7 +4940,7 @@
         <x:v>顺手</x:v>
       </x:c>
       <x:c r="D331" s="5" t="str">
-        <x:v>ʑyəŋ14ɕiu535</x:v>
+        <x:v>ryeng xiu</x:v>
       </x:c>
     </x:row>
     <x:row r="332">
@@ -4954,7 +4954,7 @@
         <x:v>正手</x:v>
       </x:c>
       <x:c r="D332" s="5" t="str">
-        <x:v>tɕiŋ55ɕiu535</x:v>
+        <x:v>jing xiu</x:v>
       </x:c>
     </x:row>
     <x:row r="333">
@@ -4968,7 +4968,7 @@
         <x:v>大拳</x:v>
       </x:c>
       <x:c r="D333" s="5" t="str">
-        <x:v>tuɤ55dʑyɤ14</x:v>
+        <x:v>tue jye</x:v>
       </x:c>
     </x:row>
     <x:row r="334">
@@ -4982,7 +4982,7 @@
         <x:v>手拇急=头</x:v>
       </x:c>
       <x:c r="D334" s="5" t="str">
-        <x:v>ɕiu55mɛ33tɕiəʔ3tiu55</x:v>
+        <x:v>xiu me jie tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="335">
@@ -4996,7 +4996,7 @@
         <x:v>大手拇急=头</x:v>
       </x:c>
       <x:c r="D335" s="5" t="str">
-        <x:v>duɤ14ɕiu55mɛ33tɕiəʔ3tiu55</x:v>
+        <x:v>due xiu me jie tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="336">
@@ -5010,7 +5010,7 @@
         <x:v>小手拇急=头</x:v>
       </x:c>
       <x:c r="D336" s="5" t="str">
-        <x:v>siɑo53ɕiu55mɛ33tɕiəʔ3tiu55</x:v>
+        <x:v>siao xiu me jie tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="337">
@@ -5024,7 +5024,7 @@
         <x:v>手指甲</x:v>
       </x:c>
       <x:c r="D337" s="5" t="str">
-        <x:v>ɕiu55tsɿ33kuɑ55</x:v>
+        <x:v>xiu tsi kua</x:v>
       </x:c>
     </x:row>
     <x:row r="338">
@@ -5038,7 +5038,7 @@
         <x:v>脚膝髁</x:v>
       </x:c>
       <x:c r="D338" s="5" t="str">
-        <x:v>tɕiəʔ4tɕhiəʔ3khuɤ55</x:v>
+        <x:v>jie qie khue</x:v>
       </x:c>
     </x:row>
     <x:row r="339">
@@ -5052,7 +5052,7 @@
         <x:v>背脊</x:v>
       </x:c>
       <x:c r="D339" s="5" t="str">
-        <x:v>pɛ33tɕiəʔ5</x:v>
+        <x:v>pe jie</x:v>
       </x:c>
     </x:row>
     <x:row r="340">
@@ -5066,7 +5066,7 @@
         <x:v>肚皮</x:v>
       </x:c>
       <x:c r="D340" s="5" t="str">
-        <x:v>tu55bi313</x:v>
+        <x:v>tu bi</x:v>
       </x:c>
     </x:row>
     <x:row r="341">
@@ -5080,7 +5080,7 @@
         <x:v>肚脐洞</x:v>
       </x:c>
       <x:c r="D341" s="5" t="str">
-        <x:v>tu55ʑie31doŋ14</x:v>
+        <x:v>tu rie dong</x:v>
       </x:c>
     </x:row>
     <x:row r="342">
@@ -5094,7 +5094,7 @@
         <x:v>奶奶</x:v>
       </x:c>
       <x:c r="D342" s="5" t="str">
-        <x:v>nɛ33nɛ55</x:v>
+        <x:v>ne ne</x:v>
       </x:c>
     </x:row>
     <x:row r="343">
@@ -5108,7 +5108,7 @@
         <x:v>屁股洞</x:v>
       </x:c>
       <x:c r="D343" s="5" t="str">
-        <x:v>phi33ku55doŋ14</x:v>
+        <x:v>phi ku dong</x:v>
       </x:c>
     </x:row>
     <x:row r="344">
@@ -5122,7 +5122,7 @@
         <x:v>老八</x:v>
       </x:c>
       <x:c r="D344" s="5" t="str">
-        <x:v>lɑo53pɤa55</x:v>
+        <x:v>lao pea</x:v>
       </x:c>
     </x:row>
     <x:row r="345">
@@ -5136,7 +5136,7 @@
         <x:v>雀</x:v>
       </x:c>
       <x:c r="D345" s="5" t="str">
-        <x:v>tɕiəʔ4</x:v>
+        <x:v>jie</x:v>
       </x:c>
     </x:row>
     <x:row r="346">
@@ -5150,7 +5150,7 @@
         <x:v>老屄</x:v>
       </x:c>
       <x:c r="D346" s="5" t="str">
-        <x:v>lɑo55pi334</x:v>
+        <x:v>lao pi</x:v>
       </x:c>
     </x:row>
     <x:row r="347">
@@ -5164,7 +5164,7 @@
         <x:v>䏘</x:v>
       </x:c>
       <x:c r="D347" s="5" t="str">
-        <x:v>phiəʔ4</x:v>
+        <x:v>phie</x:v>
       </x:c>
     </x:row>
     <x:row r="348">
@@ -5178,7 +5178,7 @@
         <x:v>入</x:v>
       </x:c>
       <x:c r="D348" s="5" t="str">
-        <x:v>ʑiəʔ212</x:v>
+        <x:v>rie</x:v>
       </x:c>
     </x:row>
     <x:row r="349">
@@ -5192,7 +5192,7 @@
         <x:v>弄</x:v>
       </x:c>
       <x:c r="D349" s="5" t="str">
-        <x:v>loŋ14</x:v>
+        <x:v>long</x:v>
       </x:c>
     </x:row>
     <x:row r="350">
@@ -5206,7 +5206,7 @@
         <x:v>㞞</x:v>
       </x:c>
       <x:c r="D350" s="5" t="str">
-        <x:v>zoŋ313</x:v>
+        <x:v>zong</x:v>
       </x:c>
     </x:row>
     <x:row r="351">
@@ -5220,7 +5220,7 @@
         <x:v>身上来</x:v>
       </x:c>
       <x:c r="D351" s="5" t="str">
-        <x:v>ɕiŋ33ɕiɑŋ55lɛ313</x:v>
+        <x:v>xing xiang le</x:v>
       </x:c>
     </x:row>
     <x:row r="352">
@@ -5234,7 +5234,7 @@
         <x:v>射涴</x:v>
       </x:c>
       <x:c r="D352" s="5" t="str">
-        <x:v>dzia14Ǿuɤ55</x:v>
+        <x:v>dzia ue</x:v>
       </x:c>
     </x:row>
     <x:row r="353">
@@ -5248,7 +5248,7 @@
         <x:v>射尿</x:v>
       </x:c>
       <x:c r="D353" s="5" t="str">
-        <x:v>dzia14sɛ334</x:v>
+        <x:v>dzia se</x:v>
       </x:c>
     </x:row>
     <x:row r="354">
@@ -5262,7 +5262,7 @@
         <x:v>娘卖屄</x:v>
       </x:c>
       <x:c r="D354" s="5" t="str">
-        <x:v>ȵiɑŋ33mɑ55pi334</x:v>
+        <x:v>niang ma pi</x:v>
       </x:c>
     </x:row>
     <x:row r="355">
@@ -5276,7 +5276,7 @@
         <x:v>生病了</x:v>
       </x:c>
       <x:c r="D355" s="5" t="str">
-        <x:v>sɑŋ33biŋ14ləʔ0</x:v>
+        <x:v>sang bing le</x:v>
       </x:c>
     </x:row>
     <x:row r="356">
@@ -5290,7 +5290,7 @@
         <x:v>生毛病了</x:v>
       </x:c>
       <x:c r="D356" s="5" t="str">
-        <x:v>sɑŋ33mɑo31biŋ14ləʔ0</x:v>
+        <x:v>sang mao bing le</x:v>
       </x:c>
     </x:row>
     <x:row r="357">
@@ -5304,7 +5304,7 @@
         <x:v>冻去</x:v>
       </x:c>
       <x:c r="D357" s="5" t="str">
-        <x:v>toŋ55khɤ0</x:v>
+        <x:v>tong khe</x:v>
       </x:c>
     </x:row>
     <x:row r="358">
@@ -5318,7 +5318,7 @@
         <x:v>受凉</x:v>
       </x:c>
       <x:c r="D358" s="5" t="str">
-        <x:v>ɕiu55liɑŋ313</x:v>
+        <x:v>xiu liang</x:v>
       </x:c>
     </x:row>
     <x:row r="359">
@@ -5332,7 +5332,7 @@
         <x:v>烧热</x:v>
       </x:c>
       <x:c r="D359" s="5" t="str">
-        <x:v>ɕiɑo33ȵie14</x:v>
+        <x:v>xiao nie</x:v>
       </x:c>
     </x:row>
     <x:row r="360">
@@ -5346,7 +5346,7 @@
         <x:v>咯咯抖</x:v>
       </x:c>
       <x:c r="D360" s="5" t="str">
-        <x:v>ɡəʔ21ɡəʔ21tiu535</x:v>
+        <x:v>ge ge tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="361">
@@ -5360,7 +5360,7 @@
         <x:v>肚皮痛</x:v>
       </x:c>
       <x:c r="D361" s="5" t="str">
-        <x:v>tu55bi31thoŋ55</x:v>
+        <x:v>tu bi thong</x:v>
       </x:c>
     </x:row>
     <x:row r="362">
@@ -5374,7 +5374,7 @@
         <x:v>肚射</x:v>
       </x:c>
       <x:c r="D362" s="5" t="str">
-        <x:v>tu55dzia14</x:v>
+        <x:v>tu dzia</x:v>
       </x:c>
     </x:row>
     <x:row r="363">
@@ -5388,7 +5388,7 @@
         <x:v>肚皮射</x:v>
       </x:c>
       <x:c r="D363" s="5" t="str">
-        <x:v>tu55bi31dzia14</x:v>
+        <x:v>tu bi dzia</x:v>
       </x:c>
     </x:row>
     <x:row r="364">
@@ -5402,7 +5402,7 @@
         <x:v>打半日</x:v>
       </x:c>
       <x:c r="D364" s="5" t="str">
-        <x:v>tɑŋ55pɤ33ȵiəʔ212</x:v>
+        <x:v>tang pe nie</x:v>
       </x:c>
     </x:row>
     <x:row r="365">
@@ -5416,7 +5416,7 @@
         <x:v>痧气</x:v>
       </x:c>
       <x:c r="D365" s="5" t="str">
-        <x:v>suɑ33tɕhi55</x:v>
+        <x:v>sua qi</x:v>
       </x:c>
     </x:row>
     <x:row r="366">
@@ -5430,7 +5430,7 @@
         <x:v>灌</x:v>
       </x:c>
       <x:c r="D366" s="5" t="str">
-        <x:v>koŋ55</x:v>
+        <x:v>kong</x:v>
       </x:c>
     </x:row>
     <x:row r="367">
@@ -5444,7 +5444,7 @@
         <x:v>鼻=</x:v>
       </x:c>
       <x:c r="D367" s="5" t="str">
-        <x:v>biəʔ212</x:v>
+        <x:v>bie</x:v>
       </x:c>
     </x:row>
     <x:row r="368">
@@ -5458,7 +5458,7 @@
         <x:v>望先生</x:v>
       </x:c>
       <x:c r="D368" s="5" t="str">
-        <x:v>moŋ33ɕie33sɑŋ55</x:v>
+        <x:v>mong xie sang</x:v>
       </x:c>
     </x:row>
     <x:row r="369">
@@ -5472,7 +5472,7 @@
         <x:v>望病</x:v>
       </x:c>
       <x:c r="D369" s="5" t="str">
-        <x:v>moŋ55biŋ14</x:v>
+        <x:v>mong bing</x:v>
       </x:c>
     </x:row>
     <x:row r="370">
@@ -5486,7 +5486,7 @@
         <x:v>望医师</x:v>
       </x:c>
       <x:c r="D370" s="5" t="str">
-        <x:v>moŋ14Ǿi33sɿ55</x:v>
+        <x:v>mong i si</x:v>
       </x:c>
     </x:row>
     <x:row r="371">
@@ -5500,7 +5500,7 @@
         <x:v>把脉</x:v>
       </x:c>
       <x:c r="D371" s="5" t="str">
-        <x:v>pɤa55məʔ212</x:v>
+        <x:v>pea me</x:v>
       </x:c>
     </x:row>
     <x:row r="372">
@@ -5514,7 +5514,7 @@
         <x:v>挂葡萄糖</x:v>
       </x:c>
       <x:c r="D372" s="5" t="str">
-        <x:v>kuɑ55pu33dɑo31dɑŋ14</x:v>
+        <x:v>kua pu dao dang</x:v>
       </x:c>
     </x:row>
     <x:row r="373">
@@ -5528,7 +5528,7 @@
         <x:v>吊瓶</x:v>
       </x:c>
       <x:c r="D373" s="5" t="str">
-        <x:v>tiɑo33biŋ313</x:v>
+        <x:v>tiao bing</x:v>
       </x:c>
     </x:row>
     <x:row r="374">
@@ -5542,7 +5542,7 @@
         <x:v>水药</x:v>
       </x:c>
       <x:c r="D374" s="5" t="str">
-        <x:v>ɕy55Ǿiəʔ212</x:v>
+        <x:v>xy ie</x:v>
       </x:c>
     </x:row>
     <x:row r="375">
@@ -5556,7 +5556,7 @@
         <x:v>中药</x:v>
       </x:c>
       <x:c r="D375" s="5" t="str">
-        <x:v>tɕioŋ33Ǿiəʔ212</x:v>
+        <x:v>jiong ie</x:v>
       </x:c>
     </x:row>
     <x:row r="376">
@@ -5570,7 +5570,7 @@
         <x:v>病好帝=儿了</x:v>
       </x:c>
       <x:c r="D376" s="5" t="str">
-        <x:v>biŋ14xɑo53tiŋ55ləʔ0</x:v>
+        <x:v>bing xao ting le</x:v>
       </x:c>
     </x:row>
     <x:row r="377">
@@ -5584,7 +5584,7 @@
         <x:v>做媒</x:v>
       </x:c>
       <x:c r="D377" s="5" t="str">
-        <x:v>ʦuɤ33mɛ313</x:v>
+        <x:v>tsue me</x:v>
       </x:c>
     </x:row>
     <x:row r="378">
@@ -5598,7 +5598,7 @@
         <x:v>望人家</x:v>
       </x:c>
       <x:c r="D378" s="5" t="str">
-        <x:v>moŋ55ȵiŋ31kuɑ55</x:v>
+        <x:v>mong ning kua</x:v>
       </x:c>
     </x:row>
     <x:row r="379">
@@ -5612,7 +5612,7 @@
         <x:v>定婚</x:v>
       </x:c>
       <x:c r="D379" s="5" t="str">
-        <x:v>tiŋ55xuəŋ334</x:v>
+        <x:v>ting xueng</x:v>
       </x:c>
     </x:row>
     <x:row r="380">
@@ -5626,7 +5626,7 @@
         <x:v>陪嫁</x:v>
       </x:c>
       <x:c r="D380" s="5" t="str">
-        <x:v>bɛ31kuɑ55</x:v>
+        <x:v>be kua</x:v>
       </x:c>
     </x:row>
     <x:row r="381">
@@ -5640,7 +5640,7 @@
         <x:v>讨老婆</x:v>
       </x:c>
       <x:c r="D381" s="5" t="str">
-        <x:v>thɑo53lɑo55bɤ313</x:v>
+        <x:v>thao lao be</x:v>
       </x:c>
     </x:row>
     <x:row r="382">
@@ -5654,7 +5654,7 @@
         <x:v>嫁人</x:v>
       </x:c>
       <x:c r="D382" s="5" t="str">
-        <x:v>kuɑ33ȵiŋ313</x:v>
+        <x:v>kua ning</x:v>
       </x:c>
     </x:row>
     <x:row r="383">
@@ -5668,7 +5668,7 @@
         <x:v>新郎官</x:v>
       </x:c>
       <x:c r="D383" s="5" t="str">
-        <x:v>ɕiŋ33lɑŋ31kuɑ55</x:v>
+        <x:v>xing lang kua</x:v>
       </x:c>
     </x:row>
     <x:row r="384">
@@ -5682,7 +5682,7 @@
         <x:v>新孺人</x:v>
       </x:c>
       <x:c r="D384" s="5" t="str">
-        <x:v>ɕiŋ33ɕy55ȵiŋ313</x:v>
+        <x:v>xing xy ning</x:v>
       </x:c>
     </x:row>
     <x:row r="385">
@@ -5696,7 +5696,7 @@
         <x:v>大肚皮</x:v>
       </x:c>
       <x:c r="D385" s="5" t="str">
-        <x:v>tuɤ55tu55bi313</x:v>
+        <x:v>tue tu bi</x:v>
       </x:c>
     </x:row>
     <x:row r="386">
@@ -5710,7 +5710,7 @@
         <x:v>病皇=男</x:v>
       </x:c>
       <x:c r="D386" s="5" t="str">
-        <x:v>piŋ55Ǿuɑŋ31lɤ14</x:v>
+        <x:v>ping uang le</x:v>
       </x:c>
     </x:row>
     <x:row r="387">
@@ -5724,7 +5724,7 @@
         <x:v>大肚皮</x:v>
       </x:c>
       <x:c r="D387" s="5" t="str">
-        <x:v>tuɤ55tu55bi313</x:v>
+        <x:v>tue tu bi</x:v>
       </x:c>
     </x:row>
     <x:row r="388">
@@ -5738,7 +5738,7 @@
         <x:v>病皇=男</x:v>
       </x:c>
       <x:c r="D388" s="5" t="str">
-        <x:v>piŋ55Ǿuɑŋ31lɤ14</x:v>
+        <x:v>ping uang le</x:v>
       </x:c>
     </x:row>
     <x:row r="389">
@@ -5752,7 +5752,7 @@
         <x:v>生皇=男</x:v>
       </x:c>
       <x:c r="D389" s="5" t="str">
-        <x:v>sɑŋǾuɑŋ31lɤ14</x:v>
+        <x:v>sanguang le</x:v>
       </x:c>
     </x:row>
     <x:row r="390">
@@ -5766,7 +5766,7 @@
         <x:v>生小人</x:v>
       </x:c>
       <x:c r="D390" s="5" t="str">
-        <x:v>soŋ33siɑo55ȵiŋ313</x:v>
+        <x:v>song siao ning</x:v>
       </x:c>
     </x:row>
     <x:row r="391">
@@ -5780,7 +5780,7 @@
         <x:v>脱落去</x:v>
       </x:c>
       <x:c r="D391" s="5" t="str">
-        <x:v>thəʔ4loʔ0khɤ0</x:v>
+        <x:v>the lo khe</x:v>
       </x:c>
     </x:row>
     <x:row r="392">
@@ -5794,7 +5794,7 @@
         <x:v>小产</x:v>
       </x:c>
       <x:c r="D392" s="5" t="str">
-        <x:v>siɑo55tshɛ̃535</x:v>
+        <x:v>siao tshe</x:v>
       </x:c>
     </x:row>
     <x:row r="393">
@@ -5808,7 +5808,7 @@
         <x:v>双生儿</x:v>
       </x:c>
       <x:c r="D393" s="5" t="str">
-        <x:v>ɕyɑŋ33sɛ̃334</x:v>
+        <x:v>xyang se</x:v>
       </x:c>
     </x:row>
     <x:row r="394">
@@ -5822,7 +5822,7 @@
         <x:v>做产母</x:v>
       </x:c>
       <x:c r="D394" s="5" t="str">
-        <x:v>tsuɤ33suɑ33Ǿm535</x:v>
+        <x:v>tsue sua m</x:v>
       </x:c>
     </x:row>
     <x:row r="395">
@@ -5836,7 +5836,7 @@
         <x:v>吃奶奶</x:v>
       </x:c>
       <x:c r="D395" s="5" t="str">
-        <x:v>tɕhiəʔ4nɛ33nɛ55</x:v>
+        <x:v>qie ne ne</x:v>
       </x:c>
     </x:row>
     <x:row r="396">
@@ -5850,7 +5850,7 @@
         <x:v>摘奶奶</x:v>
       </x:c>
       <x:c r="D396" s="5" t="str">
-        <x:v>tsəʔ4nɛ33nɛ55</x:v>
+        <x:v>tse ne ne</x:v>
       </x:c>
     </x:row>
     <x:row r="397">
@@ -5864,7 +5864,7 @@
         <x:v>过辈</x:v>
       </x:c>
       <x:c r="D397" s="5" t="str">
-        <x:v>kuɤ33pɛ55</x:v>
+        <x:v>kue pe</x:v>
       </x:c>
     </x:row>
     <x:row r="398">
@@ -5878,7 +5878,7 @@
         <x:v>过世</x:v>
       </x:c>
       <x:c r="D398" s="5" t="str">
-        <x:v>kuɤ33ɕyɤ55</x:v>
+        <x:v>kue xye</x:v>
       </x:c>
     </x:row>
     <x:row r="399">
@@ -5892,7 +5892,7 @@
         <x:v>寻死</x:v>
       </x:c>
       <x:c r="D399" s="5" t="str">
-        <x:v>səŋ33sɿ535</x:v>
+        <x:v>seng si</x:v>
       </x:c>
     </x:row>
     <x:row r="400">
@@ -5906,7 +5906,7 @@
         <x:v>脱气</x:v>
       </x:c>
       <x:c r="D400" s="5" t="str">
-        <x:v>thəʔ3tɕhi55</x:v>
+        <x:v>the qi</x:v>
       </x:c>
     </x:row>
     <x:row r="401">
@@ -5920,7 +5920,7 @@
         <x:v>断气</x:v>
       </x:c>
       <x:c r="D401" s="5" t="str">
-        <x:v>tɤ53tɕhi55</x:v>
+        <x:v>te qi</x:v>
       </x:c>
     </x:row>
     <x:row r="402">
@@ -5934,7 +5934,7 @@
         <x:v>落材</x:v>
       </x:c>
       <x:c r="D402" s="5" t="str">
-        <x:v>loʔ21zɛ313</x:v>
+        <x:v>lo ze</x:v>
       </x:c>
     </x:row>
     <x:row r="403">
@@ -5948,7 +5948,7 @@
         <x:v>寿材</x:v>
       </x:c>
       <x:c r="D403" s="5" t="str">
-        <x:v>ɕiu55zɛ313</x:v>
+        <x:v>xiu ze</x:v>
       </x:c>
     </x:row>
     <x:row r="404">
@@ -5962,7 +5962,7 @@
         <x:v>上山</x:v>
       </x:c>
       <x:c r="D404" s="5" t="str">
-        <x:v>ɕiɑŋ55sɑ334</x:v>
+        <x:v>xiang sa</x:v>
       </x:c>
     </x:row>
     <x:row r="405">
@@ -5976,7 +5976,7 @@
         <x:v>神主牌</x:v>
       </x:c>
       <x:c r="D405" s="5" t="str">
-        <x:v>ɕiŋ33tɕy55bɑ313</x:v>
+        <x:v>xing jy ba</x:v>
       </x:c>
     </x:row>
     <x:row r="406">
@@ -5990,7 +5990,7 @@
         <x:v>坟头</x:v>
       </x:c>
       <x:c r="D406" s="5" t="str">
-        <x:v>vəŋ31diu14</x:v>
+        <x:v>veng diu</x:v>
       </x:c>
     </x:row>
     <x:row r="407">
@@ -6004,7 +6004,7 @@
         <x:v>纸铜钿</x:v>
       </x:c>
       <x:c r="D407" s="5" t="str">
-        <x:v>tsɿ55doŋ31die14</x:v>
+        <x:v>tsi dong die</x:v>
       </x:c>
     </x:row>
     <x:row r="408">
@@ -6018,7 +6018,7 @@
         <x:v>天老爷</x:v>
       </x:c>
       <x:c r="D408" s="5" t="str">
-        <x:v>thia33lɑo55Ǿia0</x:v>
+        <x:v>thia lao ia</x:v>
       </x:c>
     </x:row>
     <x:row r="409">
@@ -6032,7 +6032,7 @@
         <x:v>观音菩萨</x:v>
       </x:c>
       <x:c r="D409" s="5" t="str">
-        <x:v>kuɑ33Ǿiŋ55bu31səʔ5</x:v>
+        <x:v>kua ing bu se</x:v>
       </x:c>
     </x:row>
     <x:row r="410">
@@ -6046,7 +6046,7 @@
         <x:v>镬灶老爷</x:v>
       </x:c>
       <x:c r="D410" s="5" t="str">
-        <x:v>Ǿʔ21tsɑo55lɑo55Ǿia14</x:v>
+        <x:v>tsao lao ia</x:v>
       </x:c>
     </x:row>
     <x:row r="411">
@@ -6060,7 +6060,7 @@
         <x:v>佛殿</x:v>
       </x:c>
       <x:c r="D411" s="5" t="str">
-        <x:v>vəʔ21dia14</x:v>
+        <x:v>ve dia</x:v>
       </x:c>
     </x:row>
     <x:row r="412">
@@ -6074,7 +6074,7 @@
         <x:v>寺</x:v>
       </x:c>
       <x:c r="D412" s="5" t="str">
-        <x:v>zɿ14</x:v>
+        <x:v>zi</x:v>
       </x:c>
     </x:row>
     <x:row r="413">
@@ -6088,7 +6088,7 @@
         <x:v>男子人</x:v>
       </x:c>
       <x:c r="D413" s="5" t="str">
-        <x:v>nɤ33tsɿ55ȵiŋ313</x:v>
+        <x:v>ne tsi ning</x:v>
       </x:c>
     </x:row>
     <x:row r="414">
@@ -6102,7 +6102,7 @@
         <x:v>男个人</x:v>
       </x:c>
       <x:c r="D414" s="5" t="str">
-        <x:v>nɤ31kəʔ0ȵiŋ313</x:v>
+        <x:v>ne ke ning</x:v>
       </x:c>
     </x:row>
     <x:row r="415">
@@ -6116,7 +6116,7 @@
         <x:v>内堂</x:v>
       </x:c>
       <x:c r="D415" s="5" t="str">
-        <x:v>nɛ55dɑŋ14</x:v>
+        <x:v>ne dang</x:v>
       </x:c>
     </x:row>
     <x:row r="416">
@@ -6130,7 +6130,7 @@
         <x:v>秃铁梗儿</x:v>
       </x:c>
       <x:c r="D416" s="5" t="str">
-        <x:v>thoʔ3thia53kuɛ̃55</x:v>
+        <x:v>tho thia kue</x:v>
       </x:c>
     </x:row>
     <x:row r="417">
@@ -6144,7 +6144,7 @@
         <x:v>秃铁</x:v>
       </x:c>
       <x:c r="D417" s="5" t="str">
-        <x:v>thoʔ3thia55</x:v>
+        <x:v>tho thia</x:v>
       </x:c>
     </x:row>
     <x:row r="418">
@@ -6158,7 +6158,7 @@
         <x:v>光棍</x:v>
       </x:c>
       <x:c r="D418" s="5" t="str">
-        <x:v>kuɑŋ33kuəŋ535</x:v>
+        <x:v>kuang kueng</x:v>
       </x:c>
     </x:row>
     <x:row r="419">
@@ -6172,7 +6172,7 @@
         <x:v>皇=男</x:v>
       </x:c>
       <x:c r="D419" s="5" t="str">
-        <x:v>Ǿuɑŋ31nɤ14</x:v>
+        <x:v>uang ne</x:v>
       </x:c>
     </x:row>
     <x:row r="420">
@@ -6186,7 +6186,7 @@
         <x:v>毛毛头</x:v>
       </x:c>
       <x:c r="D420" s="5" t="str">
-        <x:v>mɑo33mɑotiu55</x:v>
+        <x:v>mao maotiu</x:v>
       </x:c>
     </x:row>
     <x:row r="421">
@@ -6200,7 +6200,7 @@
         <x:v>小个人</x:v>
       </x:c>
       <x:c r="D421" s="5" t="str">
-        <x:v>siɑo55kəʔ0ȵiŋ313</x:v>
+        <x:v>siao ke ning</x:v>
       </x:c>
     </x:row>
     <x:row r="422">
@@ -6214,7 +6214,7 @@
         <x:v>小鬼王</x:v>
       </x:c>
       <x:c r="D422" s="5" t="str">
-        <x:v>siɑo55tɕy55Ǿuɑŋ313</x:v>
+        <x:v>siao jy uang</x:v>
       </x:c>
     </x:row>
     <x:row r="423">
@@ -6228,7 +6228,7 @@
         <x:v>鬼王头</x:v>
       </x:c>
       <x:c r="D423" s="5" t="str">
-        <x:v>tɕy55Ǿuɑŋ31diu14</x:v>
+        <x:v>jy uang diu</x:v>
       </x:c>
     </x:row>
     <x:row r="424">
@@ -6242,7 +6242,7 @@
         <x:v>麻头鬼</x:v>
       </x:c>
       <x:c r="D424" s="5" t="str">
-        <x:v>mɤa33tiu55tɕy535</x:v>
+        <x:v>mea tiu jy</x:v>
       </x:c>
     </x:row>
     <x:row r="425">
@@ -6256,7 +6256,7 @@
         <x:v>小囡妮</x:v>
       </x:c>
       <x:c r="D425" s="5" t="str">
-        <x:v>siɑo55nɑ55ȵi14</x:v>
+        <x:v>siao na ni</x:v>
       </x:c>
     </x:row>
     <x:row r="426">
@@ -6270,7 +6270,7 @@
         <x:v>老个人</x:v>
       </x:c>
       <x:c r="D426" s="5" t="str">
-        <x:v>lɑo535kəʔ0ȵiŋ313</x:v>
+        <x:v>lao ke ning</x:v>
       </x:c>
     </x:row>
     <x:row r="427">
@@ -6284,7 +6284,7 @@
         <x:v>隔壁邻居</x:v>
       </x:c>
       <x:c r="D427" s="5" t="str">
-        <x:v>kəʔ4piəʔ4liŋ31sia55</x:v>
+        <x:v>ke pie ling sia</x:v>
       </x:c>
     </x:row>
     <x:row r="428">
@@ -6298,7 +6298,7 @@
         <x:v>种田地个</x:v>
       </x:c>
       <x:c r="D428" s="5" t="str">
-        <x:v>tɕioŋ33dia31di14kəʔ0</x:v>
+        <x:v>jiong dia di ke</x:v>
       </x:c>
     </x:row>
     <x:row r="429">
@@ -6312,7 +6312,7 @@
         <x:v>做生意个</x:v>
       </x:c>
       <x:c r="D429" s="5" t="str">
-        <x:v>tsuɤ33sɑŋ33Ǿi55kəʔ0</x:v>
+        <x:v>tsue sang i ke</x:v>
       </x:c>
     </x:row>
     <x:row r="430">
@@ -6326,7 +6326,7 @@
         <x:v>做手艺个</x:v>
       </x:c>
       <x:c r="D430" s="5" t="str">
-        <x:v>tsuɤ33ɕiu55ȵi14kəʔ0</x:v>
+        <x:v>tsue xiu ni ke</x:v>
       </x:c>
     </x:row>
     <x:row r="431">
@@ -6340,7 +6340,7 @@
         <x:v>泥水老师</x:v>
       </x:c>
       <x:c r="D431" s="5" t="str">
-        <x:v>ȵie33ɕy55lɑo55sɿ334</x:v>
+        <x:v>nie xy lao si</x:v>
       </x:c>
     </x:row>
     <x:row r="432">
@@ -6354,7 +6354,7 @@
         <x:v>做泥水个</x:v>
       </x:c>
       <x:c r="D432" s="5" t="str">
-        <x:v>tsuɤ33ȵie33ɕy55ɡəʔ0</x:v>
+        <x:v>tsue nie xy ge</x:v>
       </x:c>
     </x:row>
     <x:row r="433">
@@ -6368,7 +6368,7 @@
         <x:v>做木个</x:v>
       </x:c>
       <x:c r="D433" s="5" t="str">
-        <x:v>tsuɤ33moʔ21ɡəʔ0</x:v>
+        <x:v>tsue mo ge</x:v>
       </x:c>
     </x:row>
     <x:row r="434">
@@ -6382,7 +6382,7 @@
         <x:v>裁缝老师</x:v>
       </x:c>
       <x:c r="D434" s="5" t="str">
-        <x:v>sɛ33foŋ33lɑo55sɿ334</x:v>
+        <x:v>se fong lao si</x:v>
       </x:c>
     </x:row>
     <x:row r="435">
@@ -6396,7 +6396,7 @@
         <x:v>做裁缝个</x:v>
       </x:c>
       <x:c r="D435" s="5" t="str">
-        <x:v>tsuɤ33zɛ31voŋ14kəʔ0</x:v>
+        <x:v>tsue ze vong ke</x:v>
       </x:c>
     </x:row>
     <x:row r="436">
@@ -6410,7 +6410,7 @@
         <x:v>剃头老师</x:v>
       </x:c>
       <x:c r="D436" s="5" t="str">
-        <x:v>thie33tiu33lɑo55sɿ334</x:v>
+        <x:v>thie tiu lao si</x:v>
       </x:c>
     </x:row>
     <x:row r="437">
@@ -6424,7 +6424,7 @@
         <x:v>剃头个</x:v>
       </x:c>
       <x:c r="D437" s="5" t="str">
-        <x:v>thie33diu31ɡəʔ0</x:v>
+        <x:v>thie diu ge</x:v>
       </x:c>
     </x:row>
     <x:row r="438">
@@ -6438,7 +6438,7 @@
         <x:v>厨倌老师</x:v>
       </x:c>
       <x:c r="D438" s="5" t="str">
-        <x:v>tɕy33kuɑ33lɑo55sɿ334</x:v>
+        <x:v>jy kua lao si</x:v>
       </x:c>
     </x:row>
     <x:row r="439">
@@ -6452,7 +6452,7 @@
         <x:v>厨倌</x:v>
       </x:c>
       <x:c r="D439" s="5" t="str">
-        <x:v>dʑy31kuɑ55</x:v>
+        <x:v>jy kua</x:v>
       </x:c>
     </x:row>
     <x:row r="440">
@@ -6466,7 +6466,7 @@
         <x:v>师父</x:v>
       </x:c>
       <x:c r="D440" s="5" t="str">
-        <x:v>sɿ33fu535</x:v>
+        <x:v>si fu</x:v>
       </x:c>
     </x:row>
     <x:row r="441">
@@ -6480,7 +6480,7 @@
         <x:v>讨饭</x:v>
       </x:c>
       <x:c r="D441" s="5" t="str">
-        <x:v>thɑo55vɑ14</x:v>
+        <x:v>thao va</x:v>
       </x:c>
     </x:row>
     <x:row r="442">
@@ -6494,7 +6494,7 @@
         <x:v>讨饭个</x:v>
       </x:c>
       <x:c r="D442" s="5" t="str">
-        <x:v>thɑo55vɑ14kəʔ0</x:v>
+        <x:v>thao va ke</x:v>
       </x:c>
     </x:row>
     <x:row r="443">
@@ -6508,7 +6508,7 @@
         <x:v>婊子</x:v>
       </x:c>
       <x:c r="D443" s="5" t="str">
-        <x:v>piɑo53tsɿ535</x:v>
+        <x:v>piao tsi</x:v>
       </x:c>
     </x:row>
     <x:row r="444">
@@ -6522,7 +6522,7 @@
         <x:v>贼骨头</x:v>
       </x:c>
       <x:c r="D444" s="5" t="str">
-        <x:v>zəʔ21kuəʔ3tiu55</x:v>
+        <x:v>ze kue tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="445">
@@ -6536,7 +6536,7 @@
         <x:v>做贼</x:v>
       </x:c>
       <x:c r="D445" s="5" t="str">
-        <x:v>tsuɤ33zəʔ212</x:v>
+        <x:v>tsue ze</x:v>
       </x:c>
     </x:row>
     <x:row r="446">
@@ -6550,7 +6550,7 @@
         <x:v>做贼个</x:v>
       </x:c>
       <x:c r="D446" s="5" t="str">
-        <x:v>tsuɤ33zəʔ21ɡəʔ0</x:v>
+        <x:v>tsue ze ge</x:v>
       </x:c>
     </x:row>
     <x:row r="447">
@@ -6564,7 +6564,7 @@
         <x:v>眼睛瞎儿</x:v>
       </x:c>
       <x:c r="D447" s="5" t="str">
-        <x:v>Ǿɑ55tɕiŋ33xuɛ̃55</x:v>
+        <x:v>a jing xue</x:v>
       </x:c>
     </x:row>
     <x:row r="448">
@@ -6578,7 +6578,7 @@
         <x:v>耳朵聋</x:v>
       </x:c>
       <x:c r="D448" s="5" t="str">
-        <x:v>Ǿŋ53tuɤ55loŋ313</x:v>
+        <x:v>ng tue long</x:v>
       </x:c>
     </x:row>
     <x:row r="449">
@@ -6592,7 +6592,7 @@
         <x:v>老鸭</x:v>
       </x:c>
       <x:c r="D449" s="5" t="str">
-        <x:v>lɑo53Ǿuɑ55</x:v>
+        <x:v>lao ua</x:v>
       </x:c>
     </x:row>
     <x:row r="450">
@@ -6606,7 +6606,7 @@
         <x:v>驼背</x:v>
       </x:c>
       <x:c r="D450" s="5" t="str">
-        <x:v>duɤ31pɛ55</x:v>
+        <x:v>due pe</x:v>
       </x:c>
     </x:row>
     <x:row r="451">
@@ -6620,7 +6620,7 @@
         <x:v>跷脚</x:v>
       </x:c>
       <x:c r="D451" s="5" t="str">
-        <x:v>tɕhiɑo33tɕiəʔ4</x:v>
+        <x:v>qiao jie</x:v>
       </x:c>
     </x:row>
     <x:row r="452">
@@ -6634,7 +6634,7 @@
         <x:v>癫个人</x:v>
       </x:c>
       <x:c r="D452" s="5" t="str">
-        <x:v>tia33kəʔ0ȵiŋ313</x:v>
+        <x:v>tia ke ning</x:v>
       </x:c>
     </x:row>
     <x:row r="453">
@@ -6648,7 +6648,7 @@
         <x:v>倒=傻货</x:v>
       </x:c>
       <x:c r="D453" s="5" t="str">
-        <x:v>tɑo55sɑ33xuɤ55</x:v>
+        <x:v>tao sa xue</x:v>
       </x:c>
     </x:row>
     <x:row r="454">
@@ -6662,7 +6662,7 @@
         <x:v>倒=傻个</x:v>
       </x:c>
       <x:c r="D454" s="5" t="str">
-        <x:v>tɑo55sɑ33kəʔ0</x:v>
+        <x:v>tao sa ke</x:v>
       </x:c>
     </x:row>
     <x:row r="455">
@@ -6676,7 +6676,7 @@
         <x:v>木大</x:v>
       </x:c>
       <x:c r="D455" s="5" t="str">
-        <x:v>moʔ21duɤ14</x:v>
+        <x:v>mo due</x:v>
       </x:c>
     </x:row>
     <x:row r="456">
@@ -6690,7 +6690,7 @@
         <x:v>呆大</x:v>
       </x:c>
       <x:c r="D456" s="5" t="str">
-        <x:v>Ǿɛ31duɤ14</x:v>
+        <x:v>e due</x:v>
       </x:c>
     </x:row>
     <x:row r="457">
@@ -6704,7 +6704,7 @@
         <x:v>妈妈</x:v>
       </x:c>
       <x:c r="D457" s="5" t="str">
-        <x:v>mɑ33mɑ55</x:v>
+        <x:v>ma ma</x:v>
       </x:c>
     </x:row>
     <x:row r="458">
@@ -6718,7 +6718,7 @@
         <x:v>外公</x:v>
       </x:c>
       <x:c r="D458" s="5" t="str">
-        <x:v>Ǿɑ53koŋ55</x:v>
+        <x:v>a kong</x:v>
       </x:c>
     </x:row>
     <x:row r="459">
@@ -6732,7 +6732,7 @@
         <x:v>外婆</x:v>
       </x:c>
       <x:c r="D459" s="5" t="str">
-        <x:v>Ǿɑ55bɤ14</x:v>
+        <x:v>a be</x:v>
       </x:c>
     </x:row>
     <x:row r="460">
@@ -6746,7 +6746,7 @@
         <x:v>爷娘</x:v>
       </x:c>
       <x:c r="D460" s="5" t="str">
-        <x:v>Ǿia31ȵiɑŋ14</x:v>
+        <x:v>ia niang</x:v>
       </x:c>
     </x:row>
     <x:row r="461">
@@ -6760,7 +6760,7 @@
         <x:v>爷</x:v>
       </x:c>
       <x:c r="D461" s="5" t="str">
-        <x:v>Ǿia313</x:v>
+        <x:v>ia</x:v>
       </x:c>
     </x:row>
     <x:row r="462">
@@ -6774,7 +6774,7 @@
         <x:v>老爷</x:v>
       </x:c>
       <x:c r="D462" s="5" t="str">
-        <x:v>lɑo55Ǿia313</x:v>
+        <x:v>lao ia</x:v>
       </x:c>
     </x:row>
     <x:row r="463">
@@ -6788,7 +6788,7 @@
         <x:v>娘</x:v>
       </x:c>
       <x:c r="D463" s="5" t="str">
-        <x:v>ȵiɑŋ313</x:v>
+        <x:v>niang</x:v>
       </x:c>
     </x:row>
     <x:row r="464">
@@ -6802,7 +6802,7 @@
         <x:v>老娘</x:v>
       </x:c>
       <x:c r="D464" s="5" t="str">
-        <x:v>lɑo55ȵiɑŋ313</x:v>
+        <x:v>lao niang</x:v>
       </x:c>
     </x:row>
     <x:row r="465">
@@ -6816,7 +6816,7 @@
         <x:v>伯伯</x:v>
       </x:c>
       <x:c r="D465" s="5" t="str">
-        <x:v>pəʔ3pəʔ4</x:v>
+        <x:v>pe pe</x:v>
       </x:c>
     </x:row>
     <x:row r="466">
@@ -6830,7 +6830,7 @@
         <x:v>姆𡝠</x:v>
       </x:c>
       <x:c r="D466" s="5" t="str">
-        <x:v>Ǿm55mɛ0</x:v>
+        <x:v>m me</x:v>
       </x:c>
     </x:row>
     <x:row r="467">
@@ -6844,7 +6844,7 @@
         <x:v>𡝠</x:v>
       </x:c>
       <x:c r="D467" s="5" t="str">
-        <x:v>mɛ55</x:v>
+        <x:v>me</x:v>
       </x:c>
     </x:row>
     <x:row r="468">
@@ -6858,7 +6858,7 @@
         <x:v>亲爷</x:v>
       </x:c>
       <x:c r="D468" s="5" t="str">
-        <x:v>tɕhiŋ33Ǿia55</x:v>
+        <x:v>qing ia</x:v>
       </x:c>
     </x:row>
     <x:row r="469">
@@ -6872,7 +6872,7 @@
         <x:v>晚爷</x:v>
       </x:c>
       <x:c r="D469" s="5" t="str">
-        <x:v>mɑ55Ǿia313</x:v>
+        <x:v>ma ia</x:v>
       </x:c>
     </x:row>
     <x:row r="470">
@@ -6886,7 +6886,7 @@
         <x:v>晚娘</x:v>
       </x:c>
       <x:c r="D470" s="5" t="str">
-        <x:v>mɑ55ȵiɑŋ313</x:v>
+        <x:v>ma niang</x:v>
       </x:c>
     </x:row>
     <x:row r="471">
@@ -6900,7 +6900,7 @@
         <x:v>丈人</x:v>
       </x:c>
       <x:c r="D471" s="5" t="str">
-        <x:v>tɕiɑŋ55ȵiŋ313</x:v>
+        <x:v>jiang ning</x:v>
       </x:c>
     </x:row>
     <x:row r="472">
@@ -6914,7 +6914,7 @@
         <x:v>丈母</x:v>
       </x:c>
       <x:c r="D472" s="5" t="str">
-        <x:v>tɕiɑŋ33Ǿm535</x:v>
+        <x:v>jiang m</x:v>
       </x:c>
     </x:row>
     <x:row r="473">
@@ -6928,7 +6928,7 @@
         <x:v>丈母娘</x:v>
       </x:c>
       <x:c r="D473" s="5" t="str">
-        <x:v>tɕiɑŋ33Ǿm55ȵiɑŋ313</x:v>
+        <x:v>jiang m niang</x:v>
       </x:c>
     </x:row>
     <x:row r="474">
@@ -6942,7 +6942,7 @@
         <x:v>公</x:v>
       </x:c>
       <x:c r="D474" s="5" t="str">
-        <x:v>koŋ334</x:v>
+        <x:v>kong</x:v>
       </x:c>
     </x:row>
     <x:row r="475">
@@ -6956,7 +6956,7 @@
         <x:v>婆</x:v>
       </x:c>
       <x:c r="D475" s="5" t="str">
-        <x:v>bɤ313</x:v>
+        <x:v>be</x:v>
       </x:c>
     </x:row>
     <x:row r="476">
@@ -6970,7 +6970,7 @@
         <x:v>大伯</x:v>
       </x:c>
       <x:c r="D476" s="5" t="str">
-        <x:v>tuɤ53pəʔ4</x:v>
+        <x:v>tue pe</x:v>
       </x:c>
     </x:row>
     <x:row r="477">
@@ -6984,7 +6984,7 @@
         <x:v>大伯</x:v>
       </x:c>
       <x:c r="D477" s="5" t="str">
-        <x:v>dɑ14pəʔ0</x:v>
+        <x:v>da pe</x:v>
       </x:c>
     </x:row>
     <x:row r="478">
@@ -6998,7 +6998,7 @@
         <x:v>大姆𡝠</x:v>
       </x:c>
       <x:c r="D478" s="5" t="str">
-        <x:v>duɤ14Ǿm55mɛ0</x:v>
+        <x:v>due m me</x:v>
       </x:c>
     </x:row>
     <x:row r="479">
@@ -7012,7 +7012,7 @@
         <x:v>大妈</x:v>
       </x:c>
       <x:c r="D479" s="5" t="str">
-        <x:v>dɑ14mɑ0</x:v>
+        <x:v>da ma</x:v>
       </x:c>
     </x:row>
     <x:row r="480">
@@ -7026,7 +7026,7 @@
         <x:v>叔儿</x:v>
       </x:c>
       <x:c r="D480" s="5" t="str">
-        <x:v>ɕioŋ55</x:v>
+        <x:v>xiong</x:v>
       </x:c>
     </x:row>
     <x:row r="481">
@@ -7040,7 +7040,7 @@
         <x:v>叔叔</x:v>
       </x:c>
       <x:c r="D481" s="5" t="str">
-        <x:v>ɕyəʔ3ɕyəʔ4</x:v>
+        <x:v>xye xye</x:v>
       </x:c>
     </x:row>
     <x:row r="482">
@@ -7054,7 +7054,7 @@
         <x:v>小叔儿</x:v>
       </x:c>
       <x:c r="D482" s="5" t="str">
-        <x:v>siɑo53ɕioŋ55</x:v>
+        <x:v>siao xiong</x:v>
       </x:c>
     </x:row>
     <x:row r="483">
@@ -7068,7 +7068,7 @@
         <x:v>小叔叔</x:v>
       </x:c>
       <x:c r="D483" s="5" t="str">
-        <x:v>siɑo53ɕyəʔ3ɕyəʔ4</x:v>
+        <x:v>siao xye xye</x:v>
       </x:c>
     </x:row>
     <x:row r="484">
@@ -7082,7 +7082,7 @@
         <x:v>婶婶</x:v>
       </x:c>
       <x:c r="D484" s="5" t="str">
-        <x:v>ɕiŋ53ɕiŋ55</x:v>
+        <x:v>xing xing</x:v>
       </x:c>
     </x:row>
     <x:row r="485">
@@ -7096,7 +7096,7 @@
         <x:v>娘娘</x:v>
       </x:c>
       <x:c r="D485" s="5" t="str">
-        <x:v>ȵiɑŋ33ȵiɑŋ55</x:v>
+        <x:v>niang niang</x:v>
       </x:c>
     </x:row>
     <x:row r="486">
@@ -7110,7 +7110,7 @@
         <x:v>姑夫</x:v>
       </x:c>
       <x:c r="D486" s="5" t="str">
-        <x:v>ku33fu55</x:v>
+        <x:v>ku fu</x:v>
       </x:c>
     </x:row>
     <x:row r="487">
@@ -7124,7 +7124,7 @@
         <x:v>舅母</x:v>
       </x:c>
       <x:c r="D487" s="5" t="str">
-        <x:v>ʨiu33Ǿm535</x:v>
+        <x:v>jiu m</x:v>
       </x:c>
     </x:row>
     <x:row r="488">
@@ -7138,7 +7138,7 @@
         <x:v>姨娘</x:v>
       </x:c>
       <x:c r="D488" s="5" t="str">
-        <x:v>Ǿi31ȵiɑŋ14</x:v>
+        <x:v>i niang</x:v>
       </x:c>
     </x:row>
     <x:row r="489">
@@ -7152,7 +7152,7 @@
         <x:v>姨爷</x:v>
       </x:c>
       <x:c r="D489" s="5" t="str">
-        <x:v>Ǿi31Ǿia14</x:v>
+        <x:v>i ia</x:v>
       </x:c>
     </x:row>
     <x:row r="490">
@@ -7166,7 +7166,7 @@
         <x:v>哥弟</x:v>
       </x:c>
       <x:c r="D490" s="5" t="str">
-        <x:v>kuɤ33tie535</x:v>
+        <x:v>kue tie</x:v>
       </x:c>
     </x:row>
     <x:row r="491">
@@ -7180,7 +7180,7 @@
         <x:v>嫂嫂</x:v>
       </x:c>
       <x:c r="D491" s="5" t="str">
-        <x:v>sɑo53sɑo55</x:v>
+        <x:v>sao sao</x:v>
       </x:c>
     </x:row>
     <x:row r="492">
@@ -7194,7 +7194,7 @@
         <x:v>弟</x:v>
       </x:c>
       <x:c r="D492" s="5" t="str">
-        <x:v>tie535</x:v>
+        <x:v>tie</x:v>
       </x:c>
     </x:row>
     <x:row r="493">
@@ -7208,7 +7208,7 @@
         <x:v>弟妇</x:v>
       </x:c>
       <x:c r="D493" s="5" t="str">
-        <x:v>tie33fu535</x:v>
+        <x:v>tie fu</x:v>
       </x:c>
     </x:row>
     <x:row r="494">
@@ -7222,7 +7222,7 @@
         <x:v>姊姊</x:v>
       </x:c>
       <x:c r="D494" s="5" t="str">
-        <x:v>tɕi33tɕi55</x:v>
+        <x:v>ji ji</x:v>
       </x:c>
     </x:row>
     <x:row r="495">
@@ -7236,7 +7236,7 @@
         <x:v>姊夫</x:v>
       </x:c>
       <x:c r="D495" s="5" t="str">
-        <x:v>tɕi55fu334</x:v>
+        <x:v>ji fu</x:v>
       </x:c>
     </x:row>
     <x:row r="496">
@@ -7250,7 +7250,7 @@
         <x:v>妹</x:v>
       </x:c>
       <x:c r="D496" s="5" t="str">
-        <x:v>mɛ14</x:v>
+        <x:v>me</x:v>
       </x:c>
     </x:row>
     <x:row r="497">
@@ -7264,7 +7264,7 @@
         <x:v>叔伯哥弟</x:v>
       </x:c>
       <x:c r="D497" s="5" t="str">
-        <x:v>ɕyəʔ4pəʔ4kuɤ33tie535</x:v>
+        <x:v>xye pe kue tie</x:v>
       </x:c>
     </x:row>
     <x:row r="498">
@@ -7278,7 +7278,7 @@
         <x:v>堂份哥弟</x:v>
       </x:c>
       <x:c r="D498" s="5" t="str">
-        <x:v>dɑŋ31vəŋ14kuɤ33tie535</x:v>
+        <x:v>dang veng kue tie</x:v>
       </x:c>
     </x:row>
     <x:row r="499">
@@ -7292,7 +7292,7 @@
         <x:v>表兄哥弟</x:v>
       </x:c>
       <x:c r="D499" s="5" t="str">
-        <x:v>piɑo55ɕioŋ33kuɤ33tie535</x:v>
+        <x:v>piao xiong kue tie</x:v>
       </x:c>
     </x:row>
     <x:row r="500">
@@ -7306,7 +7306,7 @@
         <x:v>叔伯姆</x:v>
       </x:c>
       <x:c r="D500" s="5" t="str">
-        <x:v>ɕyəʔ4pəʔ4Ǿm535</x:v>
+        <x:v>xye pe m</x:v>
       </x:c>
     </x:row>
     <x:row r="501">
@@ -7320,7 +7320,7 @@
         <x:v>姨夫</x:v>
       </x:c>
       <x:c r="D501" s="5" t="str">
-        <x:v>Ǿi31fu55</x:v>
+        <x:v>i fu</x:v>
       </x:c>
     </x:row>
     <x:row r="502">
@@ -7334,7 +7334,7 @@
         <x:v>儿</x:v>
       </x:c>
       <x:c r="D502" s="5" t="str">
-        <x:v>Ǿŋ313</x:v>
+        <x:v>ng</x:v>
       </x:c>
     </x:row>
     <x:row r="503">
@@ -7348,7 +7348,7 @@
         <x:v>新妇</x:v>
       </x:c>
       <x:c r="D503" s="5" t="str">
-        <x:v>ɕiŋ33fu535</x:v>
+        <x:v>xing fu</x:v>
       </x:c>
     </x:row>
     <x:row r="504">
@@ -7362,7 +7362,7 @@
         <x:v>囡儿</x:v>
       </x:c>
       <x:c r="D504" s="5" t="str">
-        <x:v>nɛ̃14</x:v>
+        <x:v>ne</x:v>
       </x:c>
     </x:row>
     <x:row r="505">
@@ -7376,7 +7376,7 @@
         <x:v>囡婿</x:v>
       </x:c>
       <x:c r="D505" s="5" t="str">
-        <x:v>nɑ53ɕie55</x:v>
+        <x:v>na xie</x:v>
       </x:c>
     </x:row>
     <x:row r="506">
@@ -7390,7 +7390,7 @@
         <x:v>孙</x:v>
       </x:c>
       <x:c r="D506" s="5" t="str">
-        <x:v>səŋ334</x:v>
+        <x:v>seng</x:v>
       </x:c>
     </x:row>
     <x:row r="507">
@@ -7404,7 +7404,7 @@
         <x:v>玄孙</x:v>
       </x:c>
       <x:c r="D507" s="5" t="str">
-        <x:v>Ǿyɤ31səŋ55</x:v>
+        <x:v>ye seng</x:v>
       </x:c>
     </x:row>
     <x:row r="508">
@@ -7418,7 +7418,7 @@
         <x:v>侄儿</x:v>
       </x:c>
       <x:c r="D508" s="5" t="str">
-        <x:v>dʑiŋ14</x:v>
+        <x:v>jing</x:v>
       </x:c>
     </x:row>
     <x:row r="509">
@@ -7432,7 +7432,7 @@
         <x:v>外甥</x:v>
       </x:c>
       <x:c r="D509" s="5" t="str">
-        <x:v>Ǿɑ53sɑŋ55</x:v>
+        <x:v>a sang</x:v>
       </x:c>
     </x:row>
     <x:row r="510">
@@ -7446,7 +7446,7 @@
         <x:v>公婆两个</x:v>
       </x:c>
       <x:c r="D510" s="5" t="str">
-        <x:v>koŋ33pɤ33liɑŋ53kəʔ4</x:v>
+        <x:v>kong pe liang ke</x:v>
       </x:c>
     </x:row>
     <x:row r="511">
@@ -7460,7 +7460,7 @@
         <x:v>老公</x:v>
       </x:c>
       <x:c r="D511" s="5" t="str">
-        <x:v>lɑo55koŋ334</x:v>
+        <x:v>lao kong</x:v>
       </x:c>
     </x:row>
     <x:row r="512">
@@ -7474,7 +7474,7 @@
         <x:v>老婆</x:v>
       </x:c>
       <x:c r="D512" s="5" t="str">
-        <x:v>lɑo55bɤ313</x:v>
+        <x:v>lao be</x:v>
       </x:c>
     </x:row>
     <x:row r="513">
@@ -7488,7 +7488,7 @@
         <x:v>野名</x:v>
       </x:c>
       <x:c r="D513" s="5" t="str">
-        <x:v>Ǿia55miŋ313</x:v>
+        <x:v>ia ming</x:v>
       </x:c>
     </x:row>
     <x:row r="514">
@@ -7502,7 +7502,7 @@
         <x:v>做生活</x:v>
       </x:c>
       <x:c r="D514" s="5" t="str">
-        <x:v>tsuɤ33sɑŋ33Ǿuɑ14</x:v>
+        <x:v>tsue sang ua</x:v>
       </x:c>
     </x:row>
     <x:row r="515">
@@ -7516,7 +7516,7 @@
         <x:v>事干</x:v>
       </x:c>
       <x:c r="D515" s="5" t="str">
-        <x:v>zɿ31kɤ55</x:v>
+        <x:v>zi ke</x:v>
       </x:c>
     </x:row>
     <x:row r="516">
@@ -7530,7 +7530,7 @@
         <x:v>种田</x:v>
       </x:c>
       <x:c r="D516" s="5" t="str">
-        <x:v>tɕioŋ33dia313</x:v>
+        <x:v>jiong dia</x:v>
       </x:c>
     </x:row>
     <x:row r="517">
@@ -7544,7 +7544,7 @@
         <x:v>钐䥛</x:v>
       </x:c>
       <x:c r="D517" s="5" t="str">
-        <x:v>suɑ33tɕie55</x:v>
+        <x:v>sua jie</x:v>
       </x:c>
     </x:row>
     <x:row r="518">
@@ -7558,7 +7558,7 @@
         <x:v>柄</x:v>
       </x:c>
       <x:c r="D518" s="5" t="str">
-        <x:v>piŋ55</x:v>
+        <x:v>ping</x:v>
       </x:c>
     </x:row>
     <x:row r="519">
@@ -7572,7 +7572,7 @@
         <x:v>箩</x:v>
       </x:c>
       <x:c r="D519" s="5" t="str">
-        <x:v>luɤ313</x:v>
+        <x:v>lue</x:v>
       </x:c>
     </x:row>
     <x:row r="520">
@@ -7586,7 +7586,7 @@
         <x:v>筛</x:v>
       </x:c>
       <x:c r="D520" s="5" t="str">
-        <x:v>sɿ334</x:v>
+        <x:v>si</x:v>
       </x:c>
     </x:row>
     <x:row r="521">
@@ -7600,7 +7600,7 @@
         <x:v>𡊄箕</x:v>
       </x:c>
       <x:c r="D521" s="5" t="str">
-        <x:v>pəŋ33tɕi55</x:v>
+        <x:v>peng ji</x:v>
       </x:c>
     </x:row>
     <x:row r="522">
@@ -7614,7 +7614,7 @@
         <x:v>团报=</x:v>
       </x:c>
       <x:c r="D522" s="5" t="str">
-        <x:v>dɤ31pɑo55</x:v>
+        <x:v>de pao</x:v>
       </x:c>
     </x:row>
     <x:row r="523">
@@ -7628,7 +7628,7 @@
         <x:v>轮盘</x:v>
       </x:c>
       <x:c r="D523" s="5" t="str">
-        <x:v>ləŋ31bɤ14</x:v>
+        <x:v>leng be</x:v>
       </x:c>
     </x:row>
     <x:row r="524">
@@ -7642,7 +7642,7 @@
         <x:v>水碓</x:v>
       </x:c>
       <x:c r="D524" s="5" t="str">
-        <x:v>ɕy53tɛ55</x:v>
+        <x:v>xy te</x:v>
       </x:c>
     </x:row>
     <x:row r="525">
@@ -7656,7 +7656,7 @@
         <x:v>稻臼</x:v>
       </x:c>
       <x:c r="D525" s="5" t="str">
-        <x:v>tɑo33tɕiu535</x:v>
+        <x:v>tao jiu</x:v>
       </x:c>
     </x:row>
     <x:row r="526">
@@ -7670,7 +7670,7 @@
         <x:v>麦磨</x:v>
       </x:c>
       <x:c r="D526" s="5" t="str">
-        <x:v>məʔ21mɤ14</x:v>
+        <x:v>me me</x:v>
       </x:c>
     </x:row>
     <x:row r="527">
@@ -7684,7 +7684,7 @@
         <x:v>斧头</x:v>
       </x:c>
       <x:c r="D527" s="5" t="str">
-        <x:v>fu55diu313</x:v>
+        <x:v>fu diu</x:v>
       </x:c>
     </x:row>
     <x:row r="528">
@@ -7698,7 +7698,7 @@
         <x:v>老虎钳儿</x:v>
       </x:c>
       <x:c r="D528" s="5" t="str">
-        <x:v>lɑo53xu55dʑiɛ̄313</x:v>
+        <x:v>lao xu jie</x:v>
       </x:c>
     </x:row>
     <x:row r="529">
@@ -7712,7 +7712,7 @@
         <x:v>起子</x:v>
       </x:c>
       <x:c r="D529" s="5" t="str">
-        <x:v>tɕhi33tsɿ535</x:v>
+        <x:v>qi tsi</x:v>
       </x:c>
     </x:row>
     <x:row r="530">
@@ -7726,7 +7726,7 @@
         <x:v>榔头</x:v>
       </x:c>
       <x:c r="D530" s="5" t="str">
-        <x:v>lɑŋ31diu14</x:v>
+        <x:v>lang diu</x:v>
       </x:c>
     </x:row>
     <x:row r="531">
@@ -7740,7 +7740,7 @@
         <x:v>洋钉</x:v>
       </x:c>
       <x:c r="D531" s="5" t="str">
-        <x:v>Ǿiɑŋ31tiŋ55</x:v>
+        <x:v>iang ting</x:v>
       </x:c>
     </x:row>
     <x:row r="532">
@@ -7754,7 +7754,7 @@
         <x:v>铁钉</x:v>
       </x:c>
       <x:c r="D532" s="5" t="str">
-        <x:v>thia55tiŋ0</x:v>
+        <x:v>thia ting</x:v>
       </x:c>
     </x:row>
     <x:row r="533">
@@ -7768,7 +7768,7 @@
         <x:v>绳</x:v>
       </x:c>
       <x:c r="D533" s="5" t="str">
-        <x:v>ʑiŋ313</x:v>
+        <x:v>ring</x:v>
       </x:c>
     </x:row>
     <x:row r="534">
@@ -7782,7 +7782,7 @@
         <x:v>索</x:v>
       </x:c>
       <x:c r="D534" s="5" t="str">
-        <x:v>soʔ4</x:v>
+        <x:v>so</x:v>
       </x:c>
     </x:row>
     <x:row r="535">
@@ -7796,7 +7796,7 @@
         <x:v>棍</x:v>
       </x:c>
       <x:c r="D535" s="5" t="str">
-        <x:v>kuəŋ535</x:v>
+        <x:v>kueng</x:v>
       </x:c>
     </x:row>
     <x:row r="536">
@@ -7810,7 +7810,7 @@
         <x:v>做生意</x:v>
       </x:c>
       <x:c r="D536" s="5" t="str">
-        <x:v>tsuɤ33sɑŋ33Ǿi55</x:v>
+        <x:v>tsue sang i</x:v>
       </x:c>
     </x:row>
     <x:row r="537">
@@ -7824,7 +7824,7 @@
         <x:v>店</x:v>
       </x:c>
       <x:c r="D537" s="5" t="str">
-        <x:v>tia55</x:v>
+        <x:v>tia</x:v>
       </x:c>
     </x:row>
     <x:row r="538">
@@ -7838,7 +7838,7 @@
         <x:v>饭店</x:v>
       </x:c>
       <x:c r="D538" s="5" t="str">
-        <x:v>vɑ31tia55</x:v>
+        <x:v>va tia</x:v>
       </x:c>
     </x:row>
     <x:row r="539">
@@ -7852,7 +7852,7 @@
         <x:v>歇店</x:v>
       </x:c>
       <x:c r="D539" s="5" t="str">
-        <x:v>ɕie53tia55</x:v>
+        <x:v>xie tia</x:v>
       </x:c>
     </x:row>
     <x:row r="540">
@@ -7866,7 +7866,7 @@
         <x:v>贱</x:v>
       </x:c>
       <x:c r="D540" s="5" t="str">
-        <x:v>ʑie14</x:v>
+        <x:v>rie</x:v>
       </x:c>
     </x:row>
     <x:row r="541">
@@ -7880,7 +7880,7 @@
         <x:v>合着</x:v>
       </x:c>
       <x:c r="D541" s="5" t="str">
-        <x:v>kɤ55tɕiəʔ0</x:v>
+        <x:v>ke jie</x:v>
       </x:c>
     </x:row>
     <x:row r="542">
@@ -7894,7 +7894,7 @@
         <x:v>划算</x:v>
       </x:c>
       <x:c r="D542" s="5" t="str">
-        <x:v>Ǿuɑ31sɤ55</x:v>
+        <x:v>ua se</x:v>
       </x:c>
     </x:row>
     <x:row r="543">
@@ -7908,7 +7908,7 @@
         <x:v>折头</x:v>
       </x:c>
       <x:c r="D543" s="5" t="str">
-        <x:v>tɕyɤ55tiu0</x:v>
+        <x:v>jye tiu</x:v>
       </x:c>
     </x:row>
     <x:row r="544">
@@ -7922,7 +7922,7 @@
         <x:v>折本</x:v>
       </x:c>
       <x:c r="D544" s="5" t="str">
-        <x:v>ɕyɤ55pəŋ535</x:v>
+        <x:v>xye peng</x:v>
       </x:c>
     </x:row>
     <x:row r="545">
@@ -7936,7 +7936,7 @@
         <x:v>洋钿</x:v>
       </x:c>
       <x:c r="D545" s="5" t="str">
-        <x:v>Ǿiɑŋ31die14</x:v>
+        <x:v>iang die</x:v>
       </x:c>
     </x:row>
     <x:row r="546">
@@ -7950,7 +7950,7 @@
         <x:v>钞票</x:v>
       </x:c>
       <x:c r="D546" s="5" t="str">
-        <x:v>tshɑo53phiɑo55</x:v>
+        <x:v>tshao phiao</x:v>
       </x:c>
     </x:row>
     <x:row r="547">
@@ -7964,7 +7964,7 @@
         <x:v>散票</x:v>
       </x:c>
       <x:c r="D547" s="5" t="str">
-        <x:v>sɑ53phiɑo55</x:v>
+        <x:v>sa phiao</x:v>
       </x:c>
     </x:row>
     <x:row r="548">
@@ -7978,7 +7978,7 @@
         <x:v>零散钞票</x:v>
       </x:c>
       <x:c r="D548" s="5" t="str">
-        <x:v>liŋ33sɑ535tshɑo53phiɑo55</x:v>
+        <x:v>ling sa tshao phiao</x:v>
       </x:c>
     </x:row>
     <x:row r="549">
@@ -7992,7 +7992,7 @@
         <x:v>铅角子</x:v>
       </x:c>
       <x:c r="D549" s="5" t="str">
-        <x:v>khɑ33koʔ3tsɿ55</x:v>
+        <x:v>kha ko tsi</x:v>
       </x:c>
     </x:row>
     <x:row r="550">
@@ -8006,7 +8006,7 @@
         <x:v>本钿</x:v>
       </x:c>
       <x:c r="D550" s="5" t="str">
-        <x:v>pəŋ55die313</x:v>
+        <x:v>peng die</x:v>
       </x:c>
     </x:row>
     <x:row r="551">
@@ -8020,7 +8020,7 @@
         <x:v>工夫钿</x:v>
       </x:c>
       <x:c r="D551" s="5" t="str">
-        <x:v>koŋ33fu33tie55</x:v>
+        <x:v>kong fu tie</x:v>
       </x:c>
     </x:row>
     <x:row r="552">
@@ -8034,7 +8034,7 @@
         <x:v>盘缠</x:v>
       </x:c>
       <x:c r="D552" s="5" t="str">
-        <x:v>bɤ31dʑyɤ14</x:v>
+        <x:v>be jye</x:v>
       </x:c>
     </x:row>
     <x:row r="553">
@@ -8048,7 +8048,7 @@
         <x:v>用</x:v>
       </x:c>
       <x:c r="D553" s="5" t="str">
-        <x:v>Ǿioŋ14</x:v>
+        <x:v>iong</x:v>
       </x:c>
     </x:row>
     <x:row r="554">
@@ -8062,7 +8062,7 @@
         <x:v>赚</x:v>
       </x:c>
       <x:c r="D554" s="5" t="str">
-        <x:v>sɑ535</x:v>
+        <x:v>sa</x:v>
       </x:c>
     </x:row>
     <x:row r="555">
@@ -8076,7 +8076,7 @@
         <x:v>赶市日</x:v>
       </x:c>
       <x:c r="D555" s="5" t="str">
-        <x:v>kɤ53sɿ55ȵiəʔ212</x:v>
+        <x:v>ke si nie</x:v>
       </x:c>
     </x:row>
     <x:row r="556">
@@ -8090,7 +8090,7 @@
         <x:v>市日</x:v>
       </x:c>
       <x:c r="D556" s="5" t="str">
-        <x:v>sɿ55ȵiəʔ212</x:v>
+        <x:v>si nie</x:v>
       </x:c>
     </x:row>
     <x:row r="557">
@@ -8104,7 +8104,7 @@
         <x:v>学堂</x:v>
       </x:c>
       <x:c r="D557" s="5" t="str">
-        <x:v>Ǿoʔ21dɑŋ14</x:v>
+        <x:v>o dang</x:v>
       </x:c>
     </x:row>
     <x:row r="558">
@@ -8118,7 +8118,7 @@
         <x:v>上学堂</x:v>
       </x:c>
       <x:c r="D558" s="5" t="str">
-        <x:v>ɕiɑŋ53Ǿoʔ21dɑŋ14</x:v>
+        <x:v>xiang o dang</x:v>
       </x:c>
     </x:row>
     <x:row r="559">
@@ -8132,7 +8132,7 @@
         <x:v>读书</x:v>
       </x:c>
       <x:c r="D559" s="5" t="str">
-        <x:v>doʔ21ɕy334</x:v>
+        <x:v>do xy</x:v>
       </x:c>
     </x:row>
     <x:row r="560">
@@ -8146,7 +8146,7 @@
         <x:v>放夜学</x:v>
       </x:c>
       <x:c r="D560" s="5" t="str">
-        <x:v>fɑŋ33Ǿia55Ǿoʔ212</x:v>
+        <x:v>fang ia o</x:v>
       </x:c>
     </x:row>
     <x:row r="561">
@@ -8160,7 +8160,7 @@
         <x:v>书包袋</x:v>
       </x:c>
       <x:c r="D561" s="5" t="str">
-        <x:v>ɕy33pɑo33dɛ14</x:v>
+        <x:v>xy pao de</x:v>
       </x:c>
     </x:row>
     <x:row r="562">
@@ -8174,7 +8174,7 @@
         <x:v>簿</x:v>
       </x:c>
       <x:c r="D562" s="5" t="str">
-        <x:v>pu535</x:v>
+        <x:v>pu</x:v>
       </x:c>
     </x:row>
     <x:row r="563">
@@ -8188,7 +8188,7 @@
         <x:v>圆子笔</x:v>
       </x:c>
       <x:c r="D563" s="5" t="str">
-        <x:v>Ǿyɛ̃31tsɿ55piəʔ4</x:v>
+        <x:v>ye tsi pie</x:v>
       </x:c>
     </x:row>
     <x:row r="564">
@@ -8202,7 +8202,7 @@
         <x:v>墨笔</x:v>
       </x:c>
       <x:c r="D564" s="5" t="str">
-        <x:v>məʔ21piəʔ4</x:v>
+        <x:v>me pie</x:v>
       </x:c>
     </x:row>
     <x:row r="565">
@@ -8216,7 +8216,7 @@
         <x:v>砚瓦</x:v>
       </x:c>
       <x:c r="D565" s="5" t="str">
-        <x:v>ȵie33Ǿuɑ535</x:v>
+        <x:v>nie ua</x:v>
       </x:c>
     </x:row>
     <x:row r="566">
@@ -8230,7 +8230,7 @@
         <x:v>小书</x:v>
       </x:c>
       <x:c r="D566" s="5" t="str">
-        <x:v>siɑo55ɕy334</x:v>
+        <x:v>siao xy</x:v>
       </x:c>
     </x:row>
     <x:row r="567">
@@ -8244,7 +8244,7 @@
         <x:v>虾兵#3强盗</x:v>
       </x:c>
       <x:c r="D567" s="5" t="str">
-        <x:v>xuɑ53piŋ55ȵyɑ313dʑiɑŋ31dɑo14</x:v>
+        <x:v>xua ping nya jiang dao</x:v>
       </x:c>
     </x:row>
     <x:row r="568">
@@ -8258,7 +8258,7 @@
         <x:v>官兵揢强盗</x:v>
       </x:c>
       <x:c r="D568" s="5" t="str">
-        <x:v>kuɑ33piŋ55khuɑ55dʑiɑŋ31dɑo14</x:v>
+        <x:v>kua ping khua jiang dao</x:v>
       </x:c>
     </x:row>
     <x:row r="569">
@@ -8272,7 +8272,7 @@
         <x:v>毽</x:v>
       </x:c>
       <x:c r="D569" s="5" t="str">
-        <x:v>tɕie55</x:v>
+        <x:v>jie</x:v>
       </x:c>
     </x:row>
     <x:row r="570">
@@ -8286,7 +8286,7 @@
         <x:v>纸鹞</x:v>
       </x:c>
       <x:c r="D570" s="5" t="str">
-        <x:v>tsɿ55Ǿiɑo14</x:v>
+        <x:v>tsi iao</x:v>
       </x:c>
     </x:row>
     <x:row r="571">
@@ -8300,7 +8300,7 @@
         <x:v>掉狮子</x:v>
       </x:c>
       <x:c r="D571" s="5" t="str">
-        <x:v>diɑo14sɿ33tsɿ55</x:v>
+        <x:v>diao si tsi</x:v>
       </x:c>
     </x:row>
     <x:row r="572">
@@ -8314,7 +8314,7 @@
         <x:v>炮仗</x:v>
       </x:c>
       <x:c r="D572" s="5" t="str">
-        <x:v>phɑo33tɕiɑŋ55</x:v>
+        <x:v>phao jiang</x:v>
       </x:c>
     </x:row>
     <x:row r="573">
@@ -8328,7 +8328,7 @@
         <x:v>做戏</x:v>
       </x:c>
       <x:c r="D573" s="5" t="str">
-        <x:v>tsuɤ33ɕi55</x:v>
+        <x:v>tsue xi</x:v>
       </x:c>
     </x:row>
     <x:row r="574">
@@ -8342,7 +8342,7 @@
         <x:v>胡琴</x:v>
       </x:c>
       <x:c r="D574" s="5" t="str">
-        <x:v>Ǿu31dʑiŋ14</x:v>
+        <x:v>u jing</x:v>
       </x:c>
     </x:row>
     <x:row r="575">
@@ -8356,7 +8356,7 @@
         <x:v>笛儿</x:v>
       </x:c>
       <x:c r="D575" s="5" t="str">
-        <x:v>di14</x:v>
+        <x:v>di</x:v>
       </x:c>
     </x:row>
     <x:row r="576">
@@ -8370,7 +8370,7 @@
         <x:v>豁拳</x:v>
       </x:c>
       <x:c r="D576" s="5" t="str">
-        <x:v>xuɑ55dʑyɤ313</x:v>
+        <x:v>xua jye</x:v>
       </x:c>
     </x:row>
     <x:row r="577">
@@ -8384,7 +8384,7 @@
         <x:v>走棋</x:v>
       </x:c>
       <x:c r="D577" s="5" t="str">
-        <x:v>tɕiu55dʑi313</x:v>
+        <x:v>jiu ji</x:v>
       </x:c>
     </x:row>
     <x:row r="578">
@@ -8398,7 +8398,7 @@
         <x:v>打老K</x:v>
       </x:c>
       <x:c r="D578" s="5" t="str">
-        <x:v>tɑŋ55lɑo14khɛ0</x:v>
+        <x:v>tang lao khe</x:v>
       </x:c>
     </x:row>
     <x:row r="579">
@@ -8412,7 +8412,7 @@
         <x:v>搓麻将</x:v>
       </x:c>
       <x:c r="D579" s="5" t="str">
-        <x:v>tshuɑ55mɤa31tsiɑŋ55</x:v>
+        <x:v>tshua mea tsiang</x:v>
       </x:c>
     </x:row>
     <x:row r="580">
@@ -8426,7 +8426,7 @@
         <x:v>变戏法儿</x:v>
       </x:c>
       <x:c r="D580" s="5" t="str">
-        <x:v>pie33ɕi33fɤã55</x:v>
+        <x:v>pie xi fea</x:v>
       </x:c>
     </x:row>
     <x:row r="581">
@@ -8440,7 +8440,7 @@
         <x:v>讲大话</x:v>
       </x:c>
       <x:c r="D581" s="5" t="str">
-        <x:v>kɑŋ55tuɤ53Ǿuɑ14</x:v>
+        <x:v>kang tue ua</x:v>
       </x:c>
     </x:row>
     <x:row r="582">
@@ -8454,7 +8454,7 @@
         <x:v>猜语儿</x:v>
       </x:c>
       <x:c r="D582" s="5" t="str">
-        <x:v>tshɛ33ȵy14</x:v>
+        <x:v>tshe ny</x:v>
       </x:c>
     </x:row>
     <x:row r="583">
@@ -8468,7 +8468,7 @@
         <x:v>嬉</x:v>
       </x:c>
       <x:c r="D583" s="5" t="str">
-        <x:v>ɕi334</x:v>
+        <x:v>xi</x:v>
       </x:c>
     </x:row>
     <x:row r="584">
@@ -8482,7 +8482,7 @@
         <x:v>到隔壁邻舍窝=里去嬉</x:v>
       </x:c>
       <x:c r="D584" s="5" t="str">
-        <x:v>tɑo55kəʔ4piəʔ4liŋ31sia55Ǿuɤ33li535khɤ55ɕi334</x:v>
+        <x:v>tao ke pie ling sia ue li khe xi</x:v>
       </x:c>
     </x:row>
     <x:row r="585">
@@ -8496,7 +8496,7 @@
         <x:v>到亲戚窝=里去</x:v>
       </x:c>
       <x:c r="D585" s="5" t="str">
-        <x:v>tɑo55tɕhiŋ33tɕhiəʔ4Ǿuɤ33li55khɤ55</x:v>
+        <x:v>tao qing qie ue li khe</x:v>
       </x:c>
     </x:row>
     <x:row r="586">
@@ -8510,7 +8510,7 @@
         <x:v>望</x:v>
       </x:c>
       <x:c r="D586" s="5" t="str">
-        <x:v>moŋ14</x:v>
+        <x:v>mong</x:v>
       </x:c>
     </x:row>
     <x:row r="587">
@@ -8524,7 +8524,7 @@
         <x:v>呴</x:v>
       </x:c>
       <x:c r="D587" s="5" t="str">
-        <x:v>xiu334</x:v>
+        <x:v>xiu</x:v>
       </x:c>
     </x:row>
     <x:row r="588">
@@ -8538,7 +8538,7 @@
         <x:v>撑</x:v>
       </x:c>
       <x:c r="D588" s="5" t="str">
-        <x:v>tshɑŋ334</x:v>
+        <x:v>tshang</x:v>
       </x:c>
     </x:row>
     <x:row r="589">
@@ -8552,7 +8552,7 @@
         <x:v>合</x:v>
       </x:c>
       <x:c r="D589" s="5" t="str">
-        <x:v>kɤ55</x:v>
+        <x:v>ke</x:v>
       </x:c>
     </x:row>
     <x:row r="590">
@@ -8566,7 +8566,7 @@
         <x:v>开</x:v>
       </x:c>
       <x:c r="D590" s="5" t="str">
-        <x:v>khɛ334</x:v>
+        <x:v>khe</x:v>
       </x:c>
     </x:row>
     <x:row r="591">
@@ -8580,7 +8580,7 @@
         <x:v>啮</x:v>
       </x:c>
       <x:c r="D591" s="5" t="str">
-        <x:v>Ǿɤ14</x:v>
+        <x:v>e</x:v>
       </x:c>
     </x:row>
     <x:row r="592">
@@ -8594,7 +8594,7 @@
         <x:v>挟=</x:v>
       </x:c>
       <x:c r="D592" s="5" t="str">
-        <x:v>tsia55</x:v>
+        <x:v>tsia</x:v>
       </x:c>
     </x:row>
     <x:row r="593">
@@ -8608,7 +8608,7 @@
         <x:v>吞</x:v>
       </x:c>
       <x:c r="D593" s="5" t="str">
-        <x:v>thəŋ334</x:v>
+        <x:v>theng</x:v>
       </x:c>
     </x:row>
     <x:row r="594">
@@ -8622,7 +8622,7 @@
         <x:v>通#4</x:v>
       </x:c>
       <x:c r="D594" s="5" t="str">
-        <x:v>thoŋ33poŋ55</x:v>
+        <x:v>thong pong</x:v>
       </x:c>
     </x:row>
     <x:row r="595">
@@ -8636,7 +8636,7 @@
         <x:v>闻香</x:v>
       </x:c>
       <x:c r="D595" s="5" t="str">
-        <x:v>vəŋ31ɕiɑŋ334</x:v>
+        <x:v>veng xiang</x:v>
       </x:c>
     </x:row>
     <x:row r="596">
@@ -8650,7 +8650,7 @@
         <x:v>㰵</x:v>
       </x:c>
       <x:c r="D596" s="5" t="str">
-        <x:v>tɕyəʔ4</x:v>
+        <x:v>jye</x:v>
       </x:c>
     </x:row>
     <x:row r="597">
@@ -8664,7 +8664,7 @@
         <x:v>打嚏</x:v>
       </x:c>
       <x:c r="D597" s="5" t="str">
-        <x:v>tɑŋ53thi55</x:v>
+        <x:v>tang thi</x:v>
       </x:c>
     </x:row>
     <x:row r="598">
@@ -8678,7 +8678,7 @@
         <x:v>担</x:v>
       </x:c>
       <x:c r="D598" s="5" t="str">
-        <x:v>tɑ334</x:v>
+        <x:v>ta</x:v>
       </x:c>
     </x:row>
     <x:row r="599">
@@ -8692,7 +8692,7 @@
         <x:v>驮</x:v>
       </x:c>
       <x:c r="D599" s="5" t="str">
-        <x:v>duɤ313</x:v>
+        <x:v>due</x:v>
       </x:c>
     </x:row>
     <x:row r="600">
@@ -8706,7 +8706,7 @@
         <x:v>分</x:v>
       </x:c>
       <x:c r="D600" s="5" t="str">
-        <x:v>fəŋ334</x:v>
+        <x:v>feng</x:v>
       </x:c>
     </x:row>
     <x:row r="601">
@@ -8720,7 +8720,7 @@
         <x:v>担</x:v>
       </x:c>
       <x:c r="D601" s="5" t="str">
-        <x:v>tɑ334</x:v>
+        <x:v>ta</x:v>
       </x:c>
     </x:row>
     <x:row r="602">
@@ -8734,7 +8734,7 @@
         <x:v>直</x:v>
       </x:c>
       <x:c r="D602" s="5" t="str">
-        <x:v>dʑiəʔ212</x:v>
+        <x:v>jie</x:v>
       </x:c>
     </x:row>
     <x:row r="603">
@@ -8748,7 +8748,7 @@
         <x:v>抓</x:v>
       </x:c>
       <x:c r="D603" s="5" t="str">
-        <x:v>tsɑo334</x:v>
+        <x:v>tsao</x:v>
       </x:c>
     </x:row>
     <x:row r="604">
@@ -8762,7 +8762,7 @@
         <x:v>扚</x:v>
       </x:c>
       <x:c r="D604" s="5" t="str">
-        <x:v>tiəʔ4</x:v>
+        <x:v>tie</x:v>
       </x:c>
     </x:row>
     <x:row r="605">
@@ -8776,7 +8776,7 @@
         <x:v>𢈈</x:v>
       </x:c>
       <x:c r="D605" s="5" t="str">
-        <x:v>khəʔ4</x:v>
+        <x:v>khe</x:v>
       </x:c>
     </x:row>
     <x:row r="606">
@@ -8790,7 +8790,7 @@
         <x:v>旋</x:v>
       </x:c>
       <x:c r="D606" s="5" t="str">
-        <x:v>ʑie14</x:v>
+        <x:v>rie</x:v>
       </x:c>
     </x:row>
     <x:row r="607">
@@ -8804,7 +8804,7 @@
         <x:v>绞</x:v>
       </x:c>
       <x:c r="D607" s="5" t="str">
-        <x:v>kɑo535</x:v>
+        <x:v>kao</x:v>
       </x:c>
     </x:row>
     <x:row r="608">
@@ -8818,7 +8818,7 @@
         <x:v>搣</x:v>
       </x:c>
       <x:c r="D608" s="5" t="str">
-        <x:v>mie55</x:v>
+        <x:v>mie</x:v>
       </x:c>
     </x:row>
     <x:row r="609">
@@ -8832,7 +8832,7 @@
         <x:v>𤖼</x:v>
       </x:c>
       <x:c r="D609" s="5" t="str">
-        <x:v>phəʔ4</x:v>
+        <x:v>phe</x:v>
       </x:c>
     </x:row>
     <x:row r="610">
@@ -8846,7 +8846,7 @@
         <x:v>攦</x:v>
       </x:c>
       <x:c r="D610" s="5" t="str">
-        <x:v>tɕhi535</x:v>
+        <x:v>qi</x:v>
       </x:c>
     </x:row>
     <x:row r="611">
@@ -8860,7 +8860,7 @@
         <x:v>#5</x:v>
       </x:c>
       <x:c r="D611" s="5" t="str">
-        <x:v>Ǿɛ535</x:v>
+        <x:v>e</x:v>
       </x:c>
     </x:row>
     <x:row r="612">
@@ -8874,7 +8874,7 @@
         <x:v>摒</x:v>
       </x:c>
       <x:c r="D612" s="5" t="str">
-        <x:v>mɑŋ55</x:v>
+        <x:v>mang</x:v>
       </x:c>
     </x:row>
     <x:row r="613">
@@ -8888,7 +8888,7 @@
         <x:v>徛</x:v>
       </x:c>
       <x:c r="D613" s="5" t="str">
-        <x:v>kɛ535</x:v>
+        <x:v>ke</x:v>
       </x:c>
     </x:row>
     <x:row r="614">
@@ -8902,7 +8902,7 @@
         <x:v>隑</x:v>
       </x:c>
       <x:c r="D614" s="5" t="str">
-        <x:v>ɡɛ14</x:v>
+        <x:v>ge</x:v>
       </x:c>
     </x:row>
     <x:row r="615">
@@ -8916,7 +8916,7 @@
         <x:v>优=</x:v>
       </x:c>
       <x:c r="D615" s="5" t="str">
-        <x:v>Ǿiu334</x:v>
+        <x:v>iu</x:v>
       </x:c>
     </x:row>
     <x:row r="616">
@@ -8930,7 +8930,7 @@
         <x:v>#6</x:v>
       </x:c>
       <x:c r="D616" s="5" t="str">
-        <x:v>mɑŋ334</x:v>
+        <x:v>mang</x:v>
       </x:c>
     </x:row>
     <x:row r="617">
@@ -8944,7 +8944,7 @@
         <x:v>踏</x:v>
       </x:c>
       <x:c r="D617" s="5" t="str">
-        <x:v>duɑ14</x:v>
+        <x:v>dua</x:v>
       </x:c>
     </x:row>
     <x:row r="618">
@@ -8958,7 +8958,7 @@
         <x:v>#7</x:v>
       </x:c>
       <x:c r="D618" s="5" t="str">
-        <x:v>ɡɑo14</x:v>
+        <x:v>gao</x:v>
       </x:c>
     </x:row>
     <x:row r="619">
@@ -8972,7 +8972,7 @@
         <x:v>覆</x:v>
       </x:c>
       <x:c r="D619" s="5" t="str">
-        <x:v>phoʔ4</x:v>
+        <x:v>pho</x:v>
       </x:c>
     </x:row>
     <x:row r="620">
@@ -8986,7 +8986,7 @@
         <x:v>覆</x:v>
       </x:c>
       <x:c r="D620" s="5" t="str">
-        <x:v>phoʔ4</x:v>
+        <x:v>pho</x:v>
       </x:c>
     </x:row>
     <x:row r="621">
@@ -9000,7 +9000,7 @@
         <x:v>𧼱</x:v>
       </x:c>
       <x:c r="D621" s="5" t="str">
-        <x:v>biəʔ212</x:v>
+        <x:v>bie</x:v>
       </x:c>
     </x:row>
     <x:row r="622">
@@ -9014,7 +9014,7 @@
         <x:v>逃</x:v>
       </x:c>
       <x:c r="D622" s="5" t="str">
-        <x:v>dɑo313</x:v>
+        <x:v>dao</x:v>
       </x:c>
     </x:row>
     <x:row r="623">
@@ -9028,7 +9028,7 @@
         <x:v>赶</x:v>
       </x:c>
       <x:c r="D623" s="5" t="str">
-        <x:v>kɤ535</x:v>
+        <x:v>ke</x:v>
       </x:c>
     </x:row>
     <x:row r="624">
@@ -9042,7 +9042,7 @@
         <x:v>揢</x:v>
       </x:c>
       <x:c r="D624" s="5" t="str">
-        <x:v>khuɑ535</x:v>
+        <x:v>khua</x:v>
       </x:c>
     </x:row>
     <x:row r="625">
@@ -9056,7 +9056,7 @@
         <x:v>挟</x:v>
       </x:c>
       <x:c r="D625" s="5" t="str">
-        <x:v>ɡuɑ14</x:v>
+        <x:v>gua</x:v>
       </x:c>
     </x:row>
     <x:row r="626">
@@ -9070,7 +9070,7 @@
         <x:v>#8</x:v>
       </x:c>
       <x:c r="D626" s="5" t="str">
-        <x:v>Ǿiɑŋ55</x:v>
+        <x:v>iang</x:v>
       </x:c>
     </x:row>
     <x:row r="627">
@@ -9084,7 +9084,7 @@
         <x:v>挨=</x:v>
       </x:c>
       <x:c r="D627" s="5" t="str">
-        <x:v>Ǿɑ334</x:v>
+        <x:v>a</x:v>
       </x:c>
     </x:row>
     <x:row r="628">
@@ -9098,7 +9098,7 @@
         <x:v>跌</x:v>
       </x:c>
       <x:c r="D628" s="5" t="str">
-        <x:v>tia55</x:v>
+        <x:v>tia</x:v>
       </x:c>
     </x:row>
     <x:row r="629">
@@ -9112,7 +9112,7 @@
         <x:v>遮</x:v>
       </x:c>
       <x:c r="D629" s="5" t="str">
-        <x:v>tsia334</x:v>
+        <x:v>tsia</x:v>
       </x:c>
     </x:row>
     <x:row r="630">
@@ -9126,7 +9126,7 @@
         <x:v>优=</x:v>
       </x:c>
       <x:c r="D630" s="5" t="str">
-        <x:v>Ǿiu334</x:v>
+        <x:v>iu</x:v>
       </x:c>
     </x:row>
     <x:row r="631">
@@ -9140,7 +9140,7 @@
         <x:v>塞</x:v>
       </x:c>
       <x:c r="D631" s="5" t="str">
-        <x:v>səʔ4</x:v>
+        <x:v>se</x:v>
       </x:c>
     </x:row>
     <x:row r="632">
@@ -9154,7 +9154,7 @@
         <x:v>囥</x:v>
       </x:c>
       <x:c r="D632" s="5" t="str">
-        <x:v>khɑŋ55</x:v>
+        <x:v>khang</x:v>
       </x:c>
     </x:row>
     <x:row r="633">
@@ -9168,7 +9168,7 @@
         <x:v>摆</x:v>
       </x:c>
       <x:c r="D633" s="5" t="str">
-        <x:v>pɑ535</x:v>
+        <x:v>pa</x:v>
       </x:c>
     </x:row>
     <x:row r="634">
@@ -9182,7 +9182,7 @@
         <x:v>叠</x:v>
       </x:c>
       <x:c r="D634" s="5" t="str">
-        <x:v>dia14</x:v>
+        <x:v>dia</x:v>
       </x:c>
     </x:row>
     <x:row r="635">
@@ -9196,7 +9196,7 @@
         <x:v>恩=</x:v>
       </x:c>
       <x:c r="D635" s="5" t="str">
-        <x:v>Ǿəŋ334</x:v>
+        <x:v>eng</x:v>
       </x:c>
     </x:row>
     <x:row r="636">
@@ -9210,7 +9210,7 @@
         <x:v>揿</x:v>
       </x:c>
       <x:c r="D636" s="5" t="str">
-        <x:v>tɕhiŋ55</x:v>
+        <x:v>qing</x:v>
       </x:c>
     </x:row>
     <x:row r="637">
@@ -9224,7 +9224,7 @@
         <x:v>𧰵</x:v>
       </x:c>
       <x:c r="D637" s="5" t="str">
-        <x:v>toʔ4</x:v>
+        <x:v>to</x:v>
       </x:c>
     </x:row>
     <x:row r="638">
@@ -9238,7 +9238,7 @@
         <x:v>扦</x:v>
       </x:c>
       <x:c r="D638" s="5" t="str">
-        <x:v>tɕhie334</x:v>
+        <x:v>qie</x:v>
       </x:c>
     </x:row>
     <x:row r="639">
@@ -9252,7 +9252,7 @@
         <x:v>𧰵</x:v>
       </x:c>
       <x:c r="D639" s="5" t="str">
-        <x:v>toʔ4</x:v>
+        <x:v>to</x:v>
       </x:c>
     </x:row>
     <x:row r="640">
@@ -9266,7 +9266,7 @@
         <x:v>斲</x:v>
       </x:c>
       <x:c r="D640" s="5" t="str">
-        <x:v>tsoʔ4</x:v>
+        <x:v>tso</x:v>
       </x:c>
     </x:row>
     <x:row r="641">
@@ -9280,7 +9280,7 @@
         <x:v>劗</x:v>
       </x:c>
       <x:c r="D641" s="5" t="str">
-        <x:v>tsɑ334</x:v>
+        <x:v>tsa</x:v>
       </x:c>
     </x:row>
     <x:row r="642">
@@ -9294,7 +9294,7 @@
         <x:v>刨</x:v>
       </x:c>
       <x:c r="D642" s="5" t="str">
-        <x:v>bɑo14</x:v>
+        <x:v>bao</x:v>
       </x:c>
     </x:row>
     <x:row r="643">
@@ -9308,7 +9308,7 @@
         <x:v>㶁坼</x:v>
       </x:c>
       <x:c r="D643" s="5" t="str">
-        <x:v>kuəʔ4tshəʔ4</x:v>
+        <x:v>kue tshe</x:v>
       </x:c>
     </x:row>
     <x:row r="644">
@@ -9322,7 +9322,7 @@
         <x:v>㶁</x:v>
       </x:c>
       <x:c r="D644" s="5" t="str">
-        <x:v>kuəʔ4</x:v>
+        <x:v>kue</x:v>
       </x:c>
     </x:row>
     <x:row r="645">
@@ -9336,7 +9336,7 @@
         <x:v>纵=</x:v>
       </x:c>
       <x:c r="D645" s="5" t="str">
-        <x:v>tsoŋ55</x:v>
+        <x:v>tsong</x:v>
       </x:c>
     </x:row>
     <x:row r="646">
@@ -9350,7 +9350,7 @@
         <x:v>烂</x:v>
       </x:c>
       <x:c r="D646" s="5" t="str">
-        <x:v>lɑ14</x:v>
+        <x:v>la</x:v>
       </x:c>
     </x:row>
     <x:row r="647">
@@ -9364,7 +9364,7 @@
         <x:v>揩</x:v>
       </x:c>
       <x:c r="D647" s="5" t="str">
-        <x:v>khɑ334</x:v>
+        <x:v>kha</x:v>
       </x:c>
     </x:row>
     <x:row r="648">
@@ -9378,7 +9378,7 @@
         <x:v>#9</x:v>
       </x:c>
       <x:c r="D648" s="5" t="str">
-        <x:v>tɕhyɑ535</x:v>
+        <x:v>qya</x:v>
       </x:c>
     </x:row>
     <x:row r="649">
@@ -9392,7 +9392,7 @@
         <x:v>#10</x:v>
       </x:c>
       <x:c r="D649" s="5" t="str">
-        <x:v>liu55</x:v>
+        <x:v>liu</x:v>
       </x:c>
     </x:row>
     <x:row r="650">
@@ -9406,7 +9406,7 @@
         <x:v>掼</x:v>
       </x:c>
       <x:c r="D650" s="5" t="str">
-        <x:v>ɡuɑ14</x:v>
+        <x:v>gua</x:v>
       </x:c>
     </x:row>
     <x:row r="651">
@@ -9420,7 +9420,7 @@
         <x:v>#10</x:v>
       </x:c>
       <x:c r="D651" s="5" t="str">
-        <x:v>liu55</x:v>
+        <x:v>liu</x:v>
       </x:c>
     </x:row>
     <x:row r="652">
@@ -9434,7 +9434,7 @@
         <x:v>掼</x:v>
       </x:c>
       <x:c r="D652" s="5" t="str">
-        <x:v>ɡuɑ14</x:v>
+        <x:v>gua</x:v>
       </x:c>
     </x:row>
     <x:row r="653">
@@ -9448,7 +9448,7 @@
         <x:v>脱</x:v>
       </x:c>
       <x:c r="D653" s="5" t="str">
-        <x:v>thəʔ4</x:v>
+        <x:v>the</x:v>
       </x:c>
     </x:row>
     <x:row r="654">
@@ -9462,7 +9462,7 @@
         <x:v>渧</x:v>
       </x:c>
       <x:c r="D654" s="5" t="str">
-        <x:v>tia55</x:v>
+        <x:v>tia</x:v>
       </x:c>
     </x:row>
     <x:row r="655">
@@ -9476,7 +9476,7 @@
         <x:v>脱</x:v>
       </x:c>
       <x:c r="D655" s="5" t="str">
-        <x:v>thəʔ4</x:v>
+        <x:v>the</x:v>
       </x:c>
     </x:row>
     <x:row r="656">
@@ -9490,7 +9490,7 @@
         <x:v>户＝</x:v>
       </x:c>
       <x:c r="D656" s="5" t="str">
-        <x:v>Ǿu535</x:v>
+        <x:v>u</x:v>
       </x:c>
     </x:row>
     <x:row r="657">
@@ -9504,7 +9504,7 @@
         <x:v>寻</x:v>
       </x:c>
       <x:c r="D657" s="5" t="str">
-        <x:v>zəŋ313</x:v>
+        <x:v>zeng</x:v>
       </x:c>
     </x:row>
     <x:row r="658">
@@ -9518,7 +9518,7 @@
         <x:v>撮</x:v>
       </x:c>
       <x:c r="D658" s="5" t="str">
-        <x:v>tshəʔ4</x:v>
+        <x:v>tshe</x:v>
       </x:c>
     </x:row>
     <x:row r="659">
@@ -9532,7 +9532,7 @@
         <x:v>拎</x:v>
       </x:c>
       <x:c r="D659" s="5" t="str">
-        <x:v>liŋ334</x:v>
+        <x:v>ling</x:v>
       </x:c>
     </x:row>
     <x:row r="660">
@@ -9546,7 +9546,7 @@
         <x:v>𢷒</x:v>
       </x:c>
       <x:c r="D660" s="5" t="str">
-        <x:v>ɡɤ14</x:v>
+        <x:v>ge</x:v>
       </x:c>
     </x:row>
     <x:row r="661">
@@ -9560,7 +9560,7 @@
         <x:v>背</x:v>
       </x:c>
       <x:c r="D661" s="5" t="str">
-        <x:v>pɛ55</x:v>
+        <x:v>pe</x:v>
       </x:c>
     </x:row>
     <x:row r="662">
@@ -9574,7 +9574,7 @@
         <x:v>扛</x:v>
       </x:c>
       <x:c r="D662" s="5" t="str">
-        <x:v>kɑŋ334</x:v>
+        <x:v>kang</x:v>
       </x:c>
     </x:row>
     <x:row r="663">
@@ -9588,7 +9588,7 @@
         <x:v>擎</x:v>
       </x:c>
       <x:c r="D663" s="5" t="str">
-        <x:v>dʑiŋ313</x:v>
+        <x:v>jing</x:v>
       </x:c>
     </x:row>
     <x:row r="664">
@@ -9602,7 +9602,7 @@
         <x:v>照</x:v>
       </x:c>
       <x:c r="D664" s="5" t="str">
-        <x:v>tɕiɑo55</x:v>
+        <x:v>jiao</x:v>
       </x:c>
     </x:row>
     <x:row r="665">
@@ -9616,7 +9616,7 @@
         <x:v>择</x:v>
       </x:c>
       <x:c r="D665" s="5" t="str">
-        <x:v>dzəʔ212</x:v>
+        <x:v>dze</x:v>
       </x:c>
     </x:row>
     <x:row r="666">
@@ -9630,7 +9630,7 @@
         <x:v>集</x:v>
       </x:c>
       <x:c r="D666" s="5" t="str">
-        <x:v>ʑiəʔ212</x:v>
+        <x:v>rie</x:v>
       </x:c>
     </x:row>
     <x:row r="667">
@@ -9644,7 +9644,7 @@
         <x:v>滚</x:v>
       </x:c>
       <x:c r="D667" s="5" t="str">
-        <x:v>kuəŋ535</x:v>
+        <x:v>kueng</x:v>
       </x:c>
     </x:row>
     <x:row r="668">
@@ -9658,7 +9658,7 @@
         <x:v>盪</x:v>
       </x:c>
       <x:c r="D668" s="5" t="str">
-        <x:v>tɑŋ535</x:v>
+        <x:v>tang</x:v>
       </x:c>
     </x:row>
     <x:row r="669">
@@ -9672,7 +9672,7 @@
         <x:v>吊</x:v>
       </x:c>
       <x:c r="D669" s="5" t="str">
-        <x:v>tiɑo55</x:v>
+        <x:v>tiao</x:v>
       </x:c>
     </x:row>
     <x:row r="670">
@@ -9686,7 +9686,7 @@
         <x:v>缚</x:v>
       </x:c>
       <x:c r="D670" s="5" t="str">
-        <x:v>boʔ212</x:v>
+        <x:v>bo</x:v>
       </x:c>
     </x:row>
     <x:row r="671">
@@ -9700,7 +9700,7 @@
         <x:v>移</x:v>
       </x:c>
       <x:c r="D671" s="5" t="str">
-        <x:v>Ǿi313</x:v>
+        <x:v>i</x:v>
       </x:c>
     </x:row>
     <x:row r="672">
@@ -9714,7 +9714,7 @@
         <x:v>捧</x:v>
       </x:c>
       <x:c r="D672" s="5" t="str">
-        <x:v>phoŋ535</x:v>
+        <x:v>phong</x:v>
       </x:c>
     </x:row>
     <x:row r="673">
@@ -9728,7 +9728,7 @@
         <x:v>#11</x:v>
       </x:c>
       <x:c r="D673" s="5" t="str">
-        <x:v>xuɛ334</x:v>
+        <x:v>xue</x:v>
       </x:c>
     </x:row>
     <x:row r="674">
@@ -9742,7 +9742,7 @@
         <x:v>兑</x:v>
       </x:c>
       <x:c r="D674" s="5" t="str">
-        <x:v>tɛ55</x:v>
+        <x:v>te</x:v>
       </x:c>
     </x:row>
     <x:row r="675">
@@ -9756,7 +9756,7 @@
         <x:v>#12</x:v>
       </x:c>
       <x:c r="D675" s="5" t="str">
-        <x:v>loʔ4</x:v>
+        <x:v>lo</x:v>
       </x:c>
     </x:row>
     <x:row r="676">
@@ -9770,7 +9770,7 @@
         <x:v>旋</x:v>
       </x:c>
       <x:c r="D676" s="5" t="str">
-        <x:v>ʑyɤ14</x:v>
+        <x:v>rye</x:v>
       </x:c>
     </x:row>
     <x:row r="677">
@@ -9784,7 +9784,7 @@
         <x:v>敲</x:v>
       </x:c>
       <x:c r="D677" s="5" t="str">
-        <x:v>khɑo334</x:v>
+        <x:v>khao</x:v>
       </x:c>
     </x:row>
     <x:row r="678">
@@ -9798,7 +9798,7 @@
         <x:v>敲</x:v>
       </x:c>
       <x:c r="D678" s="5" t="str">
-        <x:v>khɑo334</x:v>
+        <x:v>khao</x:v>
       </x:c>
     </x:row>
     <x:row r="679">
@@ -9812,7 +9812,7 @@
         <x:v>打相打</x:v>
       </x:c>
       <x:c r="D679" s="5" t="str">
-        <x:v>tɑŋ55siɑŋ33tɑŋ535</x:v>
+        <x:v>tang siang tang</x:v>
       </x:c>
     </x:row>
     <x:row r="680">
@@ -9826,7 +9826,7 @@
         <x:v>歇力</x:v>
       </x:c>
       <x:c r="D680" s="5" t="str">
-        <x:v>ɕie55liəʔ212</x:v>
+        <x:v>xie lie</x:v>
       </x:c>
     </x:row>
     <x:row r="681">
@@ -9840,7 +9840,7 @@
         <x:v>打哈气</x:v>
       </x:c>
       <x:c r="D681" s="5" t="str">
-        <x:v>tɑŋ55xɑ33tɕhi55</x:v>
+        <x:v>tang xa qi</x:v>
       </x:c>
     </x:row>
     <x:row r="682">
@@ -9854,7 +9854,7 @@
         <x:v>打瞌𥅻</x:v>
       </x:c>
       <x:c r="D682" s="5" t="str">
-        <x:v>tɑŋ55khəʔ3tɕhioŋ55</x:v>
+        <x:v>tang khe qiong</x:v>
       </x:c>
     </x:row>
     <x:row r="683">
@@ -9868,7 +9868,7 @@
         <x:v>睏</x:v>
       </x:c>
       <x:c r="D683" s="5" t="str">
-        <x:v>khuəŋ55</x:v>
+        <x:v>khueng</x:v>
       </x:c>
     </x:row>
     <x:row r="684">
@@ -9882,7 +9882,7 @@
         <x:v>打鼾儿</x:v>
       </x:c>
       <x:c r="D684" s="5" t="str">
-        <x:v>tɑŋ55xɛ̃334</x:v>
+        <x:v>tang xe</x:v>
       </x:c>
     </x:row>
     <x:row r="685">
@@ -9896,7 +9896,7 @@
         <x:v>打鼾</x:v>
       </x:c>
       <x:c r="D685" s="5" t="str">
-        <x:v>tɑŋ55xɤ334</x:v>
+        <x:v>tang xe</x:v>
       </x:c>
     </x:row>
     <x:row r="686">
@@ -9910,7 +9910,7 @@
         <x:v>爬起来</x:v>
       </x:c>
       <x:c r="D686" s="5" t="str">
-        <x:v>bɤa31tɕhiəʔ3lɛ55</x:v>
+        <x:v>bea qie le</x:v>
       </x:c>
     </x:row>
     <x:row r="687">
@@ -9924,7 +9924,7 @@
         <x:v>洗牙齿</x:v>
       </x:c>
       <x:c r="D687" s="5" t="str">
-        <x:v>ɕie55Ǿuɑ33tshɿ535</x:v>
+        <x:v>xie ua tshi</x:v>
       </x:c>
     </x:row>
     <x:row r="688">
@@ -9938,7 +9938,7 @@
         <x:v>洗浴</x:v>
       </x:c>
       <x:c r="D688" s="5" t="str">
-        <x:v>ɕie55Ǿioʔ212</x:v>
+        <x:v>xie io</x:v>
       </x:c>
     </x:row>
     <x:row r="689">
@@ -9952,7 +9952,7 @@
         <x:v>忖</x:v>
       </x:c>
       <x:c r="D689" s="5" t="str">
-        <x:v>tshəŋ535</x:v>
+        <x:v>tsheng</x:v>
       </x:c>
     </x:row>
     <x:row r="690">
@@ -9966,7 +9966,7 @@
         <x:v>划算</x:v>
       </x:c>
       <x:c r="D690" s="5" t="str">
-        <x:v>Ǿuɑ31sɤ55</x:v>
+        <x:v>ua se</x:v>
       </x:c>
     </x:row>
     <x:row r="691">
@@ -9980,7 +9980,7 @@
         <x:v>想</x:v>
       </x:c>
       <x:c r="D691" s="5" t="str">
-        <x:v>siɑŋ535</x:v>
+        <x:v>siang</x:v>
       </x:c>
     </x:row>
     <x:row r="692">
@@ -9994,7 +9994,7 @@
         <x:v>记着</x:v>
       </x:c>
       <x:c r="D692" s="5" t="str">
-        <x:v>tɕi55tɕiəʔ0</x:v>
+        <x:v>ji jie</x:v>
       </x:c>
     </x:row>
     <x:row r="693">
@@ -10008,7 +10008,7 @@
         <x:v>惊</x:v>
       </x:c>
       <x:c r="D693" s="5" t="str">
-        <x:v>kuɑŋ334</x:v>
+        <x:v>kuang</x:v>
       </x:c>
     </x:row>
     <x:row r="694">
@@ -10022,7 +10022,7 @@
         <x:v>愁</x:v>
       </x:c>
       <x:c r="D694" s="5" t="str">
-        <x:v>ʑiu313</x:v>
+        <x:v>riu</x:v>
       </x:c>
     </x:row>
     <x:row r="695">
@@ -10036,7 +10036,7 @@
         <x:v>欢喜</x:v>
       </x:c>
       <x:c r="D695" s="5" t="str">
-        <x:v>xuɛ̃33ɕi535</x:v>
+        <x:v>xue xi</x:v>
       </x:c>
     </x:row>
     <x:row r="696">
@@ -10050,7 +10050,7 @@
         <x:v>望弗来</x:v>
       </x:c>
       <x:c r="D696" s="5" t="str">
-        <x:v>moŋ14fəʔ4lɛ313</x:v>
+        <x:v>mong fe le</x:v>
       </x:c>
     </x:row>
     <x:row r="697">
@@ -10064,7 +10064,7 @@
         <x:v>好过</x:v>
       </x:c>
       <x:c r="D697" s="5" t="str">
-        <x:v>xɑo53kuɤ55</x:v>
+        <x:v>xao kue</x:v>
       </x:c>
     </x:row>
     <x:row r="698">
@@ -10078,7 +10078,7 @@
         <x:v>难过</x:v>
       </x:c>
       <x:c r="D698" s="5" t="str">
-        <x:v>nɑ33kuɤ55</x:v>
+        <x:v>na kue</x:v>
       </x:c>
     </x:row>
     <x:row r="699">
@@ -10092,7 +10092,7 @@
         <x:v>有味</x:v>
       </x:c>
       <x:c r="D699" s="5" t="str">
-        <x:v>Ǿiu55vi14</x:v>
+        <x:v>iu vi</x:v>
       </x:c>
     </x:row>
     <x:row r="700">
@@ -10106,7 +10106,7 @@
         <x:v>开心</x:v>
       </x:c>
       <x:c r="D700" s="5" t="str">
-        <x:v>khɛ33ɕiŋ334</x:v>
+        <x:v>khe xing</x:v>
       </x:c>
     </x:row>
     <x:row r="701">
@@ -10120,7 +10120,7 @@
         <x:v>份=气</x:v>
       </x:c>
       <x:c r="D701" s="5" t="str">
-        <x:v>fəŋ53tɕhi55</x:v>
+        <x:v>feng qi</x:v>
       </x:c>
     </x:row>
     <x:row r="702">
@@ -10134,7 +10134,7 @@
         <x:v>怪</x:v>
       </x:c>
       <x:c r="D702" s="5" t="str">
-        <x:v>kuɑ55</x:v>
+        <x:v>kua</x:v>
       </x:c>
     </x:row>
     <x:row r="703">
@@ -10148,7 +10148,7 @@
         <x:v>悔</x:v>
       </x:c>
       <x:c r="D703" s="5" t="str">
-        <x:v>xui55</x:v>
+        <x:v>xui</x:v>
       </x:c>
     </x:row>
     <x:row r="704">
@@ -10162,7 +10162,7 @@
         <x:v>妒忌</x:v>
       </x:c>
       <x:c r="D704" s="5" t="str">
-        <x:v>tu55dʑi14</x:v>
+        <x:v>tu ji</x:v>
       </x:c>
     </x:row>
     <x:row r="705">
@@ -10176,7 +10176,7 @@
         <x:v>眼热</x:v>
       </x:c>
       <x:c r="D705" s="5" t="str">
-        <x:v>Ǿɑ55ȵie14</x:v>
+        <x:v>a nie</x:v>
       </x:c>
     </x:row>
     <x:row r="706">
@@ -10190,7 +10190,7 @@
         <x:v>惊倒霉</x:v>
       </x:c>
       <x:c r="D706" s="5" t="str">
-        <x:v>kuɑŋ33tɑo55mɛ313</x:v>
+        <x:v>kuang tao me</x:v>
       </x:c>
     </x:row>
     <x:row r="707">
@@ -10204,7 +10204,7 @@
         <x:v>倒霉</x:v>
       </x:c>
       <x:c r="D707" s="5" t="str">
-        <x:v>tɑo55mɛ313</x:v>
+        <x:v>tao me</x:v>
       </x:c>
     </x:row>
     <x:row r="708">
@@ -10218,7 +10218,7 @@
         <x:v>失面子</x:v>
       </x:c>
       <x:c r="D708" s="5" t="str">
-        <x:v>ɕiəʔ4mie53tsɿ55</x:v>
+        <x:v>xie mie tsi</x:v>
       </x:c>
     </x:row>
     <x:row r="709">
@@ -10232,7 +10232,7 @@
         <x:v>对=搭=</x:v>
       </x:c>
       <x:c r="D709" s="5" t="str">
-        <x:v>tɛ33tuɑ55</x:v>
+        <x:v>te tua</x:v>
       </x:c>
     </x:row>
     <x:row r="710">
@@ -10246,7 +10246,7 @@
         <x:v>诈</x:v>
       </x:c>
       <x:c r="D710" s="5" t="str">
-        <x:v>tsuɑ55</x:v>
+        <x:v>tsua</x:v>
       </x:c>
     </x:row>
     <x:row r="711">
@@ -10260,7 +10260,7 @@
         <x:v>值钿</x:v>
       </x:c>
       <x:c r="D711" s="5" t="str">
-        <x:v>dʑiəʔ21die313</x:v>
+        <x:v>jie die</x:v>
       </x:c>
     </x:row>
     <x:row r="712">
@@ -10274,7 +10274,7 @@
         <x:v>无没</x:v>
       </x:c>
       <x:c r="D712" s="5" t="str">
-        <x:v>Ǿm31məʔ12</x:v>
+        <x:v>m me</x:v>
       </x:c>
     </x:row>
     <x:row r="713">
@@ -10288,7 +10288,7 @@
         <x:v>弗是</x:v>
       </x:c>
       <x:c r="D713" s="5" t="str">
-        <x:v>fəʔ3sɿ535</x:v>
+        <x:v>fe si</x:v>
       </x:c>
     </x:row>
     <x:row r="714">
@@ -10302,7 +10302,7 @@
         <x:v>来</x:v>
       </x:c>
       <x:c r="D714" s="5" t="str">
-        <x:v>lɛ313</x:v>
+        <x:v>le</x:v>
       </x:c>
     </x:row>
     <x:row r="715">
@@ -10316,7 +10316,7 @@
         <x:v>弗来</x:v>
       </x:c>
       <x:c r="D715" s="5" t="str">
-        <x:v>fəʔ4lɛ313</x:v>
+        <x:v>fe le</x:v>
       </x:c>
     </x:row>
     <x:row r="716">
@@ -10330,7 +10330,7 @@
         <x:v>晓得</x:v>
       </x:c>
       <x:c r="D716" s="5" t="str">
-        <x:v>ɕiɑo53təʔ4</x:v>
+        <x:v>xiao te</x:v>
       </x:c>
     </x:row>
     <x:row r="717">
@@ -10344,7 +10344,7 @@
         <x:v>弗晓得</x:v>
       </x:c>
       <x:c r="D717" s="5" t="str">
-        <x:v>fəʔ3ɕiɑo53təʔ4</x:v>
+        <x:v>fe xiao te</x:v>
       </x:c>
     </x:row>
     <x:row r="718">
@@ -10358,7 +10358,7 @@
         <x:v>弗懂</x:v>
       </x:c>
       <x:c r="D718" s="5" t="str">
-        <x:v>fəʔ3toŋ535</x:v>
+        <x:v>fe tong</x:v>
       </x:c>
     </x:row>
     <x:row r="719">
@@ -10372,7 +10372,7 @@
         <x:v>[弗会]</x:v>
       </x:c>
       <x:c r="D719" s="5" t="str">
-        <x:v>fɛ55</x:v>
+        <x:v>fe</x:v>
       </x:c>
     </x:row>
     <x:row r="720">
@@ -10386,7 +10386,7 @@
         <x:v>弗会</x:v>
       </x:c>
       <x:c r="D720" s="5" t="str">
-        <x:v>fəʔ3Ǿuɛ55</x:v>
+        <x:v>fe ue</x:v>
       </x:c>
     </x:row>
     <x:row r="721">
@@ -10400,7 +10400,7 @@
         <x:v>认着</x:v>
       </x:c>
       <x:c r="D721" s="5" t="str">
-        <x:v>ȵiŋ14tɕiəʔ0</x:v>
+        <x:v>ning jie</x:v>
       </x:c>
     </x:row>
     <x:row r="722">
@@ -10414,7 +10414,7 @@
         <x:v>认弗着</x:v>
       </x:c>
       <x:c r="D722" s="5" t="str">
-        <x:v>ȵiŋ14fəʔ4dʑiəʔ212</x:v>
+        <x:v>ning fe jie</x:v>
       </x:c>
     </x:row>
     <x:row r="723">
@@ -10428,7 +10428,7 @@
         <x:v>好个</x:v>
       </x:c>
       <x:c r="D723" s="5" t="str">
-        <x:v>xɑo55ɡəʔ0</x:v>
+        <x:v>xao ge</x:v>
       </x:c>
     </x:row>
     <x:row r="724">
@@ -10442,7 +10442,7 @@
         <x:v>好</x:v>
       </x:c>
       <x:c r="D724" s="5" t="str">
-        <x:v>xɑo535</x:v>
+        <x:v>xao</x:v>
       </x:c>
     </x:row>
     <x:row r="725">
@@ -10456,7 +10456,7 @@
         <x:v>弗好</x:v>
       </x:c>
       <x:c r="D725" s="5" t="str">
-        <x:v>fəʔ3xɑo535</x:v>
+        <x:v>fe xao</x:v>
       </x:c>
     </x:row>
     <x:row r="726">
@@ -10470,7 +10470,7 @@
         <x:v>弗好个</x:v>
       </x:c>
       <x:c r="D726" s="5" t="str">
-        <x:v>fəʔ3xɑo55ɡəʔ0</x:v>
+        <x:v>fe xao ge</x:v>
       </x:c>
     </x:row>
     <x:row r="727">
@@ -10484,7 +10484,7 @@
         <x:v>该</x:v>
       </x:c>
       <x:c r="D727" s="5" t="str">
-        <x:v>kɛ334</x:v>
+        <x:v>ke</x:v>
       </x:c>
     </x:row>
     <x:row r="728">
@@ -10498,7 +10498,7 @@
         <x:v>好</x:v>
       </x:c>
       <x:c r="D728" s="5" t="str">
-        <x:v>xɑo535</x:v>
+        <x:v>xao</x:v>
       </x:c>
     </x:row>
     <x:row r="729">
@@ -10512,7 +10512,7 @@
         <x:v>讲</x:v>
       </x:c>
       <x:c r="D729" s="5" t="str">
-        <x:v>kɑŋ535</x:v>
+        <x:v>kang</x:v>
       </x:c>
     </x:row>
     <x:row r="730">
@@ -10526,7 +10526,7 @@
         <x:v>说话</x:v>
       </x:c>
       <x:c r="D730" s="5" t="str">
-        <x:v>ɕy55Ǿuɑ14</x:v>
+        <x:v>xy ua</x:v>
       </x:c>
     </x:row>
     <x:row r="731">
@@ -10540,7 +10540,7 @@
         <x:v>谈天</x:v>
       </x:c>
       <x:c r="D731" s="5" t="str">
-        <x:v>dɑ31thia334</x:v>
+        <x:v>da thia</x:v>
       </x:c>
     </x:row>
     <x:row r="732">
@@ -10554,7 +10554,7 @@
         <x:v>讴</x:v>
       </x:c>
       <x:c r="D732" s="5" t="str">
-        <x:v>Ǿiu334</x:v>
+        <x:v>iu</x:v>
       </x:c>
     </x:row>
     <x:row r="733">
@@ -10568,7 +10568,7 @@
         <x:v>烟=</x:v>
       </x:c>
       <x:c r="D733" s="5" t="str">
-        <x:v>Ǿia334</x:v>
+        <x:v>ia</x:v>
       </x:c>
     </x:row>
     <x:row r="734">
@@ -10582,7 +10582,7 @@
         <x:v>吵相骂</x:v>
       </x:c>
       <x:c r="D734" s="5" t="str">
-        <x:v>tshɑo55siɑŋ33mɤa55</x:v>
+        <x:v>tshao siang mea</x:v>
       </x:c>
     </x:row>
     <x:row r="735">
@@ -10596,7 +10596,7 @@
         <x:v>争相骂</x:v>
       </x:c>
       <x:c r="D735" s="5" t="str">
-        <x:v>tsɑŋ33siɑŋ33mɤa55</x:v>
+        <x:v>tsang siang mea</x:v>
       </x:c>
     </x:row>
     <x:row r="736">
@@ -10610,7 +10610,7 @@
         <x:v>丈=</x:v>
       </x:c>
       <x:c r="D736" s="5" t="str">
-        <x:v>dʑiɑŋ14</x:v>
+        <x:v>jiang</x:v>
       </x:c>
     </x:row>
     <x:row r="737">
@@ -10624,7 +10624,7 @@
         <x:v>白=丕=</x:v>
       </x:c>
       <x:c r="D737" s="5" t="str">
-        <x:v>bəʔ21phi535</x:v>
+        <x:v>be phi</x:v>
       </x:c>
     </x:row>
     <x:row r="738">
@@ -10638,7 +10638,7 @@
         <x:v>吹牛皮</x:v>
       </x:c>
       <x:c r="D738" s="5" t="str">
-        <x:v>tɕhy33ȵiu31bi14</x:v>
+        <x:v>qy niu bi</x:v>
       </x:c>
     </x:row>
     <x:row r="739">
@@ -10652,7 +10652,7 @@
         <x:v>脱=马屁</x:v>
       </x:c>
       <x:c r="D739" s="5" t="str">
-        <x:v>thəʔ4mɤa53phi55</x:v>
+        <x:v>the mea phi</x:v>
       </x:c>
     </x:row>
     <x:row r="740">
@@ -10666,7 +10666,7 @@
         <x:v>亨=……讲</x:v>
       </x:c>
       <x:c r="D740" s="5" t="str">
-        <x:v>xəŋ334……kɑŋ535</x:v>
+        <x:v>xeng kang</x:v>
       </x:c>
     </x:row>
     <x:row r="741">
@@ -10680,7 +10680,7 @@
         <x:v>跟……讲</x:v>
       </x:c>
       <x:c r="D741" s="5" t="str">
-        <x:v>kəŋ334……kɑŋ535</x:v>
+        <x:v>keng kang</x:v>
       </x:c>
     </x:row>
     <x:row r="742">
@@ -10694,7 +10694,7 @@
         <x:v>对弗住</x:v>
       </x:c>
       <x:c r="D742" s="5" t="str">
-        <x:v>tɛ55fəʔ0dʑy14</x:v>
+        <x:v>te fe jy</x:v>
       </x:c>
     </x:row>
     <x:row r="743">
@@ -10708,7 +10708,7 @@
         <x:v>弗好意思</x:v>
       </x:c>
       <x:c r="D743" s="5" t="str">
-        <x:v>fəʔ3xɑo55Ǿi55sɿ0</x:v>
+        <x:v>fe xao i si</x:v>
       </x:c>
     </x:row>
     <x:row r="744">
@@ -10722,7 +10722,7 @@
         <x:v>宽慢</x:v>
       </x:c>
       <x:c r="D744" s="5" t="str">
-        <x:v>khuɑ33mɑ55</x:v>
+        <x:v>khua ma</x:v>
       </x:c>
     </x:row>
     <x:row r="745">
@@ -10736,7 +10736,7 @@
         <x:v>阔</x:v>
       </x:c>
       <x:c r="D745" s="5" t="str">
-        <x:v>khuɑ55</x:v>
+        <x:v>khua</x:v>
       </x:c>
     </x:row>
     <x:row r="746">
@@ -10750,7 +10750,7 @@
         <x:v>厅=宽</x:v>
       </x:c>
       <x:c r="D746" s="5" t="str">
-        <x:v>thiŋ55khuɑ334</x:v>
+        <x:v>thing khua</x:v>
       </x:c>
     </x:row>
     <x:row r="747">
@@ -10764,7 +10764,7 @@
         <x:v>大</x:v>
       </x:c>
       <x:c r="D747" s="5" t="str">
-        <x:v>duɤ14</x:v>
+        <x:v>due</x:v>
       </x:c>
     </x:row>
     <x:row r="748">
@@ -10778,7 +10778,7 @@
         <x:v>狭</x:v>
       </x:c>
       <x:c r="D748" s="5" t="str">
-        <x:v>Ǿuɑ14</x:v>
+        <x:v>ua</x:v>
       </x:c>
     </x:row>
     <x:row r="749">
@@ -10792,7 +10792,7 @@
         <x:v>长</x:v>
       </x:c>
       <x:c r="D749" s="5" t="str">
-        <x:v>dʑiɑŋ313</x:v>
+        <x:v>jiang</x:v>
       </x:c>
     </x:row>
     <x:row r="750">
@@ -10806,7 +10806,7 @@
         <x:v>短</x:v>
       </x:c>
       <x:c r="D750" s="5" t="str">
-        <x:v>tɤ535</x:v>
+        <x:v>te</x:v>
       </x:c>
     </x:row>
     <x:row r="751">
@@ -10820,7 +10820,7 @@
         <x:v>四方</x:v>
       </x:c>
       <x:c r="D751" s="5" t="str">
-        <x:v>ɕi33fɑŋ55</x:v>
+        <x:v>xi fang</x:v>
       </x:c>
     </x:row>
     <x:row r="752">
@@ -10834,7 +10834,7 @@
         <x:v>腈</x:v>
       </x:c>
       <x:c r="D752" s="5" t="str">
-        <x:v>tɕiŋ334</x:v>
+        <x:v>jing</x:v>
       </x:c>
     </x:row>
     <x:row r="753">
@@ -10848,7 +10848,7 @@
         <x:v>壮</x:v>
       </x:c>
       <x:c r="D753" s="5" t="str">
-        <x:v>tɕyɑŋ55</x:v>
+        <x:v>jyang</x:v>
       </x:c>
     </x:row>
     <x:row r="754">
@@ -10862,7 +10862,7 @@
         <x:v>壮</x:v>
       </x:c>
       <x:c r="D754" s="5" t="str">
-        <x:v>tɕyɑŋ55</x:v>
+        <x:v>jyang</x:v>
       </x:c>
     </x:row>
     <x:row r="755">
@@ -10876,7 +10876,7 @@
         <x:v>笡</x:v>
       </x:c>
       <x:c r="D755" s="5" t="str">
-        <x:v>tshia55</x:v>
+        <x:v>tshia</x:v>
       </x:c>
     </x:row>
     <x:row r="756">
@@ -10890,7 +10890,7 @@
         <x:v>醒=</x:v>
       </x:c>
       <x:c r="D756" s="5" t="str">
-        <x:v>ɕiŋ535</x:v>
+        <x:v>xing</x:v>
       </x:c>
     </x:row>
     <x:row r="757">
@@ -10904,7 +10904,7 @@
         <x:v>笡</x:v>
       </x:c>
       <x:c r="D757" s="5" t="str">
-        <x:v>tshia55</x:v>
+        <x:v>tshia</x:v>
       </x:c>
     </x:row>
     <x:row r="758">
@@ -10918,7 +10918,7 @@
         <x:v>厚</x:v>
       </x:c>
       <x:c r="D758" s="5" t="str">
-        <x:v>kiu535</x:v>
+        <x:v>kiu</x:v>
       </x:c>
     </x:row>
     <x:row r="759">
@@ -10932,7 +10932,7 @@
         <x:v>薄</x:v>
       </x:c>
       <x:c r="D759" s="5" t="str">
-        <x:v>boʔ212</x:v>
+        <x:v>bo</x:v>
       </x:c>
     </x:row>
     <x:row r="760">
@@ -10946,7 +10946,7 @@
         <x:v>暖</x:v>
       </x:c>
       <x:c r="D760" s="5" t="str">
-        <x:v>nɤ535</x:v>
+        <x:v>ne</x:v>
       </x:c>
     </x:row>
     <x:row r="761">
@@ -10960,7 +10960,7 @@
         <x:v>暖</x:v>
       </x:c>
       <x:c r="D761" s="5" t="str">
-        <x:v>nɤ535</x:v>
+        <x:v>ne</x:v>
       </x:c>
     </x:row>
     <x:row r="762">
@@ -10974,7 +10974,7 @@
         <x:v>冷</x:v>
       </x:c>
       <x:c r="D762" s="5" t="str">
-        <x:v>lɑŋ535</x:v>
+        <x:v>lang</x:v>
       </x:c>
     </x:row>
     <x:row r="763">
@@ -10988,7 +10988,7 @@
         <x:v>冷</x:v>
       </x:c>
       <x:c r="D763" s="5" t="str">
-        <x:v>lɑŋ535</x:v>
+        <x:v>lang</x:v>
       </x:c>
     </x:row>
     <x:row r="764">
@@ -11002,7 +11002,7 @@
         <x:v>燥</x:v>
       </x:c>
       <x:c r="D764" s="5" t="str">
-        <x:v>sɑo55</x:v>
+        <x:v>sao</x:v>
       </x:c>
     </x:row>
     <x:row r="765">
@@ -11016,7 +11016,7 @@
         <x:v>尺=</x:v>
       </x:c>
       <x:c r="D765" s="5" t="str">
-        <x:v>tɕhiəʔ4</x:v>
+        <x:v>qie</x:v>
       </x:c>
     </x:row>
     <x:row r="766">
@@ -11030,7 +11030,7 @@
         <x:v>#13糟</x:v>
       </x:c>
       <x:c r="D766" s="5" t="str">
-        <x:v>Ǿɑo33tsɑo55</x:v>
+        <x:v>ao tsao</x:v>
       </x:c>
     </x:row>
     <x:row r="767">
@@ -11044,7 +11044,7 @@
         <x:v>厣=</x:v>
       </x:c>
       <x:c r="D767" s="5" t="str">
-        <x:v>Ǿie535</x:v>
+        <x:v>ie</x:v>
       </x:c>
     </x:row>
     <x:row r="768">
@@ -11058,7 +11058,7 @@
         <x:v>迟</x:v>
       </x:c>
       <x:c r="D768" s="5" t="str">
-        <x:v>dzɿ313</x:v>
+        <x:v>dzi</x:v>
       </x:c>
     </x:row>
     <x:row r="769">
@@ -11072,7 +11072,7 @@
         <x:v>迟</x:v>
       </x:c>
       <x:c r="D769" s="5" t="str">
-        <x:v>dzɿ313</x:v>
+        <x:v>dzi</x:v>
       </x:c>
     </x:row>
     <x:row r="770">
@@ -11086,7 +11086,7 @@
         <x:v>简单</x:v>
       </x:c>
       <x:c r="D770" s="5" t="str">
-        <x:v>tɕiɛ̃55tɛ̃334</x:v>
+        <x:v>jie te</x:v>
       </x:c>
     </x:row>
     <x:row r="771">
@@ -11100,7 +11100,7 @@
         <x:v>年纪轻</x:v>
       </x:c>
       <x:c r="D771" s="5" t="str">
-        <x:v>ȵia31tɕi55tɕhiŋ334</x:v>
+        <x:v>nia ji qing</x:v>
       </x:c>
     </x:row>
     <x:row r="772">
@@ -11114,7 +11114,7 @@
         <x:v>软相</x:v>
       </x:c>
       <x:c r="D772" s="5" t="str">
-        <x:v>ȵyɤ53siɑŋ55</x:v>
+        <x:v>nye siang</x:v>
       </x:c>
     </x:row>
     <x:row r="773">
@@ -11128,7 +11128,7 @@
         <x:v>花=</x:v>
       </x:c>
       <x:c r="D773" s="5" t="str">
-        <x:v>xuɑ334</x:v>
+        <x:v>xua</x:v>
       </x:c>
     </x:row>
     <x:row r="774">
@@ -11142,7 +11142,7 @@
         <x:v>焦</x:v>
       </x:c>
       <x:c r="D774" s="5" t="str">
-        <x:v>tsiɑo334</x:v>
+        <x:v>tsiao</x:v>
       </x:c>
     </x:row>
     <x:row r="775">
@@ -11156,7 +11156,7 @@
         <x:v>扎实</x:v>
       </x:c>
       <x:c r="D775" s="5" t="str">
-        <x:v>tsuɑ55ʑiəʔ212</x:v>
+        <x:v>tsua rie</x:v>
       </x:c>
     </x:row>
     <x:row r="776">
@@ -11170,7 +11170,7 @@
         <x:v>发财</x:v>
       </x:c>
       <x:c r="D776" s="5" t="str">
-        <x:v>fɤa55zɛ313</x:v>
+        <x:v>fea ze</x:v>
       </x:c>
     </x:row>
     <x:row r="777">
@@ -11184,7 +11184,7 @@
         <x:v>有铜钿</x:v>
       </x:c>
       <x:c r="D777" s="5" t="str">
-        <x:v>Ǿiu53doŋ31die14</x:v>
+        <x:v>iu dong die</x:v>
       </x:c>
     </x:row>
     <x:row r="778">
@@ -11198,7 +11198,7 @@
         <x:v>有钞票</x:v>
       </x:c>
       <x:c r="D778" s="5" t="str">
-        <x:v>Ǿiu53tshɑo53phiɑo55</x:v>
+        <x:v>iu tshao phiao</x:v>
       </x:c>
     </x:row>
     <x:row r="779">
@@ -11212,7 +11212,7 @@
         <x:v>点=股=</x:v>
       </x:c>
       <x:c r="D779" s="5" t="str">
-        <x:v>tia53ku535</x:v>
+        <x:v>tia ku</x:v>
       </x:c>
     </x:row>
     <x:row r="780">
@@ -11226,7 +11226,7 @@
         <x:v>空</x:v>
       </x:c>
       <x:c r="D780" s="5" t="str">
-        <x:v>khoŋ55</x:v>
+        <x:v>khong</x:v>
       </x:c>
     </x:row>
     <x:row r="781">
@@ -11240,7 +11240,7 @@
         <x:v>吃力</x:v>
       </x:c>
       <x:c r="D781" s="5" t="str">
-        <x:v>tɕhiəʔ4liəʔ212</x:v>
+        <x:v>qie lie</x:v>
       </x:c>
     </x:row>
     <x:row r="782">
@@ -11254,7 +11254,7 @@
         <x:v>着力</x:v>
       </x:c>
       <x:c r="D782" s="5" t="str">
-        <x:v>dʑiəʔ21liəʔ12</x:v>
+        <x:v>jie lie</x:v>
       </x:c>
     </x:row>
     <x:row r="783">
@@ -11268,7 +11268,7 @@
         <x:v>痛</x:v>
       </x:c>
       <x:c r="D783" s="5" t="str">
-        <x:v>thoŋ55</x:v>
+        <x:v>thong</x:v>
       </x:c>
     </x:row>
     <x:row r="784">
@@ -11282,7 +11282,7 @@
         <x:v>兴</x:v>
       </x:c>
       <x:c r="D784" s="5" t="str">
-        <x:v>ɕiŋ55</x:v>
+        <x:v>xing</x:v>
       </x:c>
     </x:row>
     <x:row r="785">
@@ -11296,7 +11296,7 @@
         <x:v>闹</x:v>
       </x:c>
       <x:c r="D785" s="5" t="str">
-        <x:v>nɑo14</x:v>
+        <x:v>nao</x:v>
       </x:c>
     </x:row>
     <x:row r="786">
@@ -11310,7 +11310,7 @@
         <x:v>熟</x:v>
       </x:c>
       <x:c r="D786" s="5" t="str">
-        <x:v>ʑioʔ212</x:v>
+        <x:v>rio</x:v>
       </x:c>
     </x:row>
     <x:row r="787">
@@ -11324,7 +11324,7 @@
         <x:v>生疏</x:v>
       </x:c>
       <x:c r="D787" s="5" t="str">
-        <x:v>sɑŋ33su55</x:v>
+        <x:v>sang su</x:v>
       </x:c>
     </x:row>
     <x:row r="788">
@@ -11338,7 +11338,7 @@
         <x:v>气息</x:v>
       </x:c>
       <x:c r="D788" s="5" t="str">
-        <x:v>tɕhi33ɕiəʔ4</x:v>
+        <x:v>qi xie</x:v>
       </x:c>
     </x:row>
     <x:row r="789">
@@ -11352,7 +11352,7 @@
         <x:v>鲜味</x:v>
       </x:c>
       <x:c r="D789" s="5" t="str">
-        <x:v>ɕie33fi55</x:v>
+        <x:v>xie fi</x:v>
       </x:c>
     </x:row>
     <x:row r="790">
@@ -11366,7 +11366,7 @@
         <x:v>馊气</x:v>
       </x:c>
       <x:c r="D790" s="5" t="str">
-        <x:v>ɕiu33tɕhi55</x:v>
+        <x:v>xiu qi</x:v>
       </x:c>
     </x:row>
     <x:row r="791">
@@ -11380,7 +11380,7 @@
         <x:v>腥气</x:v>
       </x:c>
       <x:c r="D791" s="5" t="str">
-        <x:v>ɕiŋ33tɕhi55</x:v>
+        <x:v>xing qi</x:v>
       </x:c>
     </x:row>
     <x:row r="792">
@@ -11394,7 +11394,7 @@
         <x:v>㽺</x:v>
       </x:c>
       <x:c r="D792" s="5" t="str">
-        <x:v>ɕiəʔ4</x:v>
+        <x:v>xie</x:v>
       </x:c>
     </x:row>
     <x:row r="793">
@@ -11408,7 +11408,7 @@
         <x:v>㽺</x:v>
       </x:c>
       <x:c r="D793" s="5" t="str">
-        <x:v>ɕiəʔ4</x:v>
+        <x:v>xie</x:v>
       </x:c>
     </x:row>
     <x:row r="794">
@@ -11422,7 +11422,7 @@
         <x:v>𧸖</x:v>
       </x:c>
       <x:c r="D794" s="5" t="str">
-        <x:v>dzɑ14</x:v>
+        <x:v>dza</x:v>
       </x:c>
     </x:row>
     <x:row r="795">
@@ -11436,7 +11436,7 @@
         <x:v>俏</x:v>
       </x:c>
       <x:c r="D795" s="5" t="str">
-        <x:v>tshiɑo55</x:v>
+        <x:v>tshiao</x:v>
       </x:c>
     </x:row>
     <x:row r="796">
@@ -11450,7 +11450,7 @@
         <x:v>好望</x:v>
       </x:c>
       <x:c r="D796" s="5" t="str">
-        <x:v>xɑo55moŋ14</x:v>
+        <x:v>xao mong</x:v>
       </x:c>
     </x:row>
     <x:row r="797">
@@ -11464,7 +11464,7 @@
         <x:v>难望</x:v>
       </x:c>
       <x:c r="D797" s="5" t="str">
-        <x:v>nɑ33moŋ14</x:v>
+        <x:v>na mong</x:v>
       </x:c>
     </x:row>
     <x:row r="798">
@@ -11478,7 +11478,7 @@
         <x:v>#14棋=</x:v>
       </x:c>
       <x:c r="D798" s="5" t="str">
-        <x:v>dʑie31dʑi14</x:v>
+        <x:v>jie ji</x:v>
       </x:c>
     </x:row>
     <x:row r="799">
@@ -11492,7 +11492,7 @@
         <x:v>会做</x:v>
       </x:c>
       <x:c r="D799" s="5" t="str">
-        <x:v>Ǿuɛ53tsuɤ55</x:v>
+        <x:v>ue tsue</x:v>
       </x:c>
     </x:row>
     <x:row r="800">
@@ -11506,7 +11506,7 @@
         <x:v>赖</x:v>
       </x:c>
       <x:c r="D800" s="5" t="str">
-        <x:v>lɑ14</x:v>
+        <x:v>la</x:v>
       </x:c>
     </x:row>
     <x:row r="801">
@@ -11520,7 +11520,7 @@
         <x:v>会=</x:v>
       </x:c>
       <x:c r="D801" s="5" t="str">
-        <x:v>Ǿuɛ14</x:v>
+        <x:v>ue</x:v>
       </x:c>
     </x:row>
     <x:row r="802">
@@ -11534,7 +11534,7 @@
         <x:v>听话</x:v>
       </x:c>
       <x:c r="D802" s="5" t="str">
-        <x:v>thiŋ33Ǿuɑ14</x:v>
+        <x:v>thing ua</x:v>
       </x:c>
     </x:row>
     <x:row r="803">
@@ -11548,7 +11548,7 @@
         <x:v>蛮</x:v>
       </x:c>
       <x:c r="D803" s="5" t="str">
-        <x:v>mɑ313</x:v>
+        <x:v>ma</x:v>
       </x:c>
     </x:row>
     <x:row r="804">
@@ -11562,7 +11562,7 @@
         <x:v>皮</x:v>
       </x:c>
       <x:c r="D804" s="5" t="str">
-        <x:v>bi313</x:v>
+        <x:v>bi</x:v>
       </x:c>
     </x:row>
     <x:row r="805">
@@ -11576,7 +11576,7 @@
         <x:v>倒=傻</x:v>
       </x:c>
       <x:c r="D805" s="5" t="str">
-        <x:v>tɑo55sɑ334</x:v>
+        <x:v>tao sa</x:v>
       </x:c>
     </x:row>
     <x:row r="806">
@@ -11590,7 +11590,7 @@
         <x:v>妈=驳=</x:v>
       </x:c>
       <x:c r="D806" s="5" t="str">
-        <x:v>mɑ33poʔ4</x:v>
+        <x:v>ma po</x:v>
       </x:c>
     </x:row>
     <x:row r="807">
@@ -11604,7 +11604,7 @@
         <x:v>木</x:v>
       </x:c>
       <x:c r="D807" s="5" t="str">
-        <x:v>moʔ212</x:v>
+        <x:v>mo</x:v>
       </x:c>
     </x:row>
     <x:row r="808">
@@ -11618,7 +11618,7 @@
         <x:v>气量大</x:v>
       </x:c>
       <x:c r="D808" s="5" t="str">
-        <x:v>tɕhi55liɑŋ14duɤ14</x:v>
+        <x:v>qi liang due</x:v>
       </x:c>
     </x:row>
     <x:row r="809">
@@ -11632,7 +11632,7 @@
         <x:v>气魄大</x:v>
       </x:c>
       <x:c r="D809" s="5" t="str">
-        <x:v>tɕhi33phəʔ4duɤ14</x:v>
+        <x:v>qi phe due</x:v>
       </x:c>
     </x:row>
     <x:row r="810">
@@ -11646,7 +11646,7 @@
         <x:v>小毛</x:v>
       </x:c>
       <x:c r="D810" s="5" t="str">
-        <x:v>siɑo55mɑo313</x:v>
+        <x:v>siao mao</x:v>
       </x:c>
     </x:row>
     <x:row r="811">
@@ -11660,7 +11660,7 @@
         <x:v>汪＝</x:v>
       </x:c>
       <x:c r="D811" s="5" t="str">
-        <x:v>Ǿuɑŋ334</x:v>
+        <x:v>uang</x:v>
       </x:c>
     </x:row>
     <x:row r="812">
@@ -11674,7 +11674,7 @@
         <x:v>樱＝</x:v>
       </x:c>
       <x:c r="D812" s="5" t="str">
-        <x:v>Ǿɑŋ334</x:v>
+        <x:v>ang</x:v>
       </x:c>
     </x:row>
     <x:row r="813">
@@ -11688,7 +11688,7 @@
         <x:v>两</x:v>
       </x:c>
       <x:c r="D813" s="5" t="str">
-        <x:v>liɑŋ535</x:v>
+        <x:v>liang</x:v>
       </x:c>
     </x:row>
     <x:row r="814">
@@ -11702,7 +11702,7 @@
         <x:v>廿</x:v>
       </x:c>
       <x:c r="D814" s="5" t="str">
-        <x:v>ȵia14</x:v>
+        <x:v>nia</x:v>
       </x:c>
     </x:row>
     <x:row r="815">
@@ -11716,7 +11716,7 @@
         <x:v>一百五</x:v>
       </x:c>
       <x:c r="D815" s="5" t="str">
-        <x:v>Ǿiəʔ3pəʔ4Ǿŋ535</x:v>
+        <x:v>ie pe ng</x:v>
       </x:c>
     </x:row>
     <x:row r="816">
@@ -11730,7 +11730,7 @@
         <x:v>两个</x:v>
       </x:c>
       <x:c r="D816" s="5" t="str">
-        <x:v>liɑŋ53kəʔ4</x:v>
+        <x:v>liang ke</x:v>
       </x:c>
     </x:row>
     <x:row r="817">
@@ -11744,7 +11744,7 @@
         <x:v>三个</x:v>
       </x:c>
       <x:c r="D817" s="5" t="str">
-        <x:v>sɑ33kəʔ4</x:v>
+        <x:v>sa ke</x:v>
       </x:c>
     </x:row>
     <x:row r="818">
@@ -11758,7 +11758,7 @@
         <x:v>只</x:v>
       </x:c>
       <x:c r="D818" s="5" t="str">
-        <x:v>tsəʔ4</x:v>
+        <x:v>tse</x:v>
       </x:c>
     </x:row>
     <x:row r="819">
@@ -11772,7 +11772,7 @@
         <x:v>只</x:v>
       </x:c>
       <x:c r="D819" s="5" t="str">
-        <x:v>tsəʔ4</x:v>
+        <x:v>tse</x:v>
       </x:c>
     </x:row>
     <x:row r="820">
@@ -11786,7 +11786,7 @@
         <x:v>个</x:v>
       </x:c>
       <x:c r="D820" s="5" t="str">
-        <x:v>kəʔ4</x:v>
+        <x:v>ke</x:v>
       </x:c>
     </x:row>
     <x:row r="821">
@@ -11800,7 +11800,7 @@
         <x:v>梗</x:v>
       </x:c>
       <x:c r="D821" s="5" t="str">
-        <x:v>kuɑŋ55</x:v>
+        <x:v>kuang</x:v>
       </x:c>
     </x:row>
     <x:row r="822">
@@ -11814,7 +11814,7 @@
         <x:v>个</x:v>
       </x:c>
       <x:c r="D822" s="5" t="str">
-        <x:v>kəʔ4</x:v>
+        <x:v>ke</x:v>
       </x:c>
     </x:row>
     <x:row r="823">
@@ -11828,7 +11828,7 @@
         <x:v>根</x:v>
       </x:c>
       <x:c r="D823" s="5" t="str">
-        <x:v>kəŋ55</x:v>
+        <x:v>keng</x:v>
       </x:c>
     </x:row>
     <x:row r="824">
@@ -11842,7 +11842,7 @@
         <x:v>张</x:v>
       </x:c>
       <x:c r="D824" s="5" t="str">
-        <x:v>tɕiɑŋ55</x:v>
+        <x:v>jiang</x:v>
       </x:c>
     </x:row>
     <x:row r="825">
@@ -11856,7 +11856,7 @@
         <x:v>部</x:v>
       </x:c>
       <x:c r="D825" s="5" t="str">
-        <x:v>bu14</x:v>
+        <x:v>bu</x:v>
       </x:c>
     </x:row>
     <x:row r="826">
@@ -11870,7 +11870,7 @@
         <x:v>退</x:v>
       </x:c>
       <x:c r="D826" s="5" t="str">
-        <x:v>thɛ55</x:v>
+        <x:v>the</x:v>
       </x:c>
     </x:row>
     <x:row r="827">
@@ -11884,7 +11884,7 @@
         <x:v>兴=</x:v>
       </x:c>
       <x:c r="D827" s="5" t="str">
-        <x:v>ɕiŋ55</x:v>
+        <x:v>xing</x:v>
       </x:c>
     </x:row>
     <x:row r="828">
@@ -11898,7 +11898,7 @@
         <x:v>埭</x:v>
       </x:c>
       <x:c r="D828" s="5" t="str">
-        <x:v>dɑ14</x:v>
+        <x:v>da</x:v>
       </x:c>
     </x:row>
     <x:row r="829">
@@ -11912,7 +11912,7 @@
         <x:v>埭</x:v>
       </x:c>
       <x:c r="D829" s="5" t="str">
-        <x:v>dɑ14</x:v>
+        <x:v>da</x:v>
       </x:c>
     </x:row>
     <x:row r="830">
@@ -11926,7 +11926,7 @@
         <x:v>根</x:v>
       </x:c>
       <x:c r="D830" s="5" t="str">
-        <x:v>kəŋ55</x:v>
+        <x:v>keng</x:v>
       </x:c>
     </x:row>
     <x:row r="831">
@@ -11940,7 +11940,7 @@
         <x:v>粒</x:v>
       </x:c>
       <x:c r="D831" s="5" t="str">
-        <x:v>lɤ14</x:v>
+        <x:v>le</x:v>
       </x:c>
     </x:row>
     <x:row r="832">
@@ -11954,7 +11954,7 @@
         <x:v>餐</x:v>
       </x:c>
       <x:c r="D832" s="5" t="str">
-        <x:v>tshɑ55</x:v>
+        <x:v>tsha</x:v>
       </x:c>
     </x:row>
     <x:row r="833">
@@ -11968,7 +11968,7 @@
         <x:v>帖</x:v>
       </x:c>
       <x:c r="D833" s="5" t="str">
-        <x:v>thia55</x:v>
+        <x:v>thia</x:v>
       </x:c>
     </x:row>
     <x:row r="834">
@@ -11982,7 +11982,7 @@
         <x:v>埭</x:v>
       </x:c>
       <x:c r="D834" s="5" t="str">
-        <x:v>dɑ14</x:v>
+        <x:v>da</x:v>
       </x:c>
     </x:row>
     <x:row r="835">
@@ -11996,7 +11996,7 @@
         <x:v>排</x:v>
       </x:c>
       <x:c r="D835" s="5" t="str">
-        <x:v>bɑ313</x:v>
+        <x:v>ba</x:v>
       </x:c>
     </x:row>
     <x:row r="836">
@@ -12010,7 +12010,7 @@
         <x:v>角</x:v>
       </x:c>
       <x:c r="D836" s="5" t="str">
-        <x:v>koʔ4</x:v>
+        <x:v>ko</x:v>
       </x:c>
     </x:row>
     <x:row r="837">
@@ -12024,7 +12024,7 @@
         <x:v>起</x:v>
       </x:c>
       <x:c r="D837" s="5" t="str">
-        <x:v>tɕhi55</x:v>
+        <x:v>qi</x:v>
       </x:c>
     </x:row>
     <x:row r="838">
@@ -12038,7 +12038,7 @@
         <x:v>样</x:v>
       </x:c>
       <x:c r="D838" s="5" t="str">
-        <x:v>Ǿiɑŋ14</x:v>
+        <x:v>iang</x:v>
       </x:c>
     </x:row>
     <x:row r="839">
@@ -12052,7 +12052,7 @@
         <x:v>帝=儿</x:v>
       </x:c>
       <x:c r="D839" s="5" t="str">
-        <x:v>tiŋ55</x:v>
+        <x:v>ting</x:v>
       </x:c>
     </x:row>
     <x:row r="840">
@@ -12066,7 +12066,7 @@
         <x:v>帝=</x:v>
       </x:c>
       <x:c r="D840" s="5" t="str">
-        <x:v>ti55</x:v>
+        <x:v>ti</x:v>
       </x:c>
     </x:row>
     <x:row r="841">
@@ -12080,7 +12080,7 @@
         <x:v>记</x:v>
       </x:c>
       <x:c r="D841" s="5" t="str">
-        <x:v>tɕie55</x:v>
+        <x:v>jie</x:v>
       </x:c>
     </x:row>
     <x:row r="842">
@@ -12094,7 +12094,7 @@
         <x:v>记</x:v>
       </x:c>
       <x:c r="D842" s="5" t="str">
-        <x:v>tɕie55</x:v>
+        <x:v>jie</x:v>
       </x:c>
     </x:row>
     <x:row r="843">
@@ -12108,7 +12108,7 @@
         <x:v>操=</x:v>
       </x:c>
       <x:c r="D843" s="5" t="str">
-        <x:v>tshɑo55</x:v>
+        <x:v>tshao</x:v>
       </x:c>
     </x:row>
     <x:row r="844">
@@ -12122,7 +12122,7 @@
         <x:v>在=</x:v>
       </x:c>
       <x:c r="D844" s="5" t="str">
-        <x:v>zɛ14</x:v>
+        <x:v>ze</x:v>
       </x:c>
     </x:row>
     <x:row r="845">
@@ -12136,7 +12136,7 @@
         <x:v>埭</x:v>
       </x:c>
       <x:c r="D845" s="5" t="str">
-        <x:v>dɑ14</x:v>
+        <x:v>da</x:v>
       </x:c>
     </x:row>
     <x:row r="846">
@@ -12150,7 +12150,7 @@
         <x:v>我侬</x:v>
       </x:c>
       <x:c r="D846" s="5" t="str">
-        <x:v>Ǿɑ33noŋ535</x:v>
+        <x:v>a nong</x:v>
       </x:c>
     </x:row>
     <x:row r="847">
@@ -12164,7 +12164,7 @@
         <x:v>侬</x:v>
       </x:c>
       <x:c r="D847" s="5" t="str">
-        <x:v>noŋ535</x:v>
+        <x:v>nong</x:v>
       </x:c>
     </x:row>
     <x:row r="848">
@@ -12178,7 +12178,7 @@
         <x:v>侬</x:v>
       </x:c>
       <x:c r="D848" s="5" t="str">
-        <x:v>noŋ535</x:v>
+        <x:v>nong</x:v>
       </x:c>
     </x:row>
     <x:row r="849">
@@ -12192,7 +12192,7 @@
         <x:v>渠</x:v>
       </x:c>
       <x:c r="D849" s="5" t="str">
-        <x:v>ɡəʔ212</x:v>
+        <x:v>ge</x:v>
       </x:c>
     </x:row>
     <x:row r="850">
@@ -12206,7 +12206,7 @@
         <x:v>我浪=</x:v>
       </x:c>
       <x:c r="D850" s="5" t="str">
-        <x:v>Ǿɑ55lɑŋ14</x:v>
+        <x:v>a lang</x:v>
       </x:c>
     </x:row>
     <x:row r="851">
@@ -12220,7 +12220,7 @@
         <x:v>自浪=</x:v>
       </x:c>
       <x:c r="D851" s="5" t="str">
-        <x:v>ʑi14lɑŋ0</x:v>
+        <x:v>ri lang</x:v>
       </x:c>
     </x:row>
     <x:row r="852">
@@ -12234,7 +12234,7 @@
         <x:v>自当=</x:v>
       </x:c>
       <x:c r="D852" s="5" t="str">
-        <x:v>ʑi14tɑŋ0</x:v>
+        <x:v>ri tang</x:v>
       </x:c>
     </x:row>
     <x:row r="853">
@@ -12248,7 +12248,7 @@
         <x:v>尔浪=</x:v>
       </x:c>
       <x:c r="D853" s="5" t="str">
-        <x:v>Ǿŋ55lɑŋ14</x:v>
+        <x:v>ng lang</x:v>
       </x:c>
     </x:row>
     <x:row r="854">
@@ -12262,7 +12262,7 @@
         <x:v>侬浪=</x:v>
       </x:c>
       <x:c r="D854" s="5" t="str">
-        <x:v>noŋ55lɑŋ14</x:v>
+        <x:v>nong lang</x:v>
       </x:c>
     </x:row>
     <x:row r="855">
@@ -12276,7 +12276,7 @@
         <x:v>渠浪=</x:v>
       </x:c>
       <x:c r="D855" s="5" t="str">
-        <x:v>ɡəʔ21lɑŋ14</x:v>
+        <x:v>ge lang</x:v>
       </x:c>
     </x:row>
     <x:row r="856">
@@ -12290,7 +12290,7 @@
         <x:v>自</x:v>
       </x:c>
       <x:c r="D856" s="5" t="str">
-        <x:v>ʑi14</x:v>
+        <x:v>ri</x:v>
       </x:c>
     </x:row>
     <x:row r="857">
@@ -12304,7 +12304,7 @@
         <x:v>别个</x:v>
       </x:c>
       <x:c r="D857" s="5" t="str">
-        <x:v>bie14kəʔ0</x:v>
+        <x:v>bie ke</x:v>
       </x:c>
     </x:row>
     <x:row r="858">
@@ -12318,7 +12318,7 @@
         <x:v>我浪=爷</x:v>
       </x:c>
       <x:c r="D858" s="5" t="str">
-        <x:v>Ǿɑ55lɑŋ14Ǿia313</x:v>
+        <x:v>a lang ia</x:v>
       </x:c>
     </x:row>
     <x:row r="859">
@@ -12332,7 +12332,7 @@
         <x:v>尔浪=爷</x:v>
       </x:c>
       <x:c r="D859" s="5" t="str">
-        <x:v>Ǿŋ55nɑŋ14Ǿia313</x:v>
+        <x:v>ng nang ia</x:v>
       </x:c>
     </x:row>
     <x:row r="860">
@@ -12346,7 +12346,7 @@
         <x:v>渠浪=爷</x:v>
       </x:c>
       <x:c r="D860" s="5" t="str">
-        <x:v>ɡəʔ21lɑŋ14Ǿia313</x:v>
+        <x:v>ge lang ia</x:v>
       </x:c>
     </x:row>
     <x:row r="861">
@@ -12360,7 +12360,7 @@
         <x:v>个个</x:v>
       </x:c>
       <x:c r="D861" s="5" t="str">
-        <x:v>kəʔ3kəʔ4</x:v>
+        <x:v>ke ke</x:v>
       </x:c>
     </x:row>
     <x:row r="862">
@@ -12374,7 +12374,7 @@
         <x:v>末=个</x:v>
       </x:c>
       <x:c r="D862" s="5" t="str">
-        <x:v>məʔ21ɡəʔ12</x:v>
+        <x:v>me ge</x:v>
       </x:c>
     </x:row>
     <x:row r="863">
@@ -12388,7 +12388,7 @@
         <x:v>哪个</x:v>
       </x:c>
       <x:c r="D863" s="5" t="str">
-        <x:v>lɑ55ɡəʔ12</x:v>
+        <x:v>la ge</x:v>
       </x:c>
     </x:row>
     <x:row r="864">
@@ -12402,7 +12402,7 @@
         <x:v>个里</x:v>
       </x:c>
       <x:c r="D864" s="5" t="str">
-        <x:v>kəʔ3li535</x:v>
+        <x:v>ke li</x:v>
       </x:c>
     </x:row>
     <x:row r="865">
@@ -12416,7 +12416,7 @@
         <x:v>末=里</x:v>
       </x:c>
       <x:c r="D865" s="5" t="str">
-        <x:v>məʔ21li14</x:v>
+        <x:v>me li</x:v>
       </x:c>
     </x:row>
     <x:row r="866">
@@ -12430,7 +12430,7 @@
         <x:v>个亨=</x:v>
       </x:c>
       <x:c r="D866" s="5" t="str">
-        <x:v>kəʔ4xɑŋ334</x:v>
+        <x:v>ke xang</x:v>
       </x:c>
     </x:row>
     <x:row r="867">
@@ -12444,7 +12444,7 @@
         <x:v>末=亨=</x:v>
       </x:c>
       <x:c r="D867" s="5" t="str">
-        <x:v>məʔ21xɑŋ334</x:v>
+        <x:v>me xang</x:v>
       </x:c>
     </x:row>
     <x:row r="868">
@@ -12458,7 +12458,7 @@
         <x:v>哪亨=</x:v>
       </x:c>
       <x:c r="D868" s="5" t="str">
-        <x:v>lɑ55xɑŋ334</x:v>
+        <x:v>la xang</x:v>
       </x:c>
     </x:row>
     <x:row r="869">
@@ -12472,7 +12472,7 @@
         <x:v>亨=</x:v>
       </x:c>
       <x:c r="D869" s="5" t="str">
-        <x:v>xɑŋ334</x:v>
+        <x:v>xang</x:v>
       </x:c>
     </x:row>
     <x:row r="870">
@@ -12486,7 +12486,7 @@
         <x:v>个亨=</x:v>
       </x:c>
       <x:c r="D870" s="5" t="str">
-        <x:v>kəʔ4xɑŋ334</x:v>
+        <x:v>ke xang</x:v>
       </x:c>
     </x:row>
     <x:row r="871">
@@ -12500,7 +12500,7 @@
         <x:v>哪亨=</x:v>
       </x:c>
       <x:c r="D871" s="5" t="str">
-        <x:v>lɑ55xɑŋ334</x:v>
+        <x:v>la xang</x:v>
       </x:c>
     </x:row>
     <x:row r="872">
@@ -12514,7 +12514,7 @@
         <x:v>淡=</x:v>
       </x:c>
       <x:c r="D872" s="5" t="str">
-        <x:v>tɑ535</x:v>
+        <x:v>ta</x:v>
       </x:c>
     </x:row>
     <x:row r="873">
@@ -12528,7 +12528,7 @@
         <x:v>淡=实=</x:v>
       </x:c>
       <x:c r="D873" s="5" t="str">
-        <x:v>tɑ55ʑiəʔ212</x:v>
+        <x:v>ta rie</x:v>
       </x:c>
     </x:row>
     <x:row r="874">
@@ -12542,7 +12542,7 @@
         <x:v>淡=东西</x:v>
       </x:c>
       <x:c r="D874" s="5" t="str">
-        <x:v>tɑ55doŋ31ɕie55</x:v>
+        <x:v>ta dong xie</x:v>
       </x:c>
     </x:row>
     <x:row r="875">
@@ -12556,7 +12556,7 @@
         <x:v>淡=实=</x:v>
       </x:c>
       <x:c r="D875" s="5" t="str">
-        <x:v>tɑ55ʑiəʔ212</x:v>
+        <x:v>ta rie</x:v>
       </x:c>
     </x:row>
     <x:row r="876">
@@ -12570,7 +12570,7 @@
         <x:v>为淡=干</x:v>
       </x:c>
       <x:c r="D876" s="5" t="str">
-        <x:v>Ǿui14tɑ53kɤ55</x:v>
+        <x:v>ui ta ke</x:v>
       </x:c>
     </x:row>
     <x:row r="877">
@@ -12584,7 +12584,7 @@
         <x:v>为淡=事干</x:v>
       </x:c>
       <x:c r="D877" s="5" t="str">
-        <x:v>Ǿui14tɑ55zɿ31kɤ55</x:v>
+        <x:v>ui ta zi ke</x:v>
       </x:c>
     </x:row>
     <x:row r="878">
@@ -12598,7 +12598,7 @@
         <x:v>做淡=实=</x:v>
       </x:c>
       <x:c r="D878" s="5" t="str">
-        <x:v>tsuɤ33tɑ55ʑiəʔ12</x:v>
+        <x:v>tsue ta rie</x:v>
       </x:c>
     </x:row>
     <x:row r="879">
@@ -12612,7 +12612,7 @@
         <x:v>做淡=事干</x:v>
       </x:c>
       <x:c r="D879" s="5" t="str">
-        <x:v>tsuɤ33tɑ55zɿ31kɤ55</x:v>
+        <x:v>tsue ta zi ke</x:v>
       </x:c>
     </x:row>
     <x:row r="880">
@@ -12626,7 +12626,7 @@
         <x:v>淡=干</x:v>
       </x:c>
       <x:c r="D880" s="5" t="str">
-        <x:v>tɑ53kɤ55</x:v>
+        <x:v>ta ke</x:v>
       </x:c>
     </x:row>
     <x:row r="881">
@@ -12640,7 +12640,7 @@
         <x:v>几许儿</x:v>
       </x:c>
       <x:c r="D881" s="5" t="str">
-        <x:v>tɕi53xəŋ55</x:v>
+        <x:v>ji xeng</x:v>
       </x:c>
     </x:row>
     <x:row r="882">
@@ -12654,7 +12654,7 @@
         <x:v>尽</x:v>
       </x:c>
       <x:c r="D882" s="5" t="str">
-        <x:v>ɕiŋ55</x:v>
+        <x:v>xing</x:v>
       </x:c>
     </x:row>
     <x:row r="883">
@@ -12668,7 +12668,7 @@
         <x:v>猛</x:v>
       </x:c>
       <x:c r="D883" s="5" t="str">
-        <x:v>mɑŋ535</x:v>
+        <x:v>mang</x:v>
       </x:c>
     </x:row>
     <x:row r="884">
@@ -12682,7 +12682,7 @@
         <x:v>危险</x:v>
       </x:c>
       <x:c r="D884" s="5" t="str">
-        <x:v>Ǿui33ɕie535</x:v>
+        <x:v>ui xie</x:v>
       </x:c>
     </x:row>
     <x:row r="885">
@@ -12696,7 +12696,7 @@
         <x:v>还要</x:v>
       </x:c>
       <x:c r="D885" s="5" t="str">
-        <x:v>Ǿuɑ31Ǿiɑo55</x:v>
+        <x:v>ua iao</x:v>
       </x:c>
     </x:row>
     <x:row r="886">
@@ -12710,7 +12710,7 @@
         <x:v>顶</x:v>
       </x:c>
       <x:c r="D886" s="5" t="str">
-        <x:v>tiŋ535</x:v>
+        <x:v>ting</x:v>
       </x:c>
     </x:row>
     <x:row r="887">
@@ -12724,7 +12724,7 @@
         <x:v>统</x:v>
       </x:c>
       <x:c r="D887" s="5" t="str">
-        <x:v>thoŋ535</x:v>
+        <x:v>thong</x:v>
       </x:c>
     </x:row>
     <x:row r="888">
@@ -12738,7 +12738,7 @@
         <x:v>共拢</x:v>
       </x:c>
       <x:c r="D888" s="5" t="str">
-        <x:v>ɡoŋ14loŋ0</x:v>
+        <x:v>gong long</x:v>
       </x:c>
     </x:row>
     <x:row r="889">
@@ -12752,7 +12752,7 @@
         <x:v>一共拢</x:v>
       </x:c>
       <x:c r="D889" s="5" t="str">
-        <x:v>Ǿiəʔ4ɡoŋ14loŋ0</x:v>
+        <x:v>ie gong long</x:v>
       </x:c>
     </x:row>
     <x:row r="890">
@@ -12766,7 +12766,7 @@
         <x:v>总共</x:v>
       </x:c>
       <x:c r="D890" s="5" t="str">
-        <x:v>tsoŋ55ɡoŋ14</x:v>
+        <x:v>tsong gong</x:v>
       </x:c>
     </x:row>
     <x:row r="891">
@@ -12780,7 +12780,7 @@
         <x:v>一起生</x:v>
       </x:c>
       <x:c r="D891" s="5" t="str">
-        <x:v>Ǿiəʔ3tɕhi55sɑŋ0</x:v>
+        <x:v>ie qi sang</x:v>
       </x:c>
     </x:row>
     <x:row r="892">
@@ -12794,7 +12794,7 @@
         <x:v>做堆</x:v>
       </x:c>
       <x:c r="D892" s="5" t="str">
-        <x:v>tsuɤ55tɛ334</x:v>
+        <x:v>tsue te</x:v>
       </x:c>
     </x:row>
     <x:row r="893">
@@ -12808,7 +12808,7 @@
         <x:v>便</x:v>
       </x:c>
       <x:c r="D893" s="5" t="str">
-        <x:v>bie14</x:v>
+        <x:v>bie</x:v>
       </x:c>
     </x:row>
     <x:row r="894">
@@ -12822,7 +12822,7 @@
         <x:v>就</x:v>
       </x:c>
       <x:c r="D894" s="5" t="str">
-        <x:v>ʑiu14</x:v>
+        <x:v>riu</x:v>
       </x:c>
     </x:row>
     <x:row r="895">
@@ -12836,7 +12836,7 @@
         <x:v>正好</x:v>
       </x:c>
       <x:c r="D895" s="5" t="str">
-        <x:v>tɕiŋ33xɑo55</x:v>
+        <x:v>jing xao</x:v>
       </x:c>
     </x:row>
     <x:row r="896">
@@ -12850,7 +12850,7 @@
         <x:v>还正</x:v>
       </x:c>
       <x:c r="D896" s="5" t="str">
-        <x:v>Ǿuɑ31tɕiŋ55</x:v>
+        <x:v>ua jing</x:v>
       </x:c>
     </x:row>
     <x:row r="897">
@@ -12864,7 +12864,7 @@
         <x:v>还正</x:v>
       </x:c>
       <x:c r="D897" s="5" t="str">
-        <x:v>Ǿuɑ31tɕiŋ55</x:v>
+        <x:v>ua jing</x:v>
       </x:c>
     </x:row>
     <x:row r="898">
@@ -12878,7 +12878,7 @@
         <x:v>便</x:v>
       </x:c>
       <x:c r="D898" s="5" t="str">
-        <x:v>bie14</x:v>
+        <x:v>bie</x:v>
       </x:c>
     </x:row>
     <x:row r="899">
@@ -12892,7 +12892,7 @@
         <x:v>专门</x:v>
       </x:c>
       <x:c r="D899" s="5" t="str">
-        <x:v>tɕyɤ44məŋ55</x:v>
+        <x:v>jye meng</x:v>
       </x:c>
     </x:row>
     <x:row r="900">
@@ -12906,7 +12906,7 @@
         <x:v>只讲</x:v>
       </x:c>
       <x:c r="D900" s="5" t="str">
-        <x:v>tɕiəʔ3kɑŋ55</x:v>
+        <x:v>jie kang</x:v>
       </x:c>
     </x:row>
     <x:row r="901">
@@ -12920,7 +12920,7 @@
         <x:v>异=</x:v>
       </x:c>
       <x:c r="D901" s="5" t="str">
-        <x:v>Ǿi14</x:v>
+        <x:v>i</x:v>
       </x:c>
     </x:row>
     <x:row r="902">
@@ -12934,7 +12934,7 @@
         <x:v>横直</x:v>
       </x:c>
       <x:c r="D902" s="5" t="str">
-        <x:v>Ǿuɑŋ31dʑiəʔ12</x:v>
+        <x:v>uang jie</x:v>
       </x:c>
     </x:row>
     <x:row r="903">
@@ -12948,7 +12948,7 @@
         <x:v>未</x:v>
       </x:c>
       <x:c r="D903" s="5" t="str">
-        <x:v>mi14</x:v>
+        <x:v>mi</x:v>
       </x:c>
     </x:row>
     <x:row r="904">
@@ -12962,7 +12962,7 @@
         <x:v>弗</x:v>
       </x:c>
       <x:c r="D904" s="5" t="str">
-        <x:v>fəʔ4</x:v>
+        <x:v>fe</x:v>
       </x:c>
     </x:row>
     <x:row r="905">
@@ -12976,7 +12976,7 @@
         <x:v>弗要</x:v>
       </x:c>
       <x:c r="D905" s="5" t="str">
-        <x:v>fəʔ4Ǿiɑo55</x:v>
+        <x:v>fe iao</x:v>
       </x:c>
     </x:row>
     <x:row r="906">
@@ -12990,7 +12990,7 @@
         <x:v>弗要</x:v>
       </x:c>
       <x:c r="D906" s="5" t="str">
-        <x:v>fəʔ4Ǿiɑo55</x:v>
+        <x:v>fe iao</x:v>
       </x:c>
     </x:row>
     <x:row r="907">
@@ -13004,7 +13004,7 @@
         <x:v>弗用</x:v>
       </x:c>
       <x:c r="D907" s="5" t="str">
-        <x:v>fəʔ4Ǿioŋ55</x:v>
+        <x:v>fe iong</x:v>
       </x:c>
     </x:row>
     <x:row r="908">
@@ -13018,7 +13018,7 @@
         <x:v>推板一帝=儿</x:v>
       </x:c>
       <x:c r="D908" s="5" t="str">
-        <x:v>thɛ33pɑ55Ǿiəʔ3tiŋ55</x:v>
+        <x:v>the pa ie ting</x:v>
       </x:c>
     </x:row>
     <x:row r="909">
@@ -13032,7 +13032,7 @@
         <x:v>情愿</x:v>
       </x:c>
       <x:c r="D909" s="5" t="str">
-        <x:v>ʑiŋ31ȵyɤ14</x:v>
+        <x:v>ring nye</x:v>
       </x:c>
     </x:row>
     <x:row r="910">
@@ -13046,7 +13046,7 @@
         <x:v>择意</x:v>
       </x:c>
       <x:c r="D910" s="5" t="str">
-        <x:v>dzəʔ21Ǿi14</x:v>
+        <x:v>dze i</x:v>
       </x:c>
     </x:row>
     <x:row r="911">
@@ -13060,7 +13060,7 @@
         <x:v>白白</x:v>
       </x:c>
       <x:c r="D911" s="5" t="str">
-        <x:v>bəʔ21bəʔ12</x:v>
+        <x:v>be be</x:v>
       </x:c>
     </x:row>
     <x:row r="912">
@@ -13074,7 +13074,7 @@
         <x:v>定住</x:v>
       </x:c>
       <x:c r="D912" s="5" t="str">
-        <x:v>diŋ14tɕy0</x:v>
+        <x:v>ding jy</x:v>
       </x:c>
     </x:row>
     <x:row r="913">
@@ -13088,7 +13088,7 @@
         <x:v>笃定</x:v>
       </x:c>
       <x:c r="D913" s="5" t="str">
-        <x:v>toʔ4diŋ14</x:v>
+        <x:v>to ding</x:v>
       </x:c>
     </x:row>
     <x:row r="914">
@@ -13102,7 +13102,7 @@
         <x:v>倘把=</x:v>
       </x:c>
       <x:c r="D914" s="5" t="str">
-        <x:v>thɑŋ55pɤa0</x:v>
+        <x:v>thang pea</x:v>
       </x:c>
     </x:row>
     <x:row r="915">
@@ -13116,7 +13116,7 @@
         <x:v>边</x:v>
       </x:c>
       <x:c r="D915" s="5" t="str">
-        <x:v>pie334</x:v>
+        <x:v>pie</x:v>
       </x:c>
     </x:row>
     <x:row r="916">
@@ -13130,7 +13130,7 @@
         <x:v>哼=</x:v>
       </x:c>
       <x:c r="D916" s="5" t="str">
-        <x:v>xəŋ334</x:v>
+        <x:v>xeng</x:v>
       </x:c>
     </x:row>
     <x:row r="917">
@@ -13144,7 +13144,7 @@
         <x:v>跟</x:v>
       </x:c>
       <x:c r="D917" s="5" t="str">
-        <x:v>kəŋ334</x:v>
+        <x:v>keng</x:v>
       </x:c>
     </x:row>
     <x:row r="918">
@@ -13158,7 +13158,7 @@
         <x:v>哼=</x:v>
       </x:c>
       <x:c r="D918" s="5" t="str">
-        <x:v>xəŋ334</x:v>
+        <x:v>xeng</x:v>
       </x:c>
     </x:row>
     <x:row r="919">
@@ -13172,7 +13172,7 @@
         <x:v>跟</x:v>
       </x:c>
       <x:c r="D919" s="5" t="str">
-        <x:v>kəŋ334</x:v>
+        <x:v>keng</x:v>
       </x:c>
     </x:row>
     <x:row r="920">
@@ -13186,7 +13186,7 @@
         <x:v>朝</x:v>
       </x:c>
       <x:c r="D920" s="5" t="str">
-        <x:v>dʑiɑo313</x:v>
+        <x:v>jiao</x:v>
       </x:c>
     </x:row>
     <x:row r="921">
@@ -13200,7 +13200,7 @@
         <x:v>问</x:v>
       </x:c>
       <x:c r="D921" s="5" t="str">
-        <x:v>məŋ14</x:v>
+        <x:v>meng</x:v>
       </x:c>
     </x:row>
     <x:row r="922">
@@ -13214,7 +13214,7 @@
         <x:v>根据</x:v>
       </x:c>
       <x:c r="D922" s="5" t="str">
-        <x:v>kəŋ33tɕy55</x:v>
+        <x:v>keng jy</x:v>
       </x:c>
     </x:row>
     <x:row r="923">
@@ -13228,7 +13228,7 @@
         <x:v>跟</x:v>
       </x:c>
       <x:c r="D923" s="5" t="str">
-        <x:v>kəŋ334</x:v>
+        <x:v>keng</x:v>
       </x:c>
     </x:row>
     <x:row r="924">
@@ -13242,7 +13242,7 @@
         <x:v>帮</x:v>
       </x:c>
       <x:c r="D924" s="5" t="str">
-        <x:v>pɑŋ334</x:v>
+        <x:v>pang</x:v>
       </x:c>
     </x:row>
     <x:row r="925">
@@ -13256,7 +13256,7 @@
         <x:v>分</x:v>
       </x:c>
       <x:c r="D925" s="5" t="str">
-        <x:v>fəŋ334</x:v>
+        <x:v>feng</x:v>
       </x:c>
     </x:row>
     <x:row r="926">
@@ -13270,7 +13270,7 @@
         <x:v>倘把=</x:v>
       </x:c>
       <x:c r="D926" s="5" t="str">
-        <x:v>thɑŋ55pɤa0</x:v>
+        <x:v>thang pea</x:v>
       </x:c>
     </x:row>
     <x:row r="927">
@@ -13284,7 +13284,7 @@
         <x:v>随便</x:v>
       </x:c>
       <x:c r="D927" s="5" t="str">
-        <x:v>ʑie31bie14</x:v>
+        <x:v>rie bie</x:v>
       </x:c>
     </x:row>
     <x:row r="928">
@@ -13298,7 +13298,7 @@
         <x:v>随便</x:v>
       </x:c>
       <x:c r="D928" s="5" t="str">
-        <x:v>zui31bie14</x:v>
+        <x:v>zui bie</x:v>
       </x:c>
     </x:row>
     <x:row r="929">
@@ -13312,7 +13312,7 @@
         <x:v>小张昨儿日儿钓了一梗大鱼，我未钓着。</x:v>
       </x:c>
       <x:c r="D929" s="5" t="str">
-        <x:v>siɑo55tɕiɑŋ33sɑŋ55ȵi14tiɑo55ləʔ0Ǿiəʔ3kuɑŋ55tuɤ55ȵy14，Ǿɑ55mi14tiɑo55tɕiəʔ0。</x:v>
+        <x:v>siao jiang sang ni tiao le ie kuang tue ny a mi tiao jie.</x:v>
       </x:c>
     </x:row>
     <x:row r="930">
@@ -13326,7 +13326,7 @@
         <x:v>a.侬平常吃香烟弗？b.我弗吃香烟。</x:v>
       </x:c>
       <x:c r="D930" s="5" t="str">
-        <x:v>a.noŋ535biŋ31dʑiɑŋ14tɕhiəʔ4ɕiɑŋ33Ǿia55fəʔ0？b.Ǿɑ535fəʔ4tɕhiəʔ4ɕiɑŋ33Ǿia55。</x:v>
+        <x:v>a nong bing jiang qie xiang ia fe? b a fe qie xiang ia.</x:v>
       </x:c>
     </x:row>
     <x:row r="931">
@@ -13340,7 +13340,7 @@
         <x:v>a.侬平常吃弗吃香烟？b.我弗吃香烟。</x:v>
       </x:c>
       <x:c r="D931" s="5" t="str">
-        <x:v>a.noŋ535biŋ31dʑiɑŋ14tɕhiəʔ4fəʔ4tɕhiəʔ4ɕiɑŋ33Ǿia55？b.Ǿɑ535fəʔ4tɕhiəʔ4ɕiɑŋ33Ǿia55。</x:v>
+        <x:v>a nong bing jiang qie fe qie xiang ia? b a fe qie xiang ia.</x:v>
       </x:c>
     </x:row>
     <x:row r="932">
@@ -13354,7 +13354,7 @@
         <x:v>a.个件事干侬哼=渠讲过未？b.我哼=渠讲过了。</x:v>
       </x:c>
       <x:c r="D932" s="5" t="str">
-        <x:v>a.kəʔ4dʑie14zɿ31kɤ55noŋ535xəŋ33ɡəʔ212kɑŋ53kuɤ55mi0？b.Ǿɑ535xəŋ33ɡəʔ212kɑŋ53kuɤ55ləʔ0。</x:v>
+        <x:v>a ke jie zi ke nong xeng ge kang kue mi? b a xeng ge kang kue le.</x:v>
       </x:c>
     </x:row>
     <x:row r="933">
@@ -13368,7 +13368,7 @@
         <x:v>侬吃饭还是吃馒头？</x:v>
       </x:c>
       <x:c r="D933" s="5" t="str">
-        <x:v>noŋ535tɕhiəʔ4vɑ14Ǿuɑ31sɿ535tɕhiəʔ4mɤ31diu14？</x:v>
+        <x:v>nong qie va ua si qie me diu?</x:v>
       </x:c>
     </x:row>
     <x:row r="934">
@@ -13382,7 +13382,7 @@
         <x:v>侬到底答弗答应渠？</x:v>
       </x:c>
       <x:c r="D934" s="5" t="str">
-        <x:v>noŋ535tɑo55ti0tuɑ53fəʔ4tuɑ53Ǿiŋ55ɡəʔ212？</x:v>
+        <x:v>nong tao ti tua fe tua ing ge?</x:v>
       </x:c>
     </x:row>
     <x:row r="935">
@@ -13396,7 +13396,7 @@
         <x:v>侬到底答应弗答应渠？</x:v>
       </x:c>
       <x:c r="D935" s="5" t="str">
-        <x:v>noŋ535tɑo55ti0tuɑ53Ǿiŋ55fəʔ0tuɑ53Ǿiŋ55ɡəʔ212？</x:v>
+        <x:v>nong tao ti tua ing fe tua ing ge?</x:v>
       </x:c>
     </x:row>
     <x:row r="936">
@@ -13410,7 +13410,7 @@
         <x:v>a.讴小强一起生去电影院望《刘三姊》。b.个本电影渠望过了。</x:v>
       </x:c>
       <x:c r="D936" s="5" t="str">
-        <x:v>a.Ǿiu33siɑo55dʑiɑŋ313Ǿiəʔ3tɕhi55sɑŋ0khɤ55tia53Ǿiŋ55Ǿyɤ14moŋ14liu31sɑ33tɕi535。b.kəʔ3pəŋ55tia53Ǿiŋ535ɡəʔ212moŋ14kuɤ0ləʔ0。</x:v>
+        <x:v>a iu siao jiang ie qi sang khe tia ing ye mong liu sa ji. b ke peng tia ing ge mong kue le.</x:v>
       </x:c>
     </x:row>
     <x:row r="937">
@@ -13424,7 +13424,7 @@
         <x:v>a.讴小强一起生去电影院望《刘三姊》。b.渠个本电影望过了。</x:v>
       </x:c>
       <x:c r="D937" s="5" t="str">
-        <x:v>a.Ǿiu33siɑo55dʑiɑŋ313Ǿiəʔ3tɕhi55sɑŋ0khɤ55tia53Ǿiŋ55Ǿyɤ14moŋ14liu31sɑ33tɕi535。b.ɡəʔ212kəʔ3pəŋ55tia53Ǿiŋ535moŋ14kuɤ0ləʔ0。</x:v>
+        <x:v>a iu siao jiang ie qi sang khe tia ing ye mong liu sa ji. b ge ke peng tia ing mong kue le.</x:v>
       </x:c>
     </x:row>
     <x:row r="938">
@@ -13438,7 +13438,7 @@
         <x:v>侬帮碗碟洗记渠。</x:v>
       </x:c>
       <x:c r="D938" s="5" t="str">
-        <x:v>noŋ535pɑŋ33Ǿuɑ55dia14ɕie53tɕie55ɡəʔ212。</x:v>
+        <x:v>nong pang ua dia xie jie ge.</x:v>
       </x:c>
     </x:row>
     <x:row r="939">
@@ -13452,7 +13452,7 @@
         <x:v>侬分碗碟洗记渠。</x:v>
       </x:c>
       <x:c r="D939" s="5" t="str">
-        <x:v>noŋ535fəŋ33Ǿuɑ55dia14ɕie53tɕie55ɡəʔ212。</x:v>
+        <x:v>nong feng ua dia xie jie ge.</x:v>
       </x:c>
     </x:row>
     <x:row r="940">
@@ -13466,7 +13466,7 @@
         <x:v>渠帮桔儿皮剥掉了，就是还未吃。</x:v>
       </x:c>
       <x:c r="D940" s="5" t="str">
-        <x:v>ɡəʔ212pɑŋ33tɕyẽ55bi313poʔ4tiɑo55ləʔ0，ʑiu14sɿ0Ǿuɑ31mi14tɕhiəʔ4。</x:v>
+        <x:v>ge pang jye bi po tiao le riu si ua mi qie.</x:v>
       </x:c>
     </x:row>
     <x:row r="941">
@@ -13480,7 +13480,7 @@
         <x:v>渠分桔儿皮剥掉了，就是还未吃。</x:v>
       </x:c>
       <x:c r="D941" s="5" t="str">
-        <x:v>ɡəʔ212fəŋ33tɕyẽ55bi313poʔ4tiɑo55ləʔ0，ʑiu14sɿ0Ǿuɑ31mi14tɕhiəʔ4。</x:v>
+        <x:v>ge feng jye bi po tiao le riu si ua mi qie.</x:v>
       </x:c>
     </x:row>
     <x:row r="942">
@@ -13494,7 +13494,7 @@
         <x:v>渠浪=帮教室都装上了空调。</x:v>
       </x:c>
       <x:c r="D942" s="5" t="str">
-        <x:v>ɡəʔ21lɑŋ14pɑŋ33tɕiɑo33ɕiəʔ4tu55tɕyɑŋ33ɕiɑŋ55ləʔ0khoŋ33diɑo313。</x:v>
+        <x:v>ge lang pang jiao xie tu jyang xiang le khong diao.</x:v>
       </x:c>
     </x:row>
     <x:row r="943">
@@ -13508,7 +13508,7 @@
         <x:v>帽让风吹走了。</x:v>
       </x:c>
       <x:c r="D943" s="5" t="str">
-        <x:v>mɑo14ȵiɑŋ14foŋ334tɕhy33tɕiu55ləʔ0。</x:v>
+        <x:v>mao niang fong qy jiu le.</x:v>
       </x:c>
     </x:row>
     <x:row r="944">
@@ -13522,7 +13522,7 @@
         <x:v>张明一个包让㽺个人抢走了，人也推板一帝=儿敲伤了。</x:v>
       </x:c>
       <x:c r="D944" s="5" t="str">
-        <x:v>tɕiɑŋ33miŋ313Ǿiəʔ3kəʔ4pɑo334ȵiɑŋ14ɕiəʔ4kəʔ4ȵiŋ313tshiɑŋ53tɕiu55ləʔ0，ȵiŋ313Ǿia55thɛ33pɑ55Ǿiəʔ3tiŋ55khɑo33ɕiɑŋ33ləʔ0。</x:v>
+        <x:v>jiang ming ie ke pao niang xie ke ning tshiang jiu le ning ia the pa ie ting khao xiang le.</x:v>
       </x:c>
     </x:row>
     <x:row r="945">
@@ -13536,7 +13536,7 @@
         <x:v>一记添儿要落雨了，尔浪=弗要别=出去了。</x:v>
       </x:c>
       <x:c r="D945" s="5" t="str">
-        <x:v>Ǿiəʔ3tɕie55thiɛ̃334Ǿiɑo55loʔ21Ǿy55ləʔ0，Ǿŋ55nɑŋ14fəʔ3Ǿiɑo55biəʔ21tɕhyəʔ3khɤ55ləʔ0。</x:v>
+        <x:v>ie jie thie iao lo y le ng nang fe iao bie qye khe le.</x:v>
       </x:c>
     </x:row>
     <x:row r="946">
@@ -13550,7 +13550,7 @@
         <x:v>个块面布危险#14糟了，#11掉去算了。</x:v>
       </x:c>
       <x:c r="D946" s="5" t="str">
-        <x:v>kəʔ3khuɛ55mie31pu55Ǿui33ɕie535Ǿɑo33tsɑo55ləʔ0，liu55tiɑo0khɤ0sɤ55ləʔ0。</x:v>
+        <x:v>ke khue mie pu ui xie ao tsao le liu tiao khe se le.</x:v>
       </x:c>
     </x:row>
     <x:row r="947">
@@ -13564,7 +13564,7 @@
         <x:v>个张车票我浪=是来车站里买个。</x:v>
       </x:c>
       <x:c r="D947" s="5" t="str">
-        <x:v>kəʔ3tɕiɑŋ55tshia33phiɑo55Ǿɑ55lɑŋ14sɿ55lɛ31tshia33dzɑ14li0mɑ55kəʔ0。</x:v>
+        <x:v>ke jiang tshia phiao a lang si le tshia dza li ma ke.</x:v>
       </x:c>
     </x:row>
     <x:row r="948">
@@ -13578,7 +13578,7 @@
         <x:v>一张地图贴得墙上。</x:v>
       </x:c>
       <x:c r="D948" s="5" t="str">
-        <x:v>Ǿiəʔ3tɕiɑŋ55ti55du14thia55təʔ0ziɑŋ31ʑiɑŋ14。</x:v>
+        <x:v>ie jiang ti du thia te ziang riang.</x:v>
       </x:c>
     </x:row>
     <x:row r="949">
@@ -13592,7 +13592,7 @@
         <x:v>墙上贴了一张地图。</x:v>
       </x:c>
       <x:c r="D949" s="5" t="str">
-        <x:v>ziɑŋ31ʑiɑŋ14thia55ləʔ0Ǿiəʔ3tɕiɑŋ55ti55du14。</x:v>
+        <x:v>ziang riang thia le ie jiang ti du.</x:v>
       </x:c>
     </x:row>
     <x:row r="950">
@@ -13606,7 +13606,7 @@
         <x:v>一个老个人睏得床上。</x:v>
       </x:c>
       <x:c r="D950" s="5" t="str">
-        <x:v>Ǿiəʔ3kəʔ4lɑo55kəʔ0ȵiŋ313khuəŋ55təʔ0ʑyɑŋ31ʑiɑŋ14。</x:v>
+        <x:v>ie ke lao ke ning khueng te ryang riang.</x:v>
       </x:c>
     </x:row>
     <x:row r="951">
@@ -13620,7 +13620,7 @@
         <x:v>床上睏了一个老个人。</x:v>
       </x:c>
       <x:c r="D951" s="5" t="str">
-        <x:v>ʑyɑŋ31ʑiɑŋ14khuəŋ55ləʔ0Ǿiəʔ3kəʔ4lɑo55kəʔ0ȵiŋ313。</x:v>
+        <x:v>ryang riang khueng le ie ke lao ke ning.</x:v>
       </x:c>
     </x:row>
     <x:row r="952">
@@ -13634,7 +13634,7 @@
         <x:v>溪里有好许多小鱼来末=里游。</x:v>
       </x:c>
       <x:c r="D952" s="5" t="str">
-        <x:v>tɕhie33li55Ǿiu535xɑo55ɕy0tuɤ0siɑo55ȵy313lɛ31məʔ21li14Ǿiu313。</x:v>
+        <x:v>qie li iu xao xy tue siao ny le me li iu.</x:v>
       </x:c>
     </x:row>
     <x:row r="953">
@@ -13648,7 +13648,7 @@
         <x:v>前面𧼱过来一个壮猛个小鬼王。</x:v>
       </x:c>
       <x:c r="D953" s="5" t="str">
-        <x:v>zia31mie14biəʔ212kuɤ55lɛ0Ǿiəʔ3kəʔ4tɕyɑŋ55mɑŋ535kəʔ0siɑo55tɕy55Ǿuɑŋ313。</x:v>
+        <x:v>zia mie bie kue le ie ke jyang mang ke siao jy uang.</x:v>
       </x:c>
     </x:row>
     <x:row r="954">
@@ -13662,7 +13662,7 @@
         <x:v>渠浪=窝=里一记工夫死了三只猪。</x:v>
       </x:c>
       <x:c r="D954" s="5" t="str">
-        <x:v>ɡəʔ21laŋ14Ǿuɤ33li535Ǿiəʔ3tɕie55koŋ33fu55sɿ55ləʔ0sɑ33tsəʔ4tɕy334。</x:v>
+        <x:v>ge lang ue li ie jie kong fu si le sa tse jy.</x:v>
       </x:c>
     </x:row>
     <x:row r="955">
@@ -13676,7 +13676,7 @@
         <x:v>个部汽车要开得广州去。</x:v>
       </x:c>
       <x:c r="D955" s="5" t="str">
-        <x:v>kəʔ4bu14tɕhi33tshia55Ǿiɑo55khɛ33təʔ4kuɑŋ55tɕiu33khɤ55。</x:v>
+        <x:v>ke bu qi tshia iao khe te kuang jiu khe.</x:v>
       </x:c>
     </x:row>
     <x:row r="956">
@@ -13690,7 +13690,7 @@
         <x:v>个些学生坐了两日两夜个汽车了。</x:v>
       </x:c>
       <x:c r="D956" s="5" t="str">
-        <x:v>kəʔ3səʔ4Ǿoʔ21sɑŋ55suɤ55ləʔ0liɑŋ55ȵiəʔ21liɑŋ55Ǿia14kəʔ0tɕhi33tshia55ləʔ0。</x:v>
+        <x:v>ke se o sang sue le liang nie liang ia ke qi tshia le.</x:v>
       </x:c>
     </x:row>
     <x:row r="957">
@@ -13704,7 +13704,7 @@
         <x:v>侬尝尝渠做个点心再走。</x:v>
       </x:c>
       <x:c r="D957" s="5" t="str">
-        <x:v>noŋ535ʑiɑŋ31ʑiɑŋ14ɡəʔ212tsuɤ55kəʔ0tia55ɕiŋ334tsɛ33tɕiu535。</x:v>
+        <x:v>nong riang riang ge tsue ke tia xing tse jiu.</x:v>
       </x:c>
     </x:row>
     <x:row r="958">
@@ -13718,7 +13718,7 @@
         <x:v>a.侬来末=里唱淡=实=？b.我未唱过，我来个里放录音。</x:v>
       </x:c>
       <x:c r="D958" s="5" t="str">
-        <x:v>a.noŋ535lɛ31məʔ21li14tɕhiɑŋ55tɑ55ʑiəʔ212。b.Ǿɑ535mi14tɕhiɑŋ55kuɤ0，Ǿɑ535lɛ31kəʔ3li535fɑŋ55loʔ21Ǿiŋ334。</x:v>
+        <x:v>a nong le me li qiang ta rie. b a mi qiang kue a le ke li fang lo ing.</x:v>
       </x:c>
     </x:row>
     <x:row r="959">
@@ -13732,7 +13732,7 @@
         <x:v>a.侬来末=里唱淡=实=？b.弗是我唱个，我来个里放录音。</x:v>
       </x:c>
       <x:c r="D959" s="5" t="str">
-        <x:v>a.noŋ535lɛ31məʔ21li14tɕhiɑŋ55tɑ55ʑiəʔ212。b.fəʔ3sɿ535Ǿɑ535tɕhiɑŋ55kəʔ0，Ǿɑ535lɛ31kəʔ3li535fɑŋ55loʔ21Ǿiŋ334。</x:v>
+        <x:v>a nong le me li qiang ta rie. b fe si a qiang ke a le ke li fang lo ing.</x:v>
       </x:c>
     </x:row>
     <x:row r="960">
@@ -13746,7 +13746,7 @@
         <x:v>a.我吃过兔个肉，侬吃过未？b.还未，我未吃过。</x:v>
       </x:c>
       <x:c r="D960" s="5" t="str">
-        <x:v>a.Ǿɑ535tɕhiəʔ3kuɤ55thu55kəʔ0ȵioʔ212，noŋ535tɕhiəʔ3kuɤ55mi0？b.Ǿuɑ31mi14，Ǿɑ535mi14tɕhiəʔ4kuɤ。</x:v>
+        <x:v>a a qie kue thu ke nio nong qie kue mi? b ua mi a mi qie kue.</x:v>
       </x:c>
     </x:row>
     <x:row r="961">
@@ -13760,7 +13760,7 @@
         <x:v>我洗浴过了，今日儿弗去打篮球了。</x:v>
       </x:c>
       <x:c r="D961" s="5" t="str">
-        <x:v>Ǿɑ535ɕie55Ǿioʔ212ɡuɤ14ləʔ0，tɕiŋ33ȵi55fəʔ3khɤ55tɑŋ55lɛ̃31dʑiu14ləʔ0。</x:v>
+        <x:v>a xie io gue le jing ni fe khe tang le jiu le.</x:v>
       </x:c>
     </x:row>
     <x:row r="962">
@@ -13774,7 +13774,7 @@
         <x:v>我洗过浴了，今日儿弗去打篮球了。</x:v>
       </x:c>
       <x:c r="D962" s="5" t="str">
-        <x:v>Ǿɑ535ɕie53kuɤ55Ǿioʔ212ləʔ0，tɕiŋ33ȵi55fəʔ3khɤ55tɑŋ55lɛ̃31dʑiu14ləʔ0。</x:v>
+        <x:v>a xie kue io le jing ni fe khe tang le jiu le.</x:v>
       </x:c>
     </x:row>
     <x:row r="963">
@@ -13788,7 +13788,7 @@
         <x:v>我算得太快了，算𧸖了，让我再算一遍过。</x:v>
       </x:c>
       <x:c r="D963" s="5" t="str">
-        <x:v>Ǿɑ535sɤ55təʔ0thɛ55khuɑ55ləʔ0，sɤ55dzɑ14ləʔ0，ȵiɑŋ14Ǿɑ535tsɛ55sɤ55Ǿiəʔ3pie55kuɤ0。</x:v>
+        <x:v>a se te the khua le se dza le niang a tse se ie pie kue.</x:v>
       </x:c>
     </x:row>
     <x:row r="964">
@@ -13802,7 +13802,7 @@
         <x:v>渠一记高兴[起来]便唱歌了。</x:v>
       </x:c>
       <x:c r="D964" s="5" t="str">
-        <x:v>ɡəʔ212Ǿiəʔ3tɕie55kɑo33ɕiŋ55tɕhieʔ0bie14tɕhiɑŋ33kuɤ33ləʔ0。</x:v>
+        <x:v>ge ie jie kao xing qie bie qiang kue le.</x:v>
       </x:c>
     </x:row>
     <x:row r="965">
@@ -13816,7 +13816,7 @@
         <x:v>还正个记哪个来个里谈论我浪=老师？</x:v>
       </x:c>
       <x:c r="D965" s="5" t="str">
-        <x:v>Ǿuɑ31tɕiŋ55kəʔ3tɕie55lɑ53kəʔ4lɛ31kəʔ3li535dɑ31ləŋ14Ǿɑ55lɑŋ14lɑo55sɿ334？</x:v>
+        <x:v>ua jing ke jie la ke le ke li da leng a lang lao si?</x:v>
       </x:c>
     </x:row>
     <x:row r="966">
@@ -13830,7 +13830,7 @@
         <x:v>还正写了一半，还要写了去。</x:v>
       </x:c>
       <x:c r="D966" s="5" t="str">
-        <x:v>Ǿuɑ31tɕiŋ55sia55ləʔ0Ǿiəʔ3pɤ55，Ǿuɑ31Ǿiɑo55sia55loʔ3khɤ55。</x:v>
+        <x:v>ua jing sia le ie pe ua iao sia lo khe.</x:v>
       </x:c>
     </x:row>
     <x:row r="967">
@@ -13844,7 +13844,7 @@
         <x:v>侬还正吃了一碗饭，再吃碗添儿。</x:v>
       </x:c>
       <x:c r="D967" s="5" t="str">
-        <x:v>noŋ535Ǿuɑ31tɕiŋ55tɕhiəʔ3ləʔ0Ǿiəʔ3Ǿuɑ55vɑ14，tsɛ55tɕhiəʔ3Ǿuɑ55thiɛ̃334。</x:v>
+        <x:v>nong ua jing qie le ie ua va tse qie ua thie.</x:v>
       </x:c>
     </x:row>
     <x:row r="968">
@@ -13858,7 +13858,7 @@
         <x:v>让小个人走起，侬再帮展览会认认真真望一遍过。</x:v>
       </x:c>
       <x:c r="D968" s="5" t="str">
-        <x:v>ȵiaŋ14siɑo55kəʔ0ȵiŋ313tɕiu53tɕhi535，noŋ535tsɛ55pɑŋ33tsɛ̃55lɛ̃55Ǿui14ȵiŋ53ȵiŋ53tɕiŋ33tɕiŋ55moŋ14Ǿiəʔ3pie55kuɤ0。</x:v>
+        <x:v>niang siao ke ning jiu qi nong tse pang tse le ui ning ning jing jing mong ie pie kue.</x:v>
       </x:c>
     </x:row>
     <x:row r="969">
@@ -13872,7 +13872,7 @@
         <x:v>渠来电视机前面望记望记睏去了。</x:v>
       </x:c>
       <x:c r="D969" s="5" t="str">
-        <x:v>ɡəʔ212lɛ313diɛ̃14sɿ55tɕi334zia31mie14moŋ14tɕie0moŋ14tɕie0khuəŋ55khɤ0ləʔ0。</x:v>
+        <x:v>ge le die si ji zia mie mong jie mong jie khueng khe le.</x:v>
       </x:c>
     </x:row>
     <x:row r="970">
@@ -13886,7 +13886,7 @@
         <x:v>侬算算起，个帝=儿钞票够弗够用？</x:v>
       </x:c>
       <x:c r="D970" s="5" t="str">
-        <x:v>noŋ535sɤ55sɤ0tɕhi0，kəʔ3tiŋ55tshɑo53phiɑo55kiu55fəʔ4kiu55Ǿioŋ14？</x:v>
+        <x:v>nong se se qi ke ting tshao phiao kiu fe kiu iong?</x:v>
       </x:c>
     </x:row>
     <x:row r="971">
@@ -13900,7 +13900,7 @@
         <x:v>老师是弗是分侬一本危险厚个书？</x:v>
       </x:c>
       <x:c r="D971" s="5" t="str">
-        <x:v>lɑo55sɿ334sɿ53fəʔ3sɿ535fəŋ33noŋ535Ǿiəʔ3pəŋ55Ǿui33ɕie53kiu535kəʔ0ɕy334？</x:v>
+        <x:v>lao si si fe si feng nong ie peng ui xie kiu ke xy?</x:v>
       </x:c>
     </x:row>
     <x:row r="972">
@@ -13914,7 +13914,7 @@
         <x:v>老师是弗是分侬一本厚猛个书？</x:v>
       </x:c>
       <x:c r="D972" s="5" t="str">
-        <x:v>lɑo55sɿ334sɿ53fəʔ3sɿ535fəŋ33noŋ535Ǿiəʔ3pəŋ55kiu53mɑŋ535kəʔ0ɕy334？</x:v>
+        <x:v>lao si si fe si feng nong ie peng kiu mang ke xy?</x:v>
       </x:c>
     </x:row>
     <x:row r="973">
@@ -13928,7 +13928,7 @@
         <x:v>渠让末=个卖药个骗走一干块钞票。</x:v>
       </x:c>
       <x:c r="D973" s="5" t="str">
-        <x:v>ɡəʔ212ȵiɑŋ14məʔ21ɡəʔ12mɑ14Ǿiəʔ21kəʔ0phie55tɕiu0Ǿiəʔ3tshia55khuɛ0tshɑo53phiɑo55。</x:v>
+        <x:v>ge niang me ge ma ie ke phie jiu ie tshia khue tshao phiao.</x:v>
       </x:c>
     </x:row>
     <x:row r="974">
@@ -13942,7 +13942,7 @@
         <x:v>a.上个月我问渠借了三百块钞票。b.我上个月借得渠三百块钞票。</x:v>
       </x:c>
       <x:c r="D974" s="5" t="str">
-        <x:v>a.ʑiɑŋ14kəʔ0ȵyɤ14Ǿɑ535məŋ14ɡəʔ212tsia55ləʔ0sɑ33pəʔ4khuɛ0tshɑo53phiɑo55。b.Ǿɑ535ʑiɑŋ14kəʔ0ȵyɤ14tsia55təʔ0ɡəʔ212sɑ33pəʔ4khuɛ0tshɑo53phiɑo55。</x:v>
+        <x:v>a riang ke nye a meng ge tsia le sa pe khue tshao phiao. b a riang ke nye tsia te ge sa pe khue tshao phiao.</x:v>
       </x:c>
     </x:row>
     <x:row r="975">
@@ -13956,7 +13956,7 @@
         <x:v>a.上个月我问渠借了三百块钞票。b.我上个月借渠三百块钞票。</x:v>
       </x:c>
       <x:c r="D975" s="5" t="str">
-        <x:v>a.ʑiɑŋ14kəʔ0ȵyɤ14Ǿɑ535məŋ14ɡəʔ212tsia55ləʔ0sɑ33pəʔ4khuɛ0tshɑo53phiɑo55。b.Ǿɑ535ʑiɑŋ14kəʔ0ȵyɤ14tsia55ɡəʔ212sɑ33pəʔ4khuɛ0tshɑo53phiɑo55。</x:v>
+        <x:v>a riang ke nye a meng ge tsia le sa pe khue tshao phiao. b a riang ke nye tsia ge sa pe khue tshao phiao.</x:v>
       </x:c>
     </x:row>
     <x:row r="976">
@@ -13970,7 +13970,7 @@
         <x:v>a.王先生个刀开得危险好。b.王先生个刀开得危险好。</x:v>
       </x:c>
       <x:c r="D976" s="5" t="str">
-        <x:v>a.Ǿuɑŋ31ɕie33sɑŋ55kəʔ0tɑo334khɛ33təʔ0Ǿui33ɕie53xɑo535。b.Ǿuɑŋ31ɕie33sɑŋ55kəʔ0tɑo334khɛ33təʔ0Ǿui33ɕie53xɑo535。</x:v>
+        <x:v>a uang xie sang ke tao khe te ui xie xao. b uang xie sang ke tao khe te ui xie xao.</x:v>
       </x:c>
     </x:row>
     <x:row r="977">
@@ -13984,7 +13984,7 @@
         <x:v>我弗好怪别个，只好怪我自。</x:v>
       </x:c>
       <x:c r="D977" s="5" t="str">
-        <x:v>Ǿɑ535fəʔ3xɑo535kuɑ55bie14kəʔ0，tɕiəʔ4xɑo535kuɑ55Ǿɑ55ʑi14。</x:v>
+        <x:v>a fe xao kua bie ke jie xao kua a ri.</x:v>
       </x:c>
     </x:row>
     <x:row r="978">
@@ -13998,7 +13998,7 @@
         <x:v>a.明朝王经理会弗会来公司？b.我望渠弗会来。</x:v>
       </x:c>
       <x:c r="D978" s="5" t="str">
-        <x:v>a.miŋ31tɕiɑo334Ǿuɑŋ31tɕi33li535Ǿuɛ55fəʔ3Ǿuɛ55lɛ313koŋ33sɿ55？b.Ǿɑ535moŋ14ɡəʔ212fəʔ3Ǿuɛ55lɛ313。</x:v>
+        <x:v>a ming jiao uang ji li ue fe ue le kong si? b a mong ge fe ue le.</x:v>
       </x:c>
     </x:row>
     <x:row r="979">
@@ -14012,7 +14012,7 @@
         <x:v>a.明朝王经理会来公司弗？b.我望渠[弗会]来。</x:v>
       </x:c>
       <x:c r="D979" s="5" t="str">
-        <x:v>a.miŋ31tɕiɑo334Ǿuɑŋ31tɕi33li535Ǿuɛ55lɛ313koŋ33sɿ55fəʔ0？b.Ǿɑ535moŋ14ɡəʔ212fɛ55lɛ313。</x:v>
+        <x:v>a ming jiao uang ji li ue le kong si fe? b a mong ge fe le.</x:v>
       </x:c>
     </x:row>
     <x:row r="980">
@@ -14026,7 +14026,7 @@
         <x:v>我浪=用淡=实=车分个些家具从南京运归来呢？</x:v>
       </x:c>
       <x:c r="D980" s="5" t="str">
-        <x:v>Ǿɑ55lɑŋ14Ǿioŋ14tɑ55ʑiəʔ212tshia334fəŋ33kəʔ4səʔ4tɕia33dʑy14zoŋ313nɤ31tɕiŋ55Ǿyəŋ14kuɛ55lɛ55ȵi55？</x:v>
+        <x:v>a lang iong ta rie tshia feng ke se jia jy zong ne jing yeng kue le ni?</x:v>
       </x:c>
     </x:row>
     <x:row r="981">
@@ -14040,7 +14040,7 @@
         <x:v>渠跟生病个人一样隑得沙发上。</x:v>
       </x:c>
       <x:c r="D981" s="5" t="str">
-        <x:v>ɡəʔ212kəŋ33sɑŋ33biŋ14kəʔ0ȵiŋ313Ǿi55Ǿiɑŋ14ɡɛ14təʔ0sɑ33fəʔ4ɕiɑŋ0。</x:v>
+        <x:v>ge keng sang bing ke ning i iang ge te sa fe xiang.</x:v>
       </x:c>
     </x:row>
     <x:row r="982">
@@ -14054,7 +14054,7 @@
         <x:v>个亨=样子做生活，连后生都吃弗落。</x:v>
       </x:c>
       <x:c r="D982" s="5" t="str">
-        <x:v>kəʔ4xɑŋ334Ǿiɑŋ53tsɿ535tsuɤ55sɑŋ33Ǿuɑ14，lie313Ǿeu55sɑŋ334tu55tɕhiəʔ4fəʔ4loʔ212。</x:v>
+        <x:v>ke xang iang tsi tsue sang ua lie eu sang tu qie fe lo.</x:v>
       </x:c>
     </x:row>
     <x:row r="983">
@@ -14068,7 +14068,7 @@
         <x:v>渠爬上顶后面一班车走了。我侬推板一帝=，只好自慢慢儿𧼱转学堂里。</x:v>
       </x:c>
       <x:c r="D983" s="5" t="str">
-        <x:v>ɡəʔ212bɤa31ʑiɑŋ14tiŋ55Ǿeu55mie14Ǿiəʔ3pɑ55tshia334tɕiu55ləʔ0。Ǿɑ33noŋ535thɛ33pɑ55Ǿiəʔ3ti55，tɕiəʔ4xɑo0ʑi14mɑ33mɑ55ȵi334biəʔ21tɕyɤ55Ǿoʔ21dɑŋ14li0。</x:v>
+        <x:v>ge bea riang ting eu mie ie pa tshia jiu le. a nong the pa ie ti jie xao ri ma ma ni bie jye o dang li.</x:v>
       </x:c>
     </x:row>
     <x:row r="984">
@@ -14082,7 +14082,7 @@
         <x:v>个首诗哪个写个？哪个猜着我便赏渠十块钞票。</x:v>
       </x:c>
       <x:c r="D984" s="5" t="str">
-        <x:v>kəʔ3ɕiu55sɿ334lɑ55ɡəʔ12sia55kəʔ0？lɑ55ɡəʔ21tshɛ33tɕiəʔ4，Ǿa535bie14ɕiɑŋ55ɡə212ʑiəʔ21khuɛ55tshɑo53phiɑo55。</x:v>
+        <x:v>ke xiu si la ge sia ke? la ge tshe jie a bie xiang ge rie khue tshao phiao.</x:v>
       </x:c>
     </x:row>
     <x:row r="985">
@@ -14096,7 +14096,7 @@
         <x:v>我分侬个末=本书是我教初中个娘舅写个。</x:v>
       </x:c>
       <x:c r="D985" s="5" t="str">
-        <x:v>Ǿɑ535fəŋ33noŋ535kəʔ0məʔ21pəŋ55ɕy334，sɿ55Ǿɑ535kɑo33tshu33tɕioŋ334kəʔ0ȵiɑŋ31dʑiu14sia55kəʔ0。</x:v>
+        <x:v>a feng nong ke me peng xy si a kao tshu jiong ke niang jiu sia ke.</x:v>
       </x:c>
     </x:row>
     <x:row r="986">
@@ -14110,7 +14110,7 @@
         <x:v>侬比我长些，渠比侬还要长。</x:v>
       </x:c>
       <x:c r="D986" s="5" t="str">
-        <x:v>noŋ535pi53Ǿɑ535dʑiɑŋ31zəʔ12，ɡə212pi53noŋ535Ǿuɑ31Ǿiɑo55dʑiɑŋ313。</x:v>
+        <x:v>nong pi a jiang ze ge pi nong ua iao jiang.</x:v>
       </x:c>
     </x:row>
     <x:row r="987">
@@ -14124,7 +14124,7 @@
         <x:v>老王跟老张一样长。</x:v>
       </x:c>
       <x:c r="D987" s="5" t="str">
-        <x:v>lɑo55Ǿuɑŋ313kəŋ33lɑo55tɕiɑŋ334Ǿi55Ǿiɑŋ14dʑiɑŋ313。</x:v>
+        <x:v>lao uang keng lao jiang i iang jiang.</x:v>
       </x:c>
     </x:row>
     <x:row r="988">
@@ -14138,7 +14138,7 @@
         <x:v>我去起，尔浪=两个再坐记添儿。</x:v>
       </x:c>
       <x:c r="D988" s="5" t="str">
-        <x:v>Ǿɑ535khɤ55tɕhi535，Ǿŋ55nɑŋ14liɑŋ53kəʔ4tsɛ55suɤ53tɕie55thiɛ̃334。</x:v>
+        <x:v>a khe qi ng nang liang ke tse sue jie thie.</x:v>
       </x:c>
     </x:row>
     <x:row r="989">
@@ -14152,7 +14152,7 @@
         <x:v>我讲弗过渠，随便哪个都讲弗过个个货。</x:v>
       </x:c>
       <x:c r="D989" s="5" t="str">
-        <x:v>Ǿɑ535kɑŋ53fəʔ3kuɤ55ɡəʔ212，ʑie31bie14lɑ53kəʔ4tu33kɑŋ53fəʔ3kuɤ55kəʔ3kəʔ4xuɤ55。</x:v>
+        <x:v>a kang fe kue ge rie bie la ke tu kang fe kue ke ke xue.</x:v>
       </x:c>
     </x:row>
     <x:row r="990">
@@ -14166,7 +14166,7 @@
         <x:v>我讲弗渠过，随便哪个都讲弗过个个货。</x:v>
       </x:c>
       <x:c r="D990" s="5" t="str">
-        <x:v>Ǿɑ535kɑŋ53fəʔ3ɡəʔ212kuɤ55，ʑie31bie14lɑ53kəʔ4tu33kɑŋ53fəʔ3kuɤ55kəʔ3kəʔ4xuɤ55。</x:v>
+        <x:v>a kang fe ge kue rie bie la ke tu kang fe kue ke ke xue.</x:v>
       </x:c>
     </x:row>
     <x:row r="991">
@@ -14180,7 +14180,7 @@
         <x:v>我讲渠弗过，随便哪个都讲弗过个个货。</x:v>
       </x:c>
       <x:c r="D991" s="5" t="str">
-        <x:v>Ǿɑ535kɑŋ55ɡəʔ212fəʔ3kuɤ55，ʑie31bie14lɑ53kəʔ4tu33kɑŋ53fəʔ3kuɤ55kəʔ3kəʔ4xuɤ55。</x:v>
+        <x:v>a kang ge fe kue rie bie la ke tu kang fe kue ke ke xue.</x:v>
       </x:c>
     </x:row>
     <x:row r="992">
@@ -14194,7 +14194,7 @@
         <x:v>上趟就买了一本书，今日儿要多买两本。</x:v>
       </x:c>
       <x:c r="D992" s="5" t="str">
-        <x:v>ʑiɑŋ14thɑŋ0ʑiu14mɑ55ləʔ0Ǿiəʔ3pəŋ55ɕy334，tɕiŋ33ȵi55Ǿiɑo33tuɤ33mɑ535liɑŋ55pəŋ334。</x:v>
+        <x:v>riang thang riu ma le ie peng xy jing ni iao tue ma liang peng.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
